--- a/data/input/bank/Excel_Marzo.xlsx
+++ b/data/input/bank/Excel_Marzo.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aprendiz.it\Desktop\Automatizacion Conciliacion\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aprendiz.it\Desktop\bank_reconciliation_project\data\input\bank\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -5124,24 +5124,12 @@
       <family val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="-0.249977111117893"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="8">
@@ -5233,7 +5221,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -5328,75 +5316,44 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="5"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="7"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="7"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="9"/>
     </xf>
   </cellXfs>
@@ -5738,8 +5695,7 @@
   <cols>
     <col min="3" max="3" width="19.125" customWidth="1"/>
     <col min="4" max="4" width="14.25" customWidth="1"/>
-    <col min="5" max="5" width="15.25" style="32" customWidth="1"/>
-    <col min="6" max="6" width="15.25" style="43" customWidth="1"/>
+    <col min="5" max="6" width="15.25" style="32" customWidth="1"/>
     <col min="7" max="7" width="16.5" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5843,7 +5799,7 @@
       <c r="E9" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="F9" s="44" t="s">
+      <c r="F9" s="33" t="s">
         <v>5</v>
       </c>
       <c r="G9" s="4" t="s">
@@ -5866,7 +5822,7 @@
       <c r="E10" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="F10" s="45"/>
+      <c r="F10" s="35"/>
       <c r="G10" s="8" t="s">
         <v>10</v>
       </c>
@@ -5887,7 +5843,7 @@
       <c r="E11" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="F11" s="45"/>
+      <c r="F11" s="35"/>
       <c r="G11" s="8" t="s">
         <v>13</v>
       </c>
@@ -5908,7 +5864,7 @@
       <c r="E12" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="F12" s="45"/>
+      <c r="F12" s="35"/>
       <c r="G12" s="8" t="s">
         <v>15</v>
       </c>
@@ -5929,7 +5885,7 @@
       <c r="E13" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="F13" s="45"/>
+      <c r="F13" s="35"/>
       <c r="G13" s="8" t="s">
         <v>17</v>
       </c>
@@ -5950,7 +5906,7 @@
       <c r="E14" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="F14" s="45"/>
+      <c r="F14" s="35"/>
       <c r="G14" s="8" t="s">
         <v>19</v>
       </c>
@@ -5971,7 +5927,7 @@
       <c r="E15" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="F15" s="45"/>
+      <c r="F15" s="35"/>
       <c r="G15" s="8" t="s">
         <v>21</v>
       </c>
@@ -5992,7 +5948,7 @@
       <c r="E16" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="F16" s="45"/>
+      <c r="F16" s="35"/>
       <c r="G16" s="8" t="s">
         <v>23</v>
       </c>
@@ -6013,7 +5969,7 @@
       <c r="E17" s="34" t="s">
         <v>24</v>
       </c>
-      <c r="F17" s="45"/>
+      <c r="F17" s="35"/>
       <c r="G17" s="8" t="s">
         <v>25</v>
       </c>
@@ -6032,7 +5988,7 @@
         <v>8</v>
       </c>
       <c r="E18" s="35"/>
-      <c r="F18" s="46" t="s">
+      <c r="F18" s="34" t="s">
         <v>27</v>
       </c>
       <c r="G18" s="8" t="s">
@@ -6055,7 +6011,7 @@
       <c r="E19" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="F19" s="45"/>
+      <c r="F19" s="35"/>
       <c r="G19" s="8" t="s">
         <v>31</v>
       </c>
@@ -6074,7 +6030,7 @@
         <v>8</v>
       </c>
       <c r="E20" s="35"/>
-      <c r="F20" s="46" t="s">
+      <c r="F20" s="34" t="s">
         <v>33</v>
       </c>
       <c r="G20" s="8" t="s">
@@ -6097,7 +6053,7 @@
       <c r="E21" s="34" t="s">
         <v>35</v>
       </c>
-      <c r="F21" s="45"/>
+      <c r="F21" s="35"/>
       <c r="G21" s="8" t="s">
         <v>36</v>
       </c>
@@ -6118,7 +6074,7 @@
       <c r="E22" s="34" t="s">
         <v>37</v>
       </c>
-      <c r="F22" s="45"/>
+      <c r="F22" s="35"/>
       <c r="G22" s="8" t="s">
         <v>38</v>
       </c>
@@ -6139,7 +6095,7 @@
       <c r="E23" s="34" t="s">
         <v>39</v>
       </c>
-      <c r="F23" s="45"/>
+      <c r="F23" s="35"/>
       <c r="G23" s="8" t="s">
         <v>40</v>
       </c>
@@ -6160,7 +6116,7 @@
       <c r="E24" s="34" t="s">
         <v>41</v>
       </c>
-      <c r="F24" s="45"/>
+      <c r="F24" s="35"/>
       <c r="G24" s="8" t="s">
         <v>42</v>
       </c>
@@ -6181,7 +6137,7 @@
       <c r="E25" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="F25" s="45"/>
+      <c r="F25" s="35"/>
       <c r="G25" s="8" t="s">
         <v>46</v>
       </c>
@@ -6202,7 +6158,7 @@
       <c r="E26" s="34" t="s">
         <v>47</v>
       </c>
-      <c r="F26" s="45"/>
+      <c r="F26" s="35"/>
       <c r="G26" s="8" t="s">
         <v>48</v>
       </c>
@@ -6223,7 +6179,7 @@
       <c r="E27" s="34" t="s">
         <v>49</v>
       </c>
-      <c r="F27" s="45"/>
+      <c r="F27" s="35"/>
       <c r="G27" s="8" t="s">
         <v>50</v>
       </c>
@@ -6244,7 +6200,7 @@
       <c r="E28" s="34" t="s">
         <v>51</v>
       </c>
-      <c r="F28" s="45"/>
+      <c r="F28" s="35"/>
       <c r="G28" s="8" t="s">
         <v>52</v>
       </c>
@@ -6265,7 +6221,7 @@
       <c r="E29" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="F29" s="45"/>
+      <c r="F29" s="35"/>
       <c r="G29" s="8" t="s">
         <v>54</v>
       </c>
@@ -6286,7 +6242,7 @@
       <c r="E30" s="34" t="s">
         <v>55</v>
       </c>
-      <c r="F30" s="45"/>
+      <c r="F30" s="35"/>
       <c r="G30" s="8" t="s">
         <v>56</v>
       </c>
@@ -6307,7 +6263,7 @@
       <c r="E31" s="34" t="s">
         <v>57</v>
       </c>
-      <c r="F31" s="45"/>
+      <c r="F31" s="35"/>
       <c r="G31" s="8" t="s">
         <v>58</v>
       </c>
@@ -6328,7 +6284,7 @@
       <c r="E32" s="34" t="s">
         <v>59</v>
       </c>
-      <c r="F32" s="45"/>
+      <c r="F32" s="35"/>
       <c r="G32" s="8" t="s">
         <v>60</v>
       </c>
@@ -6349,7 +6305,7 @@
       <c r="E33" s="34" t="s">
         <v>57</v>
       </c>
-      <c r="F33" s="45"/>
+      <c r="F33" s="35"/>
       <c r="G33" s="8" t="s">
         <v>61</v>
       </c>
@@ -6370,7 +6326,7 @@
       <c r="E34" s="34" t="s">
         <v>59</v>
       </c>
-      <c r="F34" s="45"/>
+      <c r="F34" s="35"/>
       <c r="G34" s="8" t="s">
         <v>62</v>
       </c>
@@ -6391,7 +6347,7 @@
       <c r="E35" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="F35" s="45"/>
+      <c r="F35" s="35"/>
       <c r="G35" s="8" t="s">
         <v>64</v>
       </c>
@@ -6412,7 +6368,7 @@
       <c r="E36" s="34" t="s">
         <v>65</v>
       </c>
-      <c r="F36" s="45"/>
+      <c r="F36" s="35"/>
       <c r="G36" s="8" t="s">
         <v>66</v>
       </c>
@@ -6433,7 +6389,7 @@
       <c r="E37" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="F37" s="45"/>
+      <c r="F37" s="35"/>
       <c r="G37" s="8" t="s">
         <v>67</v>
       </c>
@@ -6454,7 +6410,7 @@
       <c r="E38" s="34" t="s">
         <v>65</v>
       </c>
-      <c r="F38" s="45"/>
+      <c r="F38" s="35"/>
       <c r="G38" s="8" t="s">
         <v>68</v>
       </c>
@@ -6475,7 +6431,7 @@
       <c r="E39" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="F39" s="45"/>
+      <c r="F39" s="35"/>
       <c r="G39" s="8" t="s">
         <v>69</v>
       </c>
@@ -6496,7 +6452,7 @@
       <c r="E40" s="34" t="s">
         <v>65</v>
       </c>
-      <c r="F40" s="45"/>
+      <c r="F40" s="35"/>
       <c r="G40" s="8" t="s">
         <v>70</v>
       </c>
@@ -6517,7 +6473,7 @@
       <c r="E41" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="F41" s="45"/>
+      <c r="F41" s="35"/>
       <c r="G41" s="8" t="s">
         <v>71</v>
       </c>
@@ -6530,7 +6486,7 @@
       </c>
       <c r="D42" s="11"/>
       <c r="E42" s="36"/>
-      <c r="F42" s="47"/>
+      <c r="F42" s="36"/>
       <c r="G42" s="13" t="s">
         <v>73</v>
       </c>
@@ -6547,7 +6503,7 @@
       <c r="E43" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="F43" s="48"/>
+      <c r="F43" s="38"/>
       <c r="G43" s="28" t="s">
         <v>89</v>
       </c>
@@ -6561,8 +6517,8 @@
       <c r="D44" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E44" s="38"/>
-      <c r="F44" s="49"/>
+      <c r="E44" s="39"/>
+      <c r="F44" s="40"/>
       <c r="G44" s="29"/>
     </row>
     <row r="45" spans="1:7">
@@ -6581,7 +6537,7 @@
       <c r="E45" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="F45" s="50"/>
+      <c r="F45" s="41"/>
       <c r="G45" s="8" t="s">
         <v>90</v>
       </c>
@@ -6602,7 +6558,7 @@
       <c r="E46" s="34" t="s">
         <v>65</v>
       </c>
-      <c r="F46" s="50"/>
+      <c r="F46" s="41"/>
       <c r="G46" s="8" t="s">
         <v>91</v>
       </c>
@@ -6620,8 +6576,8 @@
       <c r="D47" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E47" s="39"/>
-      <c r="F47" s="46" t="s">
+      <c r="E47" s="41"/>
+      <c r="F47" s="34" t="s">
         <v>92</v>
       </c>
       <c r="G47" s="8" t="s">
@@ -6641,8 +6597,8 @@
       <c r="D48" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E48" s="39"/>
-      <c r="F48" s="46" t="s">
+      <c r="E48" s="41"/>
+      <c r="F48" s="34" t="s">
         <v>94</v>
       </c>
       <c r="G48" s="8" t="s">
@@ -6665,7 +6621,7 @@
       <c r="E49" s="34" t="s">
         <v>96</v>
       </c>
-      <c r="F49" s="50"/>
+      <c r="F49" s="41"/>
       <c r="G49" s="8" t="s">
         <v>97</v>
       </c>
@@ -6686,7 +6642,7 @@
       <c r="E50" s="34" t="s">
         <v>98</v>
       </c>
-      <c r="F50" s="50"/>
+      <c r="F50" s="41"/>
       <c r="G50" s="8" t="s">
         <v>99</v>
       </c>
@@ -6707,7 +6663,7 @@
       <c r="E51" s="34" t="s">
         <v>100</v>
       </c>
-      <c r="F51" s="50"/>
+      <c r="F51" s="41"/>
       <c r="G51" s="8" t="s">
         <v>101</v>
       </c>
@@ -6728,7 +6684,7 @@
       <c r="E52" s="34" t="s">
         <v>102</v>
       </c>
-      <c r="F52" s="50"/>
+      <c r="F52" s="41"/>
       <c r="G52" s="8" t="s">
         <v>103</v>
       </c>
@@ -6749,7 +6705,7 @@
       <c r="E53" s="34" t="s">
         <v>104</v>
       </c>
-      <c r="F53" s="50"/>
+      <c r="F53" s="41"/>
       <c r="G53" s="8" t="s">
         <v>105</v>
       </c>
@@ -6770,7 +6726,7 @@
       <c r="E54" s="34" t="s">
         <v>106</v>
       </c>
-      <c r="F54" s="50"/>
+      <c r="F54" s="41"/>
       <c r="G54" s="8" t="s">
         <v>107</v>
       </c>
@@ -6788,8 +6744,8 @@
       <c r="D55" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="E55" s="39"/>
-      <c r="F55" s="46" t="s">
+      <c r="E55" s="41"/>
+      <c r="F55" s="34" t="s">
         <v>110</v>
       </c>
       <c r="G55" s="8" t="s">
@@ -6812,7 +6768,7 @@
       <c r="E56" s="34" t="s">
         <v>112</v>
       </c>
-      <c r="F56" s="50"/>
+      <c r="F56" s="41"/>
       <c r="G56" s="8" t="s">
         <v>113</v>
       </c>
@@ -6833,7 +6789,7 @@
       <c r="E57" s="34" t="s">
         <v>114</v>
       </c>
-      <c r="F57" s="50"/>
+      <c r="F57" s="41"/>
       <c r="G57" s="8" t="s">
         <v>115</v>
       </c>
@@ -6854,7 +6810,7 @@
       <c r="E58" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="F58" s="50"/>
+      <c r="F58" s="41"/>
       <c r="G58" s="8" t="s">
         <v>117</v>
       </c>
@@ -6875,7 +6831,7 @@
       <c r="E59" s="34" t="s">
         <v>118</v>
       </c>
-      <c r="F59" s="50"/>
+      <c r="F59" s="41"/>
       <c r="G59" s="8" t="s">
         <v>119</v>
       </c>
@@ -6896,7 +6852,7 @@
       <c r="E60" s="34" t="s">
         <v>120</v>
       </c>
-      <c r="F60" s="50"/>
+      <c r="F60" s="41"/>
       <c r="G60" s="8" t="s">
         <v>121</v>
       </c>
@@ -6917,7 +6873,7 @@
       <c r="E61" s="34" t="s">
         <v>122</v>
       </c>
-      <c r="F61" s="50"/>
+      <c r="F61" s="41"/>
       <c r="G61" s="8" t="s">
         <v>123</v>
       </c>
@@ -6938,7 +6894,7 @@
       <c r="E62" s="34" t="s">
         <v>124</v>
       </c>
-      <c r="F62" s="50"/>
+      <c r="F62" s="41"/>
       <c r="G62" s="8" t="s">
         <v>125</v>
       </c>
@@ -6959,7 +6915,7 @@
       <c r="E63" s="34" t="s">
         <v>126</v>
       </c>
-      <c r="F63" s="50"/>
+      <c r="F63" s="41"/>
       <c r="G63" s="8" t="s">
         <v>127</v>
       </c>
@@ -6980,7 +6936,7 @@
       <c r="E64" s="34" t="s">
         <v>128</v>
       </c>
-      <c r="F64" s="50"/>
+      <c r="F64" s="41"/>
       <c r="G64" s="8" t="s">
         <v>129</v>
       </c>
@@ -7001,7 +6957,7 @@
       <c r="E65" s="34" t="s">
         <v>130</v>
       </c>
-      <c r="F65" s="50"/>
+      <c r="F65" s="41"/>
       <c r="G65" s="8" t="s">
         <v>131</v>
       </c>
@@ -7022,7 +6978,7 @@
       <c r="E66" s="34" t="s">
         <v>132</v>
       </c>
-      <c r="F66" s="50"/>
+      <c r="F66" s="41"/>
       <c r="G66" s="8" t="s">
         <v>133</v>
       </c>
@@ -7043,7 +6999,7 @@
       <c r="E67" s="34" t="s">
         <v>134</v>
       </c>
-      <c r="F67" s="50"/>
+      <c r="F67" s="41"/>
       <c r="G67" s="8" t="s">
         <v>135</v>
       </c>
@@ -7064,7 +7020,7 @@
       <c r="E68" s="34" t="s">
         <v>136</v>
       </c>
-      <c r="F68" s="50"/>
+      <c r="F68" s="41"/>
       <c r="G68" s="8" t="s">
         <v>137</v>
       </c>
@@ -7085,7 +7041,7 @@
       <c r="E69" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="F69" s="50"/>
+      <c r="F69" s="41"/>
       <c r="G69" s="8" t="s">
         <v>138</v>
       </c>
@@ -7106,7 +7062,7 @@
       <c r="E70" s="34" t="s">
         <v>139</v>
       </c>
-      <c r="F70" s="50"/>
+      <c r="F70" s="41"/>
       <c r="G70" s="8" t="s">
         <v>140</v>
       </c>
@@ -7127,7 +7083,7 @@
       <c r="E71" s="34" t="s">
         <v>141</v>
       </c>
-      <c r="F71" s="50"/>
+      <c r="F71" s="41"/>
       <c r="G71" s="8" t="s">
         <v>142</v>
       </c>
@@ -7148,7 +7104,7 @@
       <c r="E72" s="34" t="s">
         <v>143</v>
       </c>
-      <c r="F72" s="50"/>
+      <c r="F72" s="41"/>
       <c r="G72" s="8" t="s">
         <v>144</v>
       </c>
@@ -7169,7 +7125,7 @@
       <c r="E73" s="34" t="s">
         <v>145</v>
       </c>
-      <c r="F73" s="50"/>
+      <c r="F73" s="41"/>
       <c r="G73" s="8" t="s">
         <v>146</v>
       </c>
@@ -7190,7 +7146,7 @@
       <c r="E74" s="34" t="s">
         <v>147</v>
       </c>
-      <c r="F74" s="50"/>
+      <c r="F74" s="41"/>
       <c r="G74" s="8" t="s">
         <v>148</v>
       </c>
@@ -7211,7 +7167,7 @@
       <c r="E75" s="34" t="s">
         <v>150</v>
       </c>
-      <c r="F75" s="50"/>
+      <c r="F75" s="41"/>
       <c r="G75" s="8" t="s">
         <v>151</v>
       </c>
@@ -7229,8 +7185,8 @@
       <c r="D76" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E76" s="39"/>
-      <c r="F76" s="46" t="s">
+      <c r="E76" s="41"/>
+      <c r="F76" s="34" t="s">
         <v>152</v>
       </c>
       <c r="G76" s="8" t="s">
@@ -7253,7 +7209,7 @@
       <c r="E77" s="34" t="s">
         <v>154</v>
       </c>
-      <c r="F77" s="50"/>
+      <c r="F77" s="41"/>
       <c r="G77" s="8" t="s">
         <v>155</v>
       </c>
@@ -7274,7 +7230,7 @@
       <c r="E78" s="34" t="s">
         <v>156</v>
       </c>
-      <c r="F78" s="50"/>
+      <c r="F78" s="41"/>
       <c r="G78" s="8" t="s">
         <v>157</v>
       </c>
@@ -7295,7 +7251,7 @@
       <c r="E79" s="34" t="s">
         <v>158</v>
       </c>
-      <c r="F79" s="50"/>
+      <c r="F79" s="41"/>
       <c r="G79" s="8" t="s">
         <v>159</v>
       </c>
@@ -7316,7 +7272,7 @@
       <c r="E80" s="34" t="s">
         <v>160</v>
       </c>
-      <c r="F80" s="50"/>
+      <c r="F80" s="41"/>
       <c r="G80" s="8" t="s">
         <v>161</v>
       </c>
@@ -7337,7 +7293,7 @@
       <c r="E81" s="34" t="s">
         <v>162</v>
       </c>
-      <c r="F81" s="50"/>
+      <c r="F81" s="41"/>
       <c r="G81" s="8" t="s">
         <v>163</v>
       </c>
@@ -7358,7 +7314,7 @@
       <c r="E82" s="34" t="s">
         <v>164</v>
       </c>
-      <c r="F82" s="50"/>
+      <c r="F82" s="41"/>
       <c r="G82" s="8" t="s">
         <v>165</v>
       </c>
@@ -7379,7 +7335,7 @@
       <c r="E83" s="34" t="s">
         <v>166</v>
       </c>
-      <c r="F83" s="50"/>
+      <c r="F83" s="41"/>
       <c r="G83" s="8" t="s">
         <v>167</v>
       </c>
@@ -7400,7 +7356,7 @@
       <c r="E84" s="34" t="s">
         <v>168</v>
       </c>
-      <c r="F84" s="50"/>
+      <c r="F84" s="41"/>
       <c r="G84" s="8" t="s">
         <v>169</v>
       </c>
@@ -7421,7 +7377,7 @@
       <c r="E85" s="34" t="s">
         <v>170</v>
       </c>
-      <c r="F85" s="50"/>
+      <c r="F85" s="41"/>
       <c r="G85" s="8" t="s">
         <v>171</v>
       </c>
@@ -7433,8 +7389,8 @@
         <v>72</v>
       </c>
       <c r="D86" s="22"/>
-      <c r="E86" s="40"/>
-      <c r="F86" s="51"/>
+      <c r="E86" s="42"/>
+      <c r="F86" s="42"/>
       <c r="G86" s="13" t="s">
         <v>73</v>
       </c>
@@ -7451,7 +7407,7 @@
       <c r="E87" s="37" t="s">
         <v>172</v>
       </c>
-      <c r="F87" s="48"/>
+      <c r="F87" s="38"/>
       <c r="G87" s="28" t="s">
         <v>173</v>
       </c>
@@ -7465,8 +7421,8 @@
       <c r="D88" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E88" s="38"/>
-      <c r="F88" s="49"/>
+      <c r="E88" s="39"/>
+      <c r="F88" s="40"/>
       <c r="G88" s="29"/>
     </row>
     <row r="89" spans="1:7">
@@ -7485,7 +7441,7 @@
       <c r="E89" s="34" t="s">
         <v>174</v>
       </c>
-      <c r="F89" s="50"/>
+      <c r="F89" s="41"/>
       <c r="G89" s="8" t="s">
         <v>175</v>
       </c>
@@ -7506,7 +7462,7 @@
       <c r="E90" s="34" t="s">
         <v>176</v>
       </c>
-      <c r="F90" s="50"/>
+      <c r="F90" s="41"/>
       <c r="G90" s="8" t="s">
         <v>177</v>
       </c>
@@ -7527,7 +7483,7 @@
       <c r="E91" s="34" t="s">
         <v>178</v>
       </c>
-      <c r="F91" s="50"/>
+      <c r="F91" s="41"/>
       <c r="G91" s="8" t="s">
         <v>179</v>
       </c>
@@ -7548,7 +7504,7 @@
       <c r="E92" s="34" t="s">
         <v>180</v>
       </c>
-      <c r="F92" s="50"/>
+      <c r="F92" s="41"/>
       <c r="G92" s="8" t="s">
         <v>181</v>
       </c>
@@ -7569,7 +7525,7 @@
       <c r="E93" s="34" t="s">
         <v>182</v>
       </c>
-      <c r="F93" s="50"/>
+      <c r="F93" s="41"/>
       <c r="G93" s="8" t="s">
         <v>183</v>
       </c>
@@ -7590,7 +7546,7 @@
       <c r="E94" s="34" t="s">
         <v>184</v>
       </c>
-      <c r="F94" s="50"/>
+      <c r="F94" s="41"/>
       <c r="G94" s="8" t="s">
         <v>185</v>
       </c>
@@ -7611,7 +7567,7 @@
       <c r="E95" s="34" t="s">
         <v>186</v>
       </c>
-      <c r="F95" s="50"/>
+      <c r="F95" s="41"/>
       <c r="G95" s="8" t="s">
         <v>187</v>
       </c>
@@ -7632,7 +7588,7 @@
       <c r="E96" s="34" t="s">
         <v>188</v>
       </c>
-      <c r="F96" s="50"/>
+      <c r="F96" s="41"/>
       <c r="G96" s="8" t="s">
         <v>189</v>
       </c>
@@ -7653,7 +7609,7 @@
       <c r="E97" s="34" t="s">
         <v>190</v>
       </c>
-      <c r="F97" s="50"/>
+      <c r="F97" s="41"/>
       <c r="G97" s="8" t="s">
         <v>191</v>
       </c>
@@ -7674,7 +7630,7 @@
       <c r="E98" s="34" t="s">
         <v>192</v>
       </c>
-      <c r="F98" s="50"/>
+      <c r="F98" s="41"/>
       <c r="G98" s="8" t="s">
         <v>193</v>
       </c>
@@ -7695,7 +7651,7 @@
       <c r="E99" s="34" t="s">
         <v>194</v>
       </c>
-      <c r="F99" s="50"/>
+      <c r="F99" s="41"/>
       <c r="G99" s="8" t="s">
         <v>195</v>
       </c>
@@ -7716,7 +7672,7 @@
       <c r="E100" s="34" t="s">
         <v>196</v>
       </c>
-      <c r="F100" s="50"/>
+      <c r="F100" s="41"/>
       <c r="G100" s="8" t="s">
         <v>197</v>
       </c>
@@ -7737,7 +7693,7 @@
       <c r="E101" s="34" t="s">
         <v>198</v>
       </c>
-      <c r="F101" s="50"/>
+      <c r="F101" s="41"/>
       <c r="G101" s="8" t="s">
         <v>199</v>
       </c>
@@ -7758,7 +7714,7 @@
       <c r="E102" s="34" t="s">
         <v>200</v>
       </c>
-      <c r="F102" s="50"/>
+      <c r="F102" s="41"/>
       <c r="G102" s="8" t="s">
         <v>201</v>
       </c>
@@ -7779,7 +7735,7 @@
       <c r="E103" s="34" t="s">
         <v>202</v>
       </c>
-      <c r="F103" s="50"/>
+      <c r="F103" s="41"/>
       <c r="G103" s="8" t="s">
         <v>203</v>
       </c>
@@ -7800,7 +7756,7 @@
       <c r="E104" s="34" t="s">
         <v>204</v>
       </c>
-      <c r="F104" s="50"/>
+      <c r="F104" s="41"/>
       <c r="G104" s="8" t="s">
         <v>205</v>
       </c>
@@ -7821,7 +7777,7 @@
       <c r="E105" s="34" t="s">
         <v>206</v>
       </c>
-      <c r="F105" s="50"/>
+      <c r="F105" s="41"/>
       <c r="G105" s="8" t="s">
         <v>207</v>
       </c>
@@ -7842,7 +7798,7 @@
       <c r="E106" s="34" t="s">
         <v>208</v>
       </c>
-      <c r="F106" s="50"/>
+      <c r="F106" s="41"/>
       <c r="G106" s="8" t="s">
         <v>209</v>
       </c>
@@ -7863,7 +7819,7 @@
       <c r="E107" s="34" t="s">
         <v>210</v>
       </c>
-      <c r="F107" s="50"/>
+      <c r="F107" s="41"/>
       <c r="G107" s="8" t="s">
         <v>211</v>
       </c>
@@ -7884,7 +7840,7 @@
       <c r="E108" s="34" t="s">
         <v>212</v>
       </c>
-      <c r="F108" s="50"/>
+      <c r="F108" s="41"/>
       <c r="G108" s="8" t="s">
         <v>213</v>
       </c>
@@ -7905,7 +7861,7 @@
       <c r="E109" s="34" t="s">
         <v>214</v>
       </c>
-      <c r="F109" s="50"/>
+      <c r="F109" s="41"/>
       <c r="G109" s="8" t="s">
         <v>215</v>
       </c>
@@ -7926,7 +7882,7 @@
       <c r="E110" s="34" t="s">
         <v>216</v>
       </c>
-      <c r="F110" s="50"/>
+      <c r="F110" s="41"/>
       <c r="G110" s="8" t="s">
         <v>217</v>
       </c>
@@ -7947,7 +7903,7 @@
       <c r="E111" s="34" t="s">
         <v>218</v>
       </c>
-      <c r="F111" s="50"/>
+      <c r="F111" s="41"/>
       <c r="G111" s="8" t="s">
         <v>219</v>
       </c>
@@ -7968,7 +7924,7 @@
       <c r="E112" s="34" t="s">
         <v>220</v>
       </c>
-      <c r="F112" s="50"/>
+      <c r="F112" s="41"/>
       <c r="G112" s="8" t="s">
         <v>221</v>
       </c>
@@ -7989,7 +7945,7 @@
       <c r="E113" s="34" t="s">
         <v>222</v>
       </c>
-      <c r="F113" s="50"/>
+      <c r="F113" s="41"/>
       <c r="G113" s="8" t="s">
         <v>223</v>
       </c>
@@ -8010,7 +7966,7 @@
       <c r="E114" s="34" t="s">
         <v>224</v>
       </c>
-      <c r="F114" s="50"/>
+      <c r="F114" s="41"/>
       <c r="G114" s="8" t="s">
         <v>225</v>
       </c>
@@ -8031,7 +7987,7 @@
       <c r="E115" s="34" t="s">
         <v>226</v>
       </c>
-      <c r="F115" s="50"/>
+      <c r="F115" s="41"/>
       <c r="G115" s="8" t="s">
         <v>227</v>
       </c>
@@ -8052,7 +8008,7 @@
       <c r="E116" s="34" t="s">
         <v>228</v>
       </c>
-      <c r="F116" s="50"/>
+      <c r="F116" s="41"/>
       <c r="G116" s="8" t="s">
         <v>229</v>
       </c>
@@ -8073,7 +8029,7 @@
       <c r="E117" s="34" t="s">
         <v>230</v>
       </c>
-      <c r="F117" s="50"/>
+      <c r="F117" s="41"/>
       <c r="G117" s="8" t="s">
         <v>231</v>
       </c>
@@ -8094,7 +8050,7 @@
       <c r="E118" s="34" t="s">
         <v>232</v>
       </c>
-      <c r="F118" s="50"/>
+      <c r="F118" s="41"/>
       <c r="G118" s="8" t="s">
         <v>233</v>
       </c>
@@ -8112,8 +8068,8 @@
       <c r="D119" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E119" s="39"/>
-      <c r="F119" s="52" t="s">
+      <c r="E119" s="41"/>
+      <c r="F119" s="43" t="s">
         <v>234</v>
       </c>
       <c r="G119" s="8" t="s">
@@ -8136,7 +8092,7 @@
       <c r="E120" s="34" t="s">
         <v>236</v>
       </c>
-      <c r="F120" s="50"/>
+      <c r="F120" s="41"/>
       <c r="G120" s="8" t="s">
         <v>237</v>
       </c>
@@ -8157,7 +8113,7 @@
       <c r="E121" s="34" t="s">
         <v>238</v>
       </c>
-      <c r="F121" s="50"/>
+      <c r="F121" s="41"/>
       <c r="G121" s="8" t="s">
         <v>239</v>
       </c>
@@ -8178,7 +8134,7 @@
       <c r="E122" s="34" t="s">
         <v>240</v>
       </c>
-      <c r="F122" s="50"/>
+      <c r="F122" s="41"/>
       <c r="G122" s="8" t="s">
         <v>241</v>
       </c>
@@ -8199,7 +8155,7 @@
       <c r="E123" s="34" t="s">
         <v>242</v>
       </c>
-      <c r="F123" s="50"/>
+      <c r="F123" s="41"/>
       <c r="G123" s="8" t="s">
         <v>243</v>
       </c>
@@ -8220,7 +8176,7 @@
       <c r="E124" s="34" t="s">
         <v>244</v>
       </c>
-      <c r="F124" s="50"/>
+      <c r="F124" s="41"/>
       <c r="G124" s="8" t="s">
         <v>245</v>
       </c>
@@ -8241,7 +8197,7 @@
       <c r="E125" s="34" t="s">
         <v>246</v>
       </c>
-      <c r="F125" s="50"/>
+      <c r="F125" s="41"/>
       <c r="G125" s="8" t="s">
         <v>247</v>
       </c>
@@ -8262,7 +8218,7 @@
       <c r="E126" s="34" t="s">
         <v>248</v>
       </c>
-      <c r="F126" s="50"/>
+      <c r="F126" s="41"/>
       <c r="G126" s="8" t="s">
         <v>249</v>
       </c>
@@ -8283,7 +8239,7 @@
       <c r="E127" s="34" t="s">
         <v>250</v>
       </c>
-      <c r="F127" s="50"/>
+      <c r="F127" s="41"/>
       <c r="G127" s="8" t="s">
         <v>251</v>
       </c>
@@ -8304,7 +8260,7 @@
       <c r="E128" s="34" t="s">
         <v>252</v>
       </c>
-      <c r="F128" s="50"/>
+      <c r="F128" s="41"/>
       <c r="G128" s="8" t="s">
         <v>253</v>
       </c>
@@ -8325,7 +8281,7 @@
       <c r="E129" s="34" t="s">
         <v>254</v>
       </c>
-      <c r="F129" s="50"/>
+      <c r="F129" s="41"/>
       <c r="G129" s="8" t="s">
         <v>255</v>
       </c>
@@ -8337,8 +8293,8 @@
         <v>72</v>
       </c>
       <c r="D130" s="22"/>
-      <c r="E130" s="40"/>
-      <c r="F130" s="51"/>
+      <c r="E130" s="42"/>
+      <c r="F130" s="42"/>
       <c r="G130" s="13" t="s">
         <v>73</v>
       </c>
@@ -8355,7 +8311,7 @@
       <c r="E131" s="37" t="s">
         <v>256</v>
       </c>
-      <c r="F131" s="48"/>
+      <c r="F131" s="38"/>
       <c r="G131" s="28" t="s">
         <v>257</v>
       </c>
@@ -8369,8 +8325,8 @@
       <c r="D132" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E132" s="38"/>
-      <c r="F132" s="49"/>
+      <c r="E132" s="39"/>
+      <c r="F132" s="40"/>
       <c r="G132" s="29"/>
     </row>
     <row r="133" spans="1:7">
@@ -8389,7 +8345,7 @@
       <c r="E133" s="34" t="s">
         <v>258</v>
       </c>
-      <c r="F133" s="49"/>
+      <c r="F133" s="40"/>
       <c r="G133" s="8" t="s">
         <v>259</v>
       </c>
@@ -8410,7 +8366,7 @@
       <c r="E134" s="34" t="s">
         <v>260</v>
       </c>
-      <c r="F134" s="49"/>
+      <c r="F134" s="40"/>
       <c r="G134" s="8" t="s">
         <v>261</v>
       </c>
@@ -8431,7 +8387,7 @@
       <c r="E135" s="34" t="s">
         <v>262</v>
       </c>
-      <c r="F135" s="49"/>
+      <c r="F135" s="40"/>
       <c r="G135" s="8" t="s">
         <v>263</v>
       </c>
@@ -8452,7 +8408,7 @@
       <c r="E136" s="34" t="s">
         <v>264</v>
       </c>
-      <c r="F136" s="49"/>
+      <c r="F136" s="40"/>
       <c r="G136" s="8" t="s">
         <v>265</v>
       </c>
@@ -8473,7 +8429,7 @@
       <c r="E137" s="34" t="s">
         <v>266</v>
       </c>
-      <c r="F137" s="49"/>
+      <c r="F137" s="40"/>
       <c r="G137" s="8" t="s">
         <v>267</v>
       </c>
@@ -8494,7 +8450,7 @@
       <c r="E138" s="34" t="s">
         <v>268</v>
       </c>
-      <c r="F138" s="49"/>
+      <c r="F138" s="40"/>
       <c r="G138" s="8" t="s">
         <v>269</v>
       </c>
@@ -8515,7 +8471,7 @@
       <c r="E139" s="34" t="s">
         <v>270</v>
       </c>
-      <c r="F139" s="49"/>
+      <c r="F139" s="40"/>
       <c r="G139" s="8" t="s">
         <v>271</v>
       </c>
@@ -8536,7 +8492,7 @@
       <c r="E140" s="34" t="s">
         <v>272</v>
       </c>
-      <c r="F140" s="49"/>
+      <c r="F140" s="40"/>
       <c r="G140" s="8" t="s">
         <v>273</v>
       </c>
@@ -8557,7 +8513,7 @@
       <c r="E141" s="34" t="s">
         <v>274</v>
       </c>
-      <c r="F141" s="49"/>
+      <c r="F141" s="40"/>
       <c r="G141" s="8" t="s">
         <v>275</v>
       </c>
@@ -8578,7 +8534,7 @@
       <c r="E142" s="34" t="s">
         <v>276</v>
       </c>
-      <c r="F142" s="49"/>
+      <c r="F142" s="40"/>
       <c r="G142" s="8" t="s">
         <v>277</v>
       </c>
@@ -8599,7 +8555,7 @@
       <c r="E143" s="34" t="s">
         <v>278</v>
       </c>
-      <c r="F143" s="49"/>
+      <c r="F143" s="40"/>
       <c r="G143" s="8" t="s">
         <v>279</v>
       </c>
@@ -8620,7 +8576,7 @@
       <c r="E144" s="34" t="s">
         <v>280</v>
       </c>
-      <c r="F144" s="49"/>
+      <c r="F144" s="40"/>
       <c r="G144" s="8" t="s">
         <v>281</v>
       </c>
@@ -8641,7 +8597,7 @@
       <c r="E145" s="34" t="s">
         <v>282</v>
       </c>
-      <c r="F145" s="49"/>
+      <c r="F145" s="40"/>
       <c r="G145" s="8" t="s">
         <v>283</v>
       </c>
@@ -8662,7 +8618,7 @@
       <c r="E146" s="34" t="s">
         <v>284</v>
       </c>
-      <c r="F146" s="49"/>
+      <c r="F146" s="40"/>
       <c r="G146" s="8" t="s">
         <v>285</v>
       </c>
@@ -8683,7 +8639,7 @@
       <c r="E147" s="34" t="s">
         <v>286</v>
       </c>
-      <c r="F147" s="49"/>
+      <c r="F147" s="40"/>
       <c r="G147" s="8" t="s">
         <v>287</v>
       </c>
@@ -8704,7 +8660,7 @@
       <c r="E148" s="34" t="s">
         <v>288</v>
       </c>
-      <c r="F148" s="49"/>
+      <c r="F148" s="40"/>
       <c r="G148" s="8" t="s">
         <v>289</v>
       </c>
@@ -8725,7 +8681,7 @@
       <c r="E149" s="34" t="s">
         <v>290</v>
       </c>
-      <c r="F149" s="49"/>
+      <c r="F149" s="40"/>
       <c r="G149" s="8" t="s">
         <v>291</v>
       </c>
@@ -8746,7 +8702,7 @@
       <c r="E150" s="34" t="s">
         <v>292</v>
       </c>
-      <c r="F150" s="49"/>
+      <c r="F150" s="40"/>
       <c r="G150" s="8" t="s">
         <v>293</v>
       </c>
@@ -8767,7 +8723,7 @@
       <c r="E151" s="34" t="s">
         <v>294</v>
       </c>
-      <c r="F151" s="49"/>
+      <c r="F151" s="40"/>
       <c r="G151" s="8" t="s">
         <v>295</v>
       </c>
@@ -8788,7 +8744,7 @@
       <c r="E152" s="34" t="s">
         <v>296</v>
       </c>
-      <c r="F152" s="49"/>
+      <c r="F152" s="40"/>
       <c r="G152" s="8" t="s">
         <v>297</v>
       </c>
@@ -8809,7 +8765,7 @@
       <c r="E153" s="34" t="s">
         <v>298</v>
       </c>
-      <c r="F153" s="49"/>
+      <c r="F153" s="40"/>
       <c r="G153" s="8" t="s">
         <v>299</v>
       </c>
@@ -8830,7 +8786,7 @@
       <c r="E154" s="34" t="s">
         <v>300</v>
       </c>
-      <c r="F154" s="49"/>
+      <c r="F154" s="40"/>
       <c r="G154" s="8" t="s">
         <v>301</v>
       </c>
@@ -8851,7 +8807,7 @@
       <c r="E155" s="34" t="s">
         <v>302</v>
       </c>
-      <c r="F155" s="49"/>
+      <c r="F155" s="40"/>
       <c r="G155" s="8" t="s">
         <v>303</v>
       </c>
@@ -8872,7 +8828,7 @@
       <c r="E156" s="34" t="s">
         <v>304</v>
       </c>
-      <c r="F156" s="49"/>
+      <c r="F156" s="40"/>
       <c r="G156" s="8" t="s">
         <v>305</v>
       </c>
@@ -8893,7 +8849,7 @@
       <c r="E157" s="34" t="s">
         <v>306</v>
       </c>
-      <c r="F157" s="49"/>
+      <c r="F157" s="40"/>
       <c r="G157" s="8" t="s">
         <v>307</v>
       </c>
@@ -8914,7 +8870,7 @@
       <c r="E158" s="34" t="s">
         <v>308</v>
       </c>
-      <c r="F158" s="49"/>
+      <c r="F158" s="40"/>
       <c r="G158" s="8" t="s">
         <v>309</v>
       </c>
@@ -8935,7 +8891,7 @@
       <c r="E159" s="34" t="s">
         <v>310</v>
       </c>
-      <c r="F159" s="49"/>
+      <c r="F159" s="40"/>
       <c r="G159" s="8" t="s">
         <v>311</v>
       </c>
@@ -8956,7 +8912,7 @@
       <c r="E160" s="34" t="s">
         <v>312</v>
       </c>
-      <c r="F160" s="49"/>
+      <c r="F160" s="40"/>
       <c r="G160" s="8" t="s">
         <v>313</v>
       </c>
@@ -8977,7 +8933,7 @@
       <c r="E161" s="34" t="s">
         <v>314</v>
       </c>
-      <c r="F161" s="49"/>
+      <c r="F161" s="40"/>
       <c r="G161" s="8" t="s">
         <v>315</v>
       </c>
@@ -8998,7 +8954,7 @@
       <c r="E162" s="34" t="s">
         <v>316</v>
       </c>
-      <c r="F162" s="49"/>
+      <c r="F162" s="40"/>
       <c r="G162" s="8" t="s">
         <v>317</v>
       </c>
@@ -9019,7 +8975,7 @@
       <c r="E163" s="34" t="s">
         <v>318</v>
       </c>
-      <c r="F163" s="49"/>
+      <c r="F163" s="40"/>
       <c r="G163" s="8" t="s">
         <v>319</v>
       </c>
@@ -9040,7 +8996,7 @@
       <c r="E164" s="34" t="s">
         <v>320</v>
       </c>
-      <c r="F164" s="49"/>
+      <c r="F164" s="40"/>
       <c r="G164" s="8" t="s">
         <v>321</v>
       </c>
@@ -9061,7 +9017,7 @@
       <c r="E165" s="34" t="s">
         <v>322</v>
       </c>
-      <c r="F165" s="49"/>
+      <c r="F165" s="40"/>
       <c r="G165" s="8" t="s">
         <v>323</v>
       </c>
@@ -9082,7 +9038,7 @@
       <c r="E166" s="34" t="s">
         <v>324</v>
       </c>
-      <c r="F166" s="49"/>
+      <c r="F166" s="40"/>
       <c r="G166" s="8" t="s">
         <v>325</v>
       </c>
@@ -9103,7 +9059,7 @@
       <c r="E167" s="34" t="s">
         <v>326</v>
       </c>
-      <c r="F167" s="49"/>
+      <c r="F167" s="40"/>
       <c r="G167" s="8" t="s">
         <v>327</v>
       </c>
@@ -9124,7 +9080,7 @@
       <c r="E168" s="34" t="s">
         <v>328</v>
       </c>
-      <c r="F168" s="49"/>
+      <c r="F168" s="40"/>
       <c r="G168" s="8" t="s">
         <v>329</v>
       </c>
@@ -9145,7 +9101,7 @@
       <c r="E169" s="34" t="s">
         <v>330</v>
       </c>
-      <c r="F169" s="49"/>
+      <c r="F169" s="40"/>
       <c r="G169" s="8" t="s">
         <v>331</v>
       </c>
@@ -9166,7 +9122,7 @@
       <c r="E170" s="34" t="s">
         <v>332</v>
       </c>
-      <c r="F170" s="49"/>
+      <c r="F170" s="40"/>
       <c r="G170" s="8" t="s">
         <v>333</v>
       </c>
@@ -9187,7 +9143,7 @@
       <c r="E171" s="34" t="s">
         <v>334</v>
       </c>
-      <c r="F171" s="49"/>
+      <c r="F171" s="40"/>
       <c r="G171" s="8" t="s">
         <v>335</v>
       </c>
@@ -9208,7 +9164,7 @@
       <c r="E172" s="34" t="s">
         <v>336</v>
       </c>
-      <c r="F172" s="49"/>
+      <c r="F172" s="40"/>
       <c r="G172" s="8" t="s">
         <v>337</v>
       </c>
@@ -9229,7 +9185,7 @@
       <c r="E173" s="34" t="s">
         <v>338</v>
       </c>
-      <c r="F173" s="49"/>
+      <c r="F173" s="40"/>
       <c r="G173" s="8" t="s">
         <v>339</v>
       </c>
@@ -9241,8 +9197,8 @@
         <v>72</v>
       </c>
       <c r="D174" s="22"/>
-      <c r="E174" s="40"/>
-      <c r="F174" s="53"/>
+      <c r="E174" s="42"/>
+      <c r="F174" s="44"/>
       <c r="G174" s="13" t="s">
         <v>73</v>
       </c>
@@ -9259,7 +9215,7 @@
       <c r="E175" s="37" t="s">
         <v>340</v>
       </c>
-      <c r="F175" s="48"/>
+      <c r="F175" s="38"/>
       <c r="G175" s="28" t="s">
         <v>341</v>
       </c>
@@ -9273,8 +9229,8 @@
       <c r="D176" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E176" s="38"/>
-      <c r="F176" s="49"/>
+      <c r="E176" s="39"/>
+      <c r="F176" s="40"/>
       <c r="G176" s="29"/>
     </row>
     <row r="177" spans="1:7">
@@ -9293,7 +9249,7 @@
       <c r="E177" s="34" t="s">
         <v>342</v>
       </c>
-      <c r="F177" s="50"/>
+      <c r="F177" s="41"/>
       <c r="G177" s="8" t="s">
         <v>343</v>
       </c>
@@ -9311,8 +9267,8 @@
       <c r="D178" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E178" s="39"/>
-      <c r="F178" s="46" t="s">
+      <c r="E178" s="41"/>
+      <c r="F178" s="34" t="s">
         <v>344</v>
       </c>
       <c r="G178" s="8" t="s">
@@ -9335,7 +9291,7 @@
       <c r="E179" s="34" t="s">
         <v>346</v>
       </c>
-      <c r="F179" s="50"/>
+      <c r="F179" s="41"/>
       <c r="G179" s="8" t="s">
         <v>347</v>
       </c>
@@ -9356,7 +9312,7 @@
       <c r="E180" s="34" t="s">
         <v>348</v>
       </c>
-      <c r="F180" s="50"/>
+      <c r="F180" s="41"/>
       <c r="G180" s="8" t="s">
         <v>349</v>
       </c>
@@ -9377,7 +9333,7 @@
       <c r="E181" s="34" t="s">
         <v>350</v>
       </c>
-      <c r="F181" s="50"/>
+      <c r="F181" s="41"/>
       <c r="G181" s="8" t="s">
         <v>351</v>
       </c>
@@ -9398,7 +9354,7 @@
       <c r="E182" s="34" t="s">
         <v>352</v>
       </c>
-      <c r="F182" s="50"/>
+      <c r="F182" s="41"/>
       <c r="G182" s="8" t="s">
         <v>353</v>
       </c>
@@ -9419,7 +9375,7 @@
       <c r="E183" s="34" t="s">
         <v>354</v>
       </c>
-      <c r="F183" s="50"/>
+      <c r="F183" s="41"/>
       <c r="G183" s="8" t="s">
         <v>355</v>
       </c>
@@ -9440,7 +9396,7 @@
       <c r="E184" s="34" t="s">
         <v>356</v>
       </c>
-      <c r="F184" s="50"/>
+      <c r="F184" s="41"/>
       <c r="G184" s="8" t="s">
         <v>357</v>
       </c>
@@ -9461,7 +9417,7 @@
       <c r="E185" s="34" t="s">
         <v>358</v>
       </c>
-      <c r="F185" s="50"/>
+      <c r="F185" s="41"/>
       <c r="G185" s="8" t="s">
         <v>359</v>
       </c>
@@ -9482,7 +9438,7 @@
       <c r="E186" s="34" t="s">
         <v>360</v>
       </c>
-      <c r="F186" s="50"/>
+      <c r="F186" s="41"/>
       <c r="G186" s="8" t="s">
         <v>361</v>
       </c>
@@ -9503,7 +9459,7 @@
       <c r="E187" s="34" t="s">
         <v>362</v>
       </c>
-      <c r="F187" s="50"/>
+      <c r="F187" s="41"/>
       <c r="G187" s="8" t="s">
         <v>363</v>
       </c>
@@ -9524,7 +9480,7 @@
       <c r="E188" s="34" t="s">
         <v>364</v>
       </c>
-      <c r="F188" s="50"/>
+      <c r="F188" s="41"/>
       <c r="G188" s="8" t="s">
         <v>365</v>
       </c>
@@ -9545,7 +9501,7 @@
       <c r="E189" s="34" t="s">
         <v>367</v>
       </c>
-      <c r="F189" s="50"/>
+      <c r="F189" s="41"/>
       <c r="G189" s="8" t="s">
         <v>368</v>
       </c>
@@ -9566,7 +9522,7 @@
       <c r="E190" s="34" t="s">
         <v>369</v>
       </c>
-      <c r="F190" s="50"/>
+      <c r="F190" s="41"/>
       <c r="G190" s="8" t="s">
         <v>370</v>
       </c>
@@ -9587,7 +9543,7 @@
       <c r="E191" s="34" t="s">
         <v>371</v>
       </c>
-      <c r="F191" s="50"/>
+      <c r="F191" s="41"/>
       <c r="G191" s="8" t="s">
         <v>372</v>
       </c>
@@ -9608,7 +9564,7 @@
       <c r="E192" s="34" t="s">
         <v>373</v>
       </c>
-      <c r="F192" s="50"/>
+      <c r="F192" s="41"/>
       <c r="G192" s="8" t="s">
         <v>374</v>
       </c>
@@ -9629,7 +9585,7 @@
       <c r="E193" s="34" t="s">
         <v>375</v>
       </c>
-      <c r="F193" s="50"/>
+      <c r="F193" s="41"/>
       <c r="G193" s="8" t="s">
         <v>376</v>
       </c>
@@ -9650,7 +9606,7 @@
       <c r="E194" s="34" t="s">
         <v>377</v>
       </c>
-      <c r="F194" s="50"/>
+      <c r="F194" s="41"/>
       <c r="G194" s="8" t="s">
         <v>378</v>
       </c>
@@ -9671,7 +9627,7 @@
       <c r="E195" s="34" t="s">
         <v>379</v>
       </c>
-      <c r="F195" s="50"/>
+      <c r="F195" s="41"/>
       <c r="G195" s="8" t="s">
         <v>380</v>
       </c>
@@ -9692,7 +9648,7 @@
       <c r="E196" s="34" t="s">
         <v>381</v>
       </c>
-      <c r="F196" s="50"/>
+      <c r="F196" s="41"/>
       <c r="G196" s="8" t="s">
         <v>382</v>
       </c>
@@ -9710,8 +9666,8 @@
       <c r="D197" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E197" s="39"/>
-      <c r="F197" s="46" t="s">
+      <c r="E197" s="41"/>
+      <c r="F197" s="34" t="s">
         <v>383</v>
       </c>
       <c r="G197" s="8" t="s">
@@ -9734,7 +9690,7 @@
       <c r="E198" s="34" t="s">
         <v>385</v>
       </c>
-      <c r="F198" s="50"/>
+      <c r="F198" s="41"/>
       <c r="G198" s="8" t="s">
         <v>386</v>
       </c>
@@ -9755,7 +9711,7 @@
       <c r="E199" s="34" t="s">
         <v>387</v>
       </c>
-      <c r="F199" s="50"/>
+      <c r="F199" s="41"/>
       <c r="G199" s="8" t="s">
         <v>388</v>
       </c>
@@ -9776,7 +9732,7 @@
       <c r="E200" s="34" t="s">
         <v>389</v>
       </c>
-      <c r="F200" s="50"/>
+      <c r="F200" s="41"/>
       <c r="G200" s="8" t="s">
         <v>390</v>
       </c>
@@ -9797,7 +9753,7 @@
       <c r="E201" s="34" t="s">
         <v>391</v>
       </c>
-      <c r="F201" s="50"/>
+      <c r="F201" s="41"/>
       <c r="G201" s="8" t="s">
         <v>392</v>
       </c>
@@ -9818,7 +9774,7 @@
       <c r="E202" s="34" t="s">
         <v>393</v>
       </c>
-      <c r="F202" s="50"/>
+      <c r="F202" s="41"/>
       <c r="G202" s="8" t="s">
         <v>394</v>
       </c>
@@ -9839,7 +9795,7 @@
       <c r="E203" s="34" t="s">
         <v>395</v>
       </c>
-      <c r="F203" s="50"/>
+      <c r="F203" s="41"/>
       <c r="G203" s="8" t="s">
         <v>396</v>
       </c>
@@ -9860,7 +9816,7 @@
       <c r="E204" s="34" t="s">
         <v>397</v>
       </c>
-      <c r="F204" s="50"/>
+      <c r="F204" s="41"/>
       <c r="G204" s="8" t="s">
         <v>398</v>
       </c>
@@ -9881,7 +9837,7 @@
       <c r="E205" s="34" t="s">
         <v>172</v>
       </c>
-      <c r="F205" s="50"/>
+      <c r="F205" s="41"/>
       <c r="G205" s="8" t="s">
         <v>399</v>
       </c>
@@ -9902,7 +9858,7 @@
       <c r="E206" s="34" t="s">
         <v>356</v>
       </c>
-      <c r="F206" s="50"/>
+      <c r="F206" s="41"/>
       <c r="G206" s="8" t="s">
         <v>400</v>
       </c>
@@ -9923,7 +9879,7 @@
       <c r="E207" s="34" t="s">
         <v>401</v>
       </c>
-      <c r="F207" s="50"/>
+      <c r="F207" s="41"/>
       <c r="G207" s="8" t="s">
         <v>402</v>
       </c>
@@ -9944,7 +9900,7 @@
       <c r="E208" s="34" t="s">
         <v>403</v>
       </c>
-      <c r="F208" s="50"/>
+      <c r="F208" s="41"/>
       <c r="G208" s="8" t="s">
         <v>404</v>
       </c>
@@ -9965,7 +9921,7 @@
       <c r="E209" s="34" t="s">
         <v>405</v>
       </c>
-      <c r="F209" s="50"/>
+      <c r="F209" s="41"/>
       <c r="G209" s="8" t="s">
         <v>406</v>
       </c>
@@ -9986,7 +9942,7 @@
       <c r="E210" s="34" t="s">
         <v>407</v>
       </c>
-      <c r="F210" s="50"/>
+      <c r="F210" s="41"/>
       <c r="G210" s="8" t="s">
         <v>408</v>
       </c>
@@ -10007,7 +9963,7 @@
       <c r="E211" s="34" t="s">
         <v>409</v>
       </c>
-      <c r="F211" s="50"/>
+      <c r="F211" s="41"/>
       <c r="G211" s="8" t="s">
         <v>410</v>
       </c>
@@ -10028,7 +9984,7 @@
       <c r="E212" s="34" t="s">
         <v>411</v>
       </c>
-      <c r="F212" s="50"/>
+      <c r="F212" s="41"/>
       <c r="G212" s="8" t="s">
         <v>412</v>
       </c>
@@ -10049,7 +10005,7 @@
       <c r="E213" s="34" t="s">
         <v>413</v>
       </c>
-      <c r="F213" s="50"/>
+      <c r="F213" s="41"/>
       <c r="G213" s="8" t="s">
         <v>414</v>
       </c>
@@ -10070,7 +10026,7 @@
       <c r="E214" s="34" t="s">
         <v>415</v>
       </c>
-      <c r="F214" s="50"/>
+      <c r="F214" s="41"/>
       <c r="G214" s="8" t="s">
         <v>416</v>
       </c>
@@ -10091,7 +10047,7 @@
       <c r="E215" s="34" t="s">
         <v>417</v>
       </c>
-      <c r="F215" s="50"/>
+      <c r="F215" s="41"/>
       <c r="G215" s="8" t="s">
         <v>418</v>
       </c>
@@ -10112,7 +10068,7 @@
       <c r="E216" s="34" t="s">
         <v>419</v>
       </c>
-      <c r="F216" s="50"/>
+      <c r="F216" s="41"/>
       <c r="G216" s="8" t="s">
         <v>420</v>
       </c>
@@ -10133,7 +10089,7 @@
       <c r="E217" s="34" t="s">
         <v>421</v>
       </c>
-      <c r="F217" s="50"/>
+      <c r="F217" s="41"/>
       <c r="G217" s="8" t="s">
         <v>422</v>
       </c>
@@ -10145,8 +10101,8 @@
         <v>72</v>
       </c>
       <c r="D218" s="22"/>
-      <c r="E218" s="40"/>
-      <c r="F218" s="51"/>
+      <c r="E218" s="42"/>
+      <c r="F218" s="42"/>
       <c r="G218" s="13" t="s">
         <v>73</v>
       </c>
@@ -10163,7 +10119,7 @@
       <c r="E219" s="37" t="s">
         <v>423</v>
       </c>
-      <c r="F219" s="48"/>
+      <c r="F219" s="38"/>
       <c r="G219" s="28" t="s">
         <v>424</v>
       </c>
@@ -10177,8 +10133,8 @@
       <c r="D220" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E220" s="38"/>
-      <c r="F220" s="49"/>
+      <c r="E220" s="39"/>
+      <c r="F220" s="40"/>
       <c r="G220" s="29"/>
     </row>
     <row r="221" spans="1:7">
@@ -10197,7 +10153,7 @@
       <c r="E221" s="34" t="s">
         <v>425</v>
       </c>
-      <c r="F221" s="50"/>
+      <c r="F221" s="41"/>
       <c r="G221" s="8" t="s">
         <v>426</v>
       </c>
@@ -10218,7 +10174,7 @@
       <c r="E222" s="34" t="s">
         <v>427</v>
       </c>
-      <c r="F222" s="50"/>
+      <c r="F222" s="41"/>
       <c r="G222" s="8" t="s">
         <v>428</v>
       </c>
@@ -10239,7 +10195,7 @@
       <c r="E223" s="34" t="s">
         <v>429</v>
       </c>
-      <c r="F223" s="50"/>
+      <c r="F223" s="41"/>
       <c r="G223" s="8" t="s">
         <v>430</v>
       </c>
@@ -10260,7 +10216,7 @@
       <c r="E224" s="34" t="s">
         <v>431</v>
       </c>
-      <c r="F224" s="50"/>
+      <c r="F224" s="41"/>
       <c r="G224" s="8" t="s">
         <v>432</v>
       </c>
@@ -10281,7 +10237,7 @@
       <c r="E225" s="34" t="s">
         <v>433</v>
       </c>
-      <c r="F225" s="50"/>
+      <c r="F225" s="41"/>
       <c r="G225" s="8" t="s">
         <v>434</v>
       </c>
@@ -10302,7 +10258,7 @@
       <c r="E226" s="34" t="s">
         <v>435</v>
       </c>
-      <c r="F226" s="50"/>
+      <c r="F226" s="41"/>
       <c r="G226" s="8" t="s">
         <v>436</v>
       </c>
@@ -10323,7 +10279,7 @@
       <c r="E227" s="34" t="s">
         <v>437</v>
       </c>
-      <c r="F227" s="50"/>
+      <c r="F227" s="41"/>
       <c r="G227" s="8" t="s">
         <v>438</v>
       </c>
@@ -10344,7 +10300,7 @@
       <c r="E228" s="34" t="s">
         <v>439</v>
       </c>
-      <c r="F228" s="50"/>
+      <c r="F228" s="41"/>
       <c r="G228" s="8" t="s">
         <v>440</v>
       </c>
@@ -10365,7 +10321,7 @@
       <c r="E229" s="34" t="s">
         <v>441</v>
       </c>
-      <c r="F229" s="50"/>
+      <c r="F229" s="41"/>
       <c r="G229" s="8" t="s">
         <v>442</v>
       </c>
@@ -10386,7 +10342,7 @@
       <c r="E230" s="34" t="s">
         <v>443</v>
       </c>
-      <c r="F230" s="50"/>
+      <c r="F230" s="41"/>
       <c r="G230" s="8" t="s">
         <v>444</v>
       </c>
@@ -10407,7 +10363,7 @@
       <c r="E231" s="34" t="s">
         <v>445</v>
       </c>
-      <c r="F231" s="50"/>
+      <c r="F231" s="41"/>
       <c r="G231" s="8" t="s">
         <v>446</v>
       </c>
@@ -10428,7 +10384,7 @@
       <c r="E232" s="34" t="s">
         <v>447</v>
       </c>
-      <c r="F232" s="50"/>
+      <c r="F232" s="41"/>
       <c r="G232" s="8" t="s">
         <v>448</v>
       </c>
@@ -10449,7 +10405,7 @@
       <c r="E233" s="34" t="s">
         <v>449</v>
       </c>
-      <c r="F233" s="50"/>
+      <c r="F233" s="41"/>
       <c r="G233" s="8" t="s">
         <v>450</v>
       </c>
@@ -10470,7 +10426,7 @@
       <c r="E234" s="34" t="s">
         <v>451</v>
       </c>
-      <c r="F234" s="50"/>
+      <c r="F234" s="41"/>
       <c r="G234" s="8" t="s">
         <v>452</v>
       </c>
@@ -10491,7 +10447,7 @@
       <c r="E235" s="34" t="s">
         <v>453</v>
       </c>
-      <c r="F235" s="50"/>
+      <c r="F235" s="41"/>
       <c r="G235" s="8" t="s">
         <v>454</v>
       </c>
@@ -10512,7 +10468,7 @@
       <c r="E236" s="34" t="s">
         <v>435</v>
       </c>
-      <c r="F236" s="50"/>
+      <c r="F236" s="41"/>
       <c r="G236" s="8" t="s">
         <v>455</v>
       </c>
@@ -10533,7 +10489,7 @@
       <c r="E237" s="34" t="s">
         <v>437</v>
       </c>
-      <c r="F237" s="50"/>
+      <c r="F237" s="41"/>
       <c r="G237" s="8" t="s">
         <v>456</v>
       </c>
@@ -10554,7 +10510,7 @@
       <c r="E238" s="34" t="s">
         <v>457</v>
       </c>
-      <c r="F238" s="50"/>
+      <c r="F238" s="41"/>
       <c r="G238" s="8" t="s">
         <v>458</v>
       </c>
@@ -10575,7 +10531,7 @@
       <c r="E239" s="34" t="s">
         <v>459</v>
       </c>
-      <c r="F239" s="50"/>
+      <c r="F239" s="41"/>
       <c r="G239" s="8" t="s">
         <v>460</v>
       </c>
@@ -10596,7 +10552,7 @@
       <c r="E240" s="34" t="s">
         <v>461</v>
       </c>
-      <c r="F240" s="50"/>
+      <c r="F240" s="41"/>
       <c r="G240" s="8" t="s">
         <v>462</v>
       </c>
@@ -10617,7 +10573,7 @@
       <c r="E241" s="34" t="s">
         <v>463</v>
       </c>
-      <c r="F241" s="50"/>
+      <c r="F241" s="41"/>
       <c r="G241" s="8" t="s">
         <v>464</v>
       </c>
@@ -10638,7 +10594,7 @@
       <c r="E242" s="34" t="s">
         <v>407</v>
       </c>
-      <c r="F242" s="50"/>
+      <c r="F242" s="41"/>
       <c r="G242" s="8" t="s">
         <v>465</v>
       </c>
@@ -10659,7 +10615,7 @@
       <c r="E243" s="34" t="s">
         <v>409</v>
       </c>
-      <c r="F243" s="50"/>
+      <c r="F243" s="41"/>
       <c r="G243" s="8" t="s">
         <v>466</v>
       </c>
@@ -10680,7 +10636,7 @@
       <c r="E244" s="34" t="s">
         <v>467</v>
       </c>
-      <c r="F244" s="50"/>
+      <c r="F244" s="41"/>
       <c r="G244" s="8" t="s">
         <v>468</v>
       </c>
@@ -10701,7 +10657,7 @@
       <c r="E245" s="34" t="s">
         <v>469</v>
       </c>
-      <c r="F245" s="50"/>
+      <c r="F245" s="41"/>
       <c r="G245" s="8" t="s">
         <v>470</v>
       </c>
@@ -10722,7 +10678,7 @@
       <c r="E246" s="34" t="s">
         <v>467</v>
       </c>
-      <c r="F246" s="50"/>
+      <c r="F246" s="41"/>
       <c r="G246" s="8" t="s">
         <v>471</v>
       </c>
@@ -10743,7 +10699,7 @@
       <c r="E247" s="34" t="s">
         <v>469</v>
       </c>
-      <c r="F247" s="50"/>
+      <c r="F247" s="41"/>
       <c r="G247" s="8" t="s">
         <v>472</v>
       </c>
@@ -10764,7 +10720,7 @@
       <c r="E248" s="34" t="s">
         <v>467</v>
       </c>
-      <c r="F248" s="50"/>
+      <c r="F248" s="41"/>
       <c r="G248" s="8" t="s">
         <v>473</v>
       </c>
@@ -10785,7 +10741,7 @@
       <c r="E249" s="34" t="s">
         <v>469</v>
       </c>
-      <c r="F249" s="50"/>
+      <c r="F249" s="41"/>
       <c r="G249" s="8" t="s">
         <v>474</v>
       </c>
@@ -10806,7 +10762,7 @@
       <c r="E250" s="34" t="s">
         <v>475</v>
       </c>
-      <c r="F250" s="50"/>
+      <c r="F250" s="41"/>
       <c r="G250" s="8" t="s">
         <v>476</v>
       </c>
@@ -10827,7 +10783,7 @@
       <c r="E251" s="34" t="s">
         <v>477</v>
       </c>
-      <c r="F251" s="50"/>
+      <c r="F251" s="41"/>
       <c r="G251" s="8" t="s">
         <v>478</v>
       </c>
@@ -10848,7 +10804,7 @@
       <c r="E252" s="34" t="s">
         <v>480</v>
       </c>
-      <c r="F252" s="50"/>
+      <c r="F252" s="41"/>
       <c r="G252" s="8" t="s">
         <v>481</v>
       </c>
@@ -10869,7 +10825,7 @@
       <c r="E253" s="34" t="s">
         <v>482</v>
       </c>
-      <c r="F253" s="50"/>
+      <c r="F253" s="41"/>
       <c r="G253" s="8" t="s">
         <v>483</v>
       </c>
@@ -10887,8 +10843,8 @@
       <c r="D254" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E254" s="39"/>
-      <c r="F254" s="46" t="s">
+      <c r="E254" s="41"/>
+      <c r="F254" s="34" t="s">
         <v>485</v>
       </c>
       <c r="G254" s="8" t="s">
@@ -10908,8 +10864,8 @@
       <c r="D255" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E255" s="39"/>
-      <c r="F255" s="46" t="s">
+      <c r="E255" s="41"/>
+      <c r="F255" s="34" t="s">
         <v>487</v>
       </c>
       <c r="G255" s="8" t="s">
@@ -10932,7 +10888,7 @@
       <c r="E256" s="34" t="s">
         <v>489</v>
       </c>
-      <c r="F256" s="50"/>
+      <c r="F256" s="41"/>
       <c r="G256" s="8" t="s">
         <v>490</v>
       </c>
@@ -10953,7 +10909,7 @@
       <c r="E257" s="34" t="s">
         <v>491</v>
       </c>
-      <c r="F257" s="50"/>
+      <c r="F257" s="41"/>
       <c r="G257" s="8" t="s">
         <v>492</v>
       </c>
@@ -10974,7 +10930,7 @@
       <c r="E258" s="34" t="s">
         <v>467</v>
       </c>
-      <c r="F258" s="50"/>
+      <c r="F258" s="41"/>
       <c r="G258" s="8" t="s">
         <v>493</v>
       </c>
@@ -10995,7 +10951,7 @@
       <c r="E259" s="34" t="s">
         <v>469</v>
       </c>
-      <c r="F259" s="50"/>
+      <c r="F259" s="41"/>
       <c r="G259" s="8" t="s">
         <v>494</v>
       </c>
@@ -11016,7 +10972,7 @@
       <c r="E260" s="34" t="s">
         <v>112</v>
       </c>
-      <c r="F260" s="50"/>
+      <c r="F260" s="41"/>
       <c r="G260" s="8" t="s">
         <v>495</v>
       </c>
@@ -11037,7 +10993,7 @@
       <c r="E261" s="34" t="s">
         <v>114</v>
       </c>
-      <c r="F261" s="50"/>
+      <c r="F261" s="41"/>
       <c r="G261" s="8" t="s">
         <v>496</v>
       </c>
@@ -11049,8 +11005,8 @@
         <v>72</v>
       </c>
       <c r="D262" s="22"/>
-      <c r="E262" s="40"/>
-      <c r="F262" s="51"/>
+      <c r="E262" s="42"/>
+      <c r="F262" s="42"/>
       <c r="G262" s="13" t="s">
         <v>73</v>
       </c>
@@ -11067,7 +11023,7 @@
       <c r="E263" s="37" t="s">
         <v>497</v>
       </c>
-      <c r="F263" s="48"/>
+      <c r="F263" s="38"/>
       <c r="G263" s="28" t="s">
         <v>498</v>
       </c>
@@ -11081,8 +11037,8 @@
       <c r="D264" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E264" s="38"/>
-      <c r="F264" s="49"/>
+      <c r="E264" s="39"/>
+      <c r="F264" s="40"/>
       <c r="G264" s="29"/>
     </row>
     <row r="265" spans="1:7">
@@ -11101,7 +11057,7 @@
       <c r="E265" s="34" t="s">
         <v>499</v>
       </c>
-      <c r="F265" s="49"/>
+      <c r="F265" s="40"/>
       <c r="G265" s="8" t="s">
         <v>500</v>
       </c>
@@ -11122,7 +11078,7 @@
       <c r="E266" s="34" t="s">
         <v>501</v>
       </c>
-      <c r="F266" s="49"/>
+      <c r="F266" s="40"/>
       <c r="G266" s="8" t="s">
         <v>502</v>
       </c>
@@ -11143,7 +11099,7 @@
       <c r="E267" s="34" t="s">
         <v>503</v>
       </c>
-      <c r="F267" s="49"/>
+      <c r="F267" s="40"/>
       <c r="G267" s="8" t="s">
         <v>504</v>
       </c>
@@ -11164,7 +11120,7 @@
       <c r="E268" s="34" t="s">
         <v>505</v>
       </c>
-      <c r="F268" s="49"/>
+      <c r="F268" s="40"/>
       <c r="G268" s="8" t="s">
         <v>506</v>
       </c>
@@ -11185,7 +11141,7 @@
       <c r="E269" s="34" t="s">
         <v>507</v>
       </c>
-      <c r="F269" s="49"/>
+      <c r="F269" s="40"/>
       <c r="G269" s="8" t="s">
         <v>508</v>
       </c>
@@ -11206,7 +11162,7 @@
       <c r="E270" s="34" t="s">
         <v>509</v>
       </c>
-      <c r="F270" s="49"/>
+      <c r="F270" s="40"/>
       <c r="G270" s="8" t="s">
         <v>510</v>
       </c>
@@ -11227,7 +11183,7 @@
       <c r="E271" s="34" t="s">
         <v>511</v>
       </c>
-      <c r="F271" s="49"/>
+      <c r="F271" s="40"/>
       <c r="G271" s="8" t="s">
         <v>512</v>
       </c>
@@ -11248,7 +11204,7 @@
       <c r="E272" s="34" t="s">
         <v>513</v>
       </c>
-      <c r="F272" s="49"/>
+      <c r="F272" s="40"/>
       <c r="G272" s="8" t="s">
         <v>514</v>
       </c>
@@ -11269,7 +11225,7 @@
       <c r="E273" s="34" t="s">
         <v>515</v>
       </c>
-      <c r="F273" s="49"/>
+      <c r="F273" s="40"/>
       <c r="G273" s="8" t="s">
         <v>516</v>
       </c>
@@ -11290,7 +11246,7 @@
       <c r="E274" s="34" t="s">
         <v>517</v>
       </c>
-      <c r="F274" s="49"/>
+      <c r="F274" s="40"/>
       <c r="G274" s="8" t="s">
         <v>518</v>
       </c>
@@ -11311,7 +11267,7 @@
       <c r="E275" s="34" t="s">
         <v>519</v>
       </c>
-      <c r="F275" s="49"/>
+      <c r="F275" s="40"/>
       <c r="G275" s="8" t="s">
         <v>520</v>
       </c>
@@ -11332,7 +11288,7 @@
       <c r="E276" s="34" t="s">
         <v>521</v>
       </c>
-      <c r="F276" s="49"/>
+      <c r="F276" s="40"/>
       <c r="G276" s="8" t="s">
         <v>522</v>
       </c>
@@ -11353,7 +11309,7 @@
       <c r="E277" s="34" t="s">
         <v>523</v>
       </c>
-      <c r="F277" s="49"/>
+      <c r="F277" s="40"/>
       <c r="G277" s="8" t="s">
         <v>524</v>
       </c>
@@ -11374,7 +11330,7 @@
       <c r="E278" s="34" t="s">
         <v>525</v>
       </c>
-      <c r="F278" s="49"/>
+      <c r="F278" s="40"/>
       <c r="G278" s="8" t="s">
         <v>526</v>
       </c>
@@ -11395,7 +11351,7 @@
       <c r="E279" s="34" t="s">
         <v>527</v>
       </c>
-      <c r="F279" s="49"/>
+      <c r="F279" s="40"/>
       <c r="G279" s="8" t="s">
         <v>528</v>
       </c>
@@ -11416,7 +11372,7 @@
       <c r="E280" s="34" t="s">
         <v>529</v>
       </c>
-      <c r="F280" s="49"/>
+      <c r="F280" s="40"/>
       <c r="G280" s="8" t="s">
         <v>530</v>
       </c>
@@ -11437,7 +11393,7 @@
       <c r="E281" s="34" t="s">
         <v>531</v>
       </c>
-      <c r="F281" s="49"/>
+      <c r="F281" s="40"/>
       <c r="G281" s="8" t="s">
         <v>532</v>
       </c>
@@ -11458,7 +11414,7 @@
       <c r="E282" s="34" t="s">
         <v>533</v>
       </c>
-      <c r="F282" s="49"/>
+      <c r="F282" s="40"/>
       <c r="G282" s="8" t="s">
         <v>534</v>
       </c>
@@ -11479,7 +11435,7 @@
       <c r="E283" s="34" t="s">
         <v>535</v>
       </c>
-      <c r="F283" s="49"/>
+      <c r="F283" s="40"/>
       <c r="G283" s="8" t="s">
         <v>536</v>
       </c>
@@ -11500,7 +11456,7 @@
       <c r="E284" s="34" t="s">
         <v>537</v>
       </c>
-      <c r="F284" s="49"/>
+      <c r="F284" s="40"/>
       <c r="G284" s="8" t="s">
         <v>538</v>
       </c>
@@ -11521,7 +11477,7 @@
       <c r="E285" s="34" t="s">
         <v>539</v>
       </c>
-      <c r="F285" s="49"/>
+      <c r="F285" s="40"/>
       <c r="G285" s="8" t="s">
         <v>540</v>
       </c>
@@ -11542,7 +11498,7 @@
       <c r="E286" s="34" t="s">
         <v>541</v>
       </c>
-      <c r="F286" s="49"/>
+      <c r="F286" s="40"/>
       <c r="G286" s="8" t="s">
         <v>542</v>
       </c>
@@ -11563,7 +11519,7 @@
       <c r="E287" s="34" t="s">
         <v>543</v>
       </c>
-      <c r="F287" s="49"/>
+      <c r="F287" s="40"/>
       <c r="G287" s="8" t="s">
         <v>544</v>
       </c>
@@ -11584,7 +11540,7 @@
       <c r="E288" s="34" t="s">
         <v>545</v>
       </c>
-      <c r="F288" s="49"/>
+      <c r="F288" s="40"/>
       <c r="G288" s="8" t="s">
         <v>546</v>
       </c>
@@ -11605,7 +11561,7 @@
       <c r="E289" s="34" t="s">
         <v>547</v>
       </c>
-      <c r="F289" s="49"/>
+      <c r="F289" s="40"/>
       <c r="G289" s="8" t="s">
         <v>548</v>
       </c>
@@ -11626,7 +11582,7 @@
       <c r="E290" s="34" t="s">
         <v>549</v>
       </c>
-      <c r="F290" s="49"/>
+      <c r="F290" s="40"/>
       <c r="G290" s="8" t="s">
         <v>550</v>
       </c>
@@ -11647,7 +11603,7 @@
       <c r="E291" s="34" t="s">
         <v>551</v>
       </c>
-      <c r="F291" s="49"/>
+      <c r="F291" s="40"/>
       <c r="G291" s="8" t="s">
         <v>552</v>
       </c>
@@ -11668,7 +11624,7 @@
       <c r="E292" s="34" t="s">
         <v>553</v>
       </c>
-      <c r="F292" s="49"/>
+      <c r="F292" s="40"/>
       <c r="G292" s="8" t="s">
         <v>554</v>
       </c>
@@ -11689,7 +11645,7 @@
       <c r="E293" s="34" t="s">
         <v>555</v>
       </c>
-      <c r="F293" s="49"/>
+      <c r="F293" s="40"/>
       <c r="G293" s="8" t="s">
         <v>556</v>
       </c>
@@ -11710,7 +11666,7 @@
       <c r="E294" s="34" t="s">
         <v>557</v>
       </c>
-      <c r="F294" s="49"/>
+      <c r="F294" s="40"/>
       <c r="G294" s="8" t="s">
         <v>558</v>
       </c>
@@ -11731,7 +11687,7 @@
       <c r="E295" s="34" t="s">
         <v>559</v>
       </c>
-      <c r="F295" s="49"/>
+      <c r="F295" s="40"/>
       <c r="G295" s="8" t="s">
         <v>560</v>
       </c>
@@ -11752,7 +11708,7 @@
       <c r="E296" s="34" t="s">
         <v>561</v>
       </c>
-      <c r="F296" s="49"/>
+      <c r="F296" s="40"/>
       <c r="G296" s="8" t="s">
         <v>562</v>
       </c>
@@ -11773,7 +11729,7 @@
       <c r="E297" s="34" t="s">
         <v>563</v>
       </c>
-      <c r="F297" s="49"/>
+      <c r="F297" s="40"/>
       <c r="G297" s="8" t="s">
         <v>564</v>
       </c>
@@ -11794,7 +11750,7 @@
       <c r="E298" s="34" t="s">
         <v>565</v>
       </c>
-      <c r="F298" s="49"/>
+      <c r="F298" s="40"/>
       <c r="G298" s="8" t="s">
         <v>566</v>
       </c>
@@ -11815,7 +11771,7 @@
       <c r="E299" s="34" t="s">
         <v>567</v>
       </c>
-      <c r="F299" s="49"/>
+      <c r="F299" s="40"/>
       <c r="G299" s="8" t="s">
         <v>568</v>
       </c>
@@ -11836,7 +11792,7 @@
       <c r="E300" s="34" t="s">
         <v>569</v>
       </c>
-      <c r="F300" s="49"/>
+      <c r="F300" s="40"/>
       <c r="G300" s="8" t="s">
         <v>570</v>
       </c>
@@ -11857,7 +11813,7 @@
       <c r="E301" s="34" t="s">
         <v>571</v>
       </c>
-      <c r="F301" s="49"/>
+      <c r="F301" s="40"/>
       <c r="G301" s="8" t="s">
         <v>572</v>
       </c>
@@ -11878,7 +11834,7 @@
       <c r="E302" s="34" t="s">
         <v>573</v>
       </c>
-      <c r="F302" s="49"/>
+      <c r="F302" s="40"/>
       <c r="G302" s="8" t="s">
         <v>574</v>
       </c>
@@ -11899,7 +11855,7 @@
       <c r="E303" s="34" t="s">
         <v>575</v>
       </c>
-      <c r="F303" s="49"/>
+      <c r="F303" s="40"/>
       <c r="G303" s="8" t="s">
         <v>576</v>
       </c>
@@ -11920,7 +11876,7 @@
       <c r="E304" s="34" t="s">
         <v>577</v>
       </c>
-      <c r="F304" s="49"/>
+      <c r="F304" s="40"/>
       <c r="G304" s="8" t="s">
         <v>578</v>
       </c>
@@ -11941,7 +11897,7 @@
       <c r="E305" s="34" t="s">
         <v>579</v>
       </c>
-      <c r="F305" s="49"/>
+      <c r="F305" s="40"/>
       <c r="G305" s="8" t="s">
         <v>580</v>
       </c>
@@ -11953,8 +11909,8 @@
         <v>72</v>
       </c>
       <c r="D306" s="22"/>
-      <c r="E306" s="40"/>
-      <c r="F306" s="53"/>
+      <c r="E306" s="42"/>
+      <c r="F306" s="44"/>
       <c r="G306" s="13" t="s">
         <v>73</v>
       </c>
@@ -11971,7 +11927,7 @@
       <c r="E307" s="37" t="s">
         <v>581</v>
       </c>
-      <c r="F307" s="48"/>
+      <c r="F307" s="38"/>
       <c r="G307" s="28" t="s">
         <v>582</v>
       </c>
@@ -11985,8 +11941,8 @@
       <c r="D308" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E308" s="38"/>
-      <c r="F308" s="49"/>
+      <c r="E308" s="39"/>
+      <c r="F308" s="40"/>
       <c r="G308" s="29"/>
     </row>
     <row r="309" spans="1:7">
@@ -12005,7 +11961,7 @@
       <c r="E309" s="34" t="s">
         <v>583</v>
       </c>
-      <c r="F309" s="50"/>
+      <c r="F309" s="41"/>
       <c r="G309" s="8" t="s">
         <v>584</v>
       </c>
@@ -12026,7 +11982,7 @@
       <c r="E310" s="34" t="s">
         <v>585</v>
       </c>
-      <c r="F310" s="50"/>
+      <c r="F310" s="41"/>
       <c r="G310" s="8" t="s">
         <v>586</v>
       </c>
@@ -12047,7 +12003,7 @@
       <c r="E311" s="34" t="s">
         <v>587</v>
       </c>
-      <c r="F311" s="50"/>
+      <c r="F311" s="41"/>
       <c r="G311" s="8" t="s">
         <v>588</v>
       </c>
@@ -12068,7 +12024,7 @@
       <c r="E312" s="34" t="s">
         <v>589</v>
       </c>
-      <c r="F312" s="50"/>
+      <c r="F312" s="41"/>
       <c r="G312" s="8" t="s">
         <v>590</v>
       </c>
@@ -12089,7 +12045,7 @@
       <c r="E313" s="34" t="s">
         <v>591</v>
       </c>
-      <c r="F313" s="50"/>
+      <c r="F313" s="41"/>
       <c r="G313" s="8" t="s">
         <v>592</v>
       </c>
@@ -12110,7 +12066,7 @@
       <c r="E314" s="34" t="s">
         <v>593</v>
       </c>
-      <c r="F314" s="50"/>
+      <c r="F314" s="41"/>
       <c r="G314" s="8" t="s">
         <v>594</v>
       </c>
@@ -12131,7 +12087,7 @@
       <c r="E315" s="34" t="s">
         <v>595</v>
       </c>
-      <c r="F315" s="50"/>
+      <c r="F315" s="41"/>
       <c r="G315" s="8" t="s">
         <v>596</v>
       </c>
@@ -12152,7 +12108,7 @@
       <c r="E316" s="34" t="s">
         <v>597</v>
       </c>
-      <c r="F316" s="50"/>
+      <c r="F316" s="41"/>
       <c r="G316" s="8" t="s">
         <v>598</v>
       </c>
@@ -12173,7 +12129,7 @@
       <c r="E317" s="34" t="s">
         <v>600</v>
       </c>
-      <c r="F317" s="50"/>
+      <c r="F317" s="41"/>
       <c r="G317" s="8" t="s">
         <v>601</v>
       </c>
@@ -12194,7 +12150,7 @@
       <c r="E318" s="34" t="s">
         <v>602</v>
       </c>
-      <c r="F318" s="50"/>
+      <c r="F318" s="41"/>
       <c r="G318" s="8" t="s">
         <v>603</v>
       </c>
@@ -12215,7 +12171,7 @@
       <c r="E319" s="34" t="s">
         <v>226</v>
       </c>
-      <c r="F319" s="50"/>
+      <c r="F319" s="41"/>
       <c r="G319" s="8" t="s">
         <v>604</v>
       </c>
@@ -12233,8 +12189,8 @@
       <c r="D320" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E320" s="39"/>
-      <c r="F320" s="46" t="s">
+      <c r="E320" s="41"/>
+      <c r="F320" s="34" t="s">
         <v>605</v>
       </c>
       <c r="G320" s="8" t="s">
@@ -12254,8 +12210,8 @@
       <c r="D321" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E321" s="39"/>
-      <c r="F321" s="46" t="s">
+      <c r="E321" s="41"/>
+      <c r="F321" s="34" t="s">
         <v>607</v>
       </c>
       <c r="G321" s="8" t="s">
@@ -12278,7 +12234,7 @@
       <c r="E322" s="34" t="s">
         <v>609</v>
       </c>
-      <c r="F322" s="50"/>
+      <c r="F322" s="41"/>
       <c r="G322" s="8" t="s">
         <v>610</v>
       </c>
@@ -12299,7 +12255,7 @@
       <c r="E323" s="34" t="s">
         <v>611</v>
       </c>
-      <c r="F323" s="50"/>
+      <c r="F323" s="41"/>
       <c r="G323" s="8" t="s">
         <v>612</v>
       </c>
@@ -12320,7 +12276,7 @@
       <c r="E324" s="34" t="s">
         <v>613</v>
       </c>
-      <c r="F324" s="50"/>
+      <c r="F324" s="41"/>
       <c r="G324" s="8" t="s">
         <v>614</v>
       </c>
@@ -12341,7 +12297,7 @@
       <c r="E325" s="34" t="s">
         <v>615</v>
       </c>
-      <c r="F325" s="50"/>
+      <c r="F325" s="41"/>
       <c r="G325" s="8" t="s">
         <v>616</v>
       </c>
@@ -12362,7 +12318,7 @@
       <c r="E326" s="34" t="s">
         <v>617</v>
       </c>
-      <c r="F326" s="50"/>
+      <c r="F326" s="41"/>
       <c r="G326" s="8" t="s">
         <v>618</v>
       </c>
@@ -12383,7 +12339,7 @@
       <c r="E327" s="34" t="s">
         <v>619</v>
       </c>
-      <c r="F327" s="50"/>
+      <c r="F327" s="41"/>
       <c r="G327" s="8" t="s">
         <v>620</v>
       </c>
@@ -12404,7 +12360,7 @@
       <c r="E328" s="34" t="s">
         <v>621</v>
       </c>
-      <c r="F328" s="50"/>
+      <c r="F328" s="41"/>
       <c r="G328" s="8" t="s">
         <v>622</v>
       </c>
@@ -12425,7 +12381,7 @@
       <c r="E329" s="34" t="s">
         <v>623</v>
       </c>
-      <c r="F329" s="50"/>
+      <c r="F329" s="41"/>
       <c r="G329" s="8" t="s">
         <v>624</v>
       </c>
@@ -12446,7 +12402,7 @@
       <c r="E330" s="34" t="s">
         <v>625</v>
       </c>
-      <c r="F330" s="50"/>
+      <c r="F330" s="41"/>
       <c r="G330" s="8" t="s">
         <v>626</v>
       </c>
@@ -12467,7 +12423,7 @@
       <c r="E331" s="34" t="s">
         <v>627</v>
       </c>
-      <c r="F331" s="50"/>
+      <c r="F331" s="41"/>
       <c r="G331" s="8" t="s">
         <v>628</v>
       </c>
@@ -12488,7 +12444,7 @@
       <c r="E332" s="34" t="s">
         <v>629</v>
       </c>
-      <c r="F332" s="50"/>
+      <c r="F332" s="41"/>
       <c r="G332" s="8" t="s">
         <v>630</v>
       </c>
@@ -12509,7 +12465,7 @@
       <c r="E333" s="34" t="s">
         <v>631</v>
       </c>
-      <c r="F333" s="50"/>
+      <c r="F333" s="41"/>
       <c r="G333" s="8" t="s">
         <v>632</v>
       </c>
@@ -12530,7 +12486,7 @@
       <c r="E334" s="34" t="s">
         <v>633</v>
       </c>
-      <c r="F334" s="50"/>
+      <c r="F334" s="41"/>
       <c r="G334" s="8" t="s">
         <v>634</v>
       </c>
@@ -12551,7 +12507,7 @@
       <c r="E335" s="34" t="s">
         <v>635</v>
       </c>
-      <c r="F335" s="50"/>
+      <c r="F335" s="41"/>
       <c r="G335" s="8" t="s">
         <v>636</v>
       </c>
@@ -12572,7 +12528,7 @@
       <c r="E336" s="34" t="s">
         <v>637</v>
       </c>
-      <c r="F336" s="50"/>
+      <c r="F336" s="41"/>
       <c r="G336" s="8" t="s">
         <v>638</v>
       </c>
@@ -12593,7 +12549,7 @@
       <c r="E337" s="34" t="s">
         <v>639</v>
       </c>
-      <c r="F337" s="50"/>
+      <c r="F337" s="41"/>
       <c r="G337" s="8" t="s">
         <v>640</v>
       </c>
@@ -12611,8 +12567,8 @@
       <c r="D338" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E338" s="39"/>
-      <c r="F338" s="46" t="s">
+      <c r="E338" s="41"/>
+      <c r="F338" s="34" t="s">
         <v>641</v>
       </c>
       <c r="G338" s="8" t="s">
@@ -12635,7 +12591,7 @@
       <c r="E339" s="34" t="s">
         <v>643</v>
       </c>
-      <c r="F339" s="50"/>
+      <c r="F339" s="41"/>
       <c r="G339" s="8" t="s">
         <v>644</v>
       </c>
@@ -12656,7 +12612,7 @@
       <c r="E340" s="34" t="s">
         <v>645</v>
       </c>
-      <c r="F340" s="50"/>
+      <c r="F340" s="41"/>
       <c r="G340" s="8" t="s">
         <v>646</v>
       </c>
@@ -12677,7 +12633,7 @@
       <c r="E341" s="34" t="s">
         <v>647</v>
       </c>
-      <c r="F341" s="50"/>
+      <c r="F341" s="41"/>
       <c r="G341" s="8" t="s">
         <v>648</v>
       </c>
@@ -12698,7 +12654,7 @@
       <c r="E342" s="34" t="s">
         <v>649</v>
       </c>
-      <c r="F342" s="50"/>
+      <c r="F342" s="41"/>
       <c r="G342" s="8" t="s">
         <v>650</v>
       </c>
@@ -12719,7 +12675,7 @@
       <c r="E343" s="34" t="s">
         <v>651</v>
       </c>
-      <c r="F343" s="50"/>
+      <c r="F343" s="41"/>
       <c r="G343" s="8" t="s">
         <v>652</v>
       </c>
@@ -12740,7 +12696,7 @@
       <c r="E344" s="34" t="s">
         <v>653</v>
       </c>
-      <c r="F344" s="50"/>
+      <c r="F344" s="41"/>
       <c r="G344" s="8" t="s">
         <v>654</v>
       </c>
@@ -12758,8 +12714,8 @@
       <c r="D345" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E345" s="39"/>
-      <c r="F345" s="46" t="s">
+      <c r="E345" s="41"/>
+      <c r="F345" s="34" t="s">
         <v>655</v>
       </c>
       <c r="G345" s="8" t="s">
@@ -12779,8 +12735,8 @@
       <c r="D346" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E346" s="39"/>
-      <c r="F346" s="46" t="s">
+      <c r="E346" s="41"/>
+      <c r="F346" s="34" t="s">
         <v>657</v>
       </c>
       <c r="G346" s="8" t="s">
@@ -12803,7 +12759,7 @@
       <c r="E347" s="34" t="s">
         <v>356</v>
       </c>
-      <c r="F347" s="50"/>
+      <c r="F347" s="41"/>
       <c r="G347" s="8" t="s">
         <v>659</v>
       </c>
@@ -12824,7 +12780,7 @@
       <c r="E348" s="34" t="s">
         <v>660</v>
       </c>
-      <c r="F348" s="50"/>
+      <c r="F348" s="41"/>
       <c r="G348" s="8" t="s">
         <v>661</v>
       </c>
@@ -12845,7 +12801,7 @@
       <c r="E349" s="34" t="s">
         <v>662</v>
       </c>
-      <c r="F349" s="50"/>
+      <c r="F349" s="41"/>
       <c r="G349" s="8" t="s">
         <v>663</v>
       </c>
@@ -12857,8 +12813,8 @@
         <v>72</v>
       </c>
       <c r="D350" s="22"/>
-      <c r="E350" s="40"/>
-      <c r="F350" s="51"/>
+      <c r="E350" s="42"/>
+      <c r="F350" s="42"/>
       <c r="G350" s="13" t="s">
         <v>73</v>
       </c>
@@ -12875,7 +12831,7 @@
       <c r="E351" s="37" t="s">
         <v>664</v>
       </c>
-      <c r="F351" s="48"/>
+      <c r="F351" s="38"/>
       <c r="G351" s="28" t="s">
         <v>665</v>
       </c>
@@ -12889,8 +12845,8 @@
       <c r="D352" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E352" s="38"/>
-      <c r="F352" s="49"/>
+      <c r="E352" s="39"/>
+      <c r="F352" s="40"/>
       <c r="G352" s="29"/>
     </row>
     <row r="353" spans="1:7">
@@ -12909,7 +12865,7 @@
       <c r="E353" s="34" t="s">
         <v>666</v>
       </c>
-      <c r="F353" s="50"/>
+      <c r="F353" s="41"/>
       <c r="G353" s="8" t="s">
         <v>667</v>
       </c>
@@ -12930,7 +12886,7 @@
       <c r="E354" s="34" t="s">
         <v>668</v>
       </c>
-      <c r="F354" s="50"/>
+      <c r="F354" s="41"/>
       <c r="G354" s="8" t="s">
         <v>669</v>
       </c>
@@ -12951,7 +12907,7 @@
       <c r="E355" s="34" t="s">
         <v>670</v>
       </c>
-      <c r="F355" s="50"/>
+      <c r="F355" s="41"/>
       <c r="G355" s="8" t="s">
         <v>671</v>
       </c>
@@ -12972,7 +12928,7 @@
       <c r="E356" s="34" t="s">
         <v>672</v>
       </c>
-      <c r="F356" s="50"/>
+      <c r="F356" s="41"/>
       <c r="G356" s="8" t="s">
         <v>673</v>
       </c>
@@ -12993,7 +12949,7 @@
       <c r="E357" s="34" t="s">
         <v>674</v>
       </c>
-      <c r="F357" s="50"/>
+      <c r="F357" s="41"/>
       <c r="G357" s="8" t="s">
         <v>675</v>
       </c>
@@ -13014,7 +12970,7 @@
       <c r="E358" s="34" t="s">
         <v>676</v>
       </c>
-      <c r="F358" s="50"/>
+      <c r="F358" s="41"/>
       <c r="G358" s="8" t="s">
         <v>677</v>
       </c>
@@ -13035,7 +12991,7 @@
       <c r="E359" s="34" t="s">
         <v>678</v>
       </c>
-      <c r="F359" s="50"/>
+      <c r="F359" s="41"/>
       <c r="G359" s="8" t="s">
         <v>679</v>
       </c>
@@ -13053,8 +13009,8 @@
       <c r="D360" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E360" s="39"/>
-      <c r="F360" s="46" t="s">
+      <c r="E360" s="41"/>
+      <c r="F360" s="34" t="s">
         <v>680</v>
       </c>
       <c r="G360" s="8" t="s">
@@ -13074,8 +13030,8 @@
       <c r="D361" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E361" s="39"/>
-      <c r="F361" s="46" t="s">
+      <c r="E361" s="41"/>
+      <c r="F361" s="34" t="s">
         <v>682</v>
       </c>
       <c r="G361" s="8" t="s">
@@ -13095,8 +13051,8 @@
       <c r="D362" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E362" s="39"/>
-      <c r="F362" s="46" t="s">
+      <c r="E362" s="41"/>
+      <c r="F362" s="34" t="s">
         <v>684</v>
       </c>
       <c r="G362" s="8" t="s">
@@ -13119,7 +13075,7 @@
       <c r="E363" s="34" t="s">
         <v>686</v>
       </c>
-      <c r="F363" s="50"/>
+      <c r="F363" s="41"/>
       <c r="G363" s="8" t="s">
         <v>687</v>
       </c>
@@ -13140,7 +13096,7 @@
       <c r="E364" s="34" t="s">
         <v>688</v>
       </c>
-      <c r="F364" s="50"/>
+      <c r="F364" s="41"/>
       <c r="G364" s="8" t="s">
         <v>689</v>
       </c>
@@ -13161,7 +13117,7 @@
       <c r="E365" s="34" t="s">
         <v>690</v>
       </c>
-      <c r="F365" s="50"/>
+      <c r="F365" s="41"/>
       <c r="G365" s="8" t="s">
         <v>691</v>
       </c>
@@ -13182,7 +13138,7 @@
       <c r="E366" s="34" t="s">
         <v>692</v>
       </c>
-      <c r="F366" s="50"/>
+      <c r="F366" s="41"/>
       <c r="G366" s="8" t="s">
         <v>693</v>
       </c>
@@ -13203,7 +13159,7 @@
       <c r="E367" s="34" t="s">
         <v>694</v>
       </c>
-      <c r="F367" s="50"/>
+      <c r="F367" s="41"/>
       <c r="G367" s="8" t="s">
         <v>695</v>
       </c>
@@ -13224,7 +13180,7 @@
       <c r="E368" s="34" t="s">
         <v>696</v>
       </c>
-      <c r="F368" s="50"/>
+      <c r="F368" s="41"/>
       <c r="G368" s="8" t="s">
         <v>697</v>
       </c>
@@ -13245,7 +13201,7 @@
       <c r="E369" s="34" t="s">
         <v>698</v>
       </c>
-      <c r="F369" s="50"/>
+      <c r="F369" s="41"/>
       <c r="G369" s="8" t="s">
         <v>699</v>
       </c>
@@ -13266,7 +13222,7 @@
       <c r="E370" s="34" t="s">
         <v>700</v>
       </c>
-      <c r="F370" s="50"/>
+      <c r="F370" s="41"/>
       <c r="G370" s="8" t="s">
         <v>701</v>
       </c>
@@ -13287,7 +13243,7 @@
       <c r="E371" s="34" t="s">
         <v>702</v>
       </c>
-      <c r="F371" s="50"/>
+      <c r="F371" s="41"/>
       <c r="G371" s="8" t="s">
         <v>703</v>
       </c>
@@ -13308,7 +13264,7 @@
       <c r="E372" s="34" t="s">
         <v>704</v>
       </c>
-      <c r="F372" s="50"/>
+      <c r="F372" s="41"/>
       <c r="G372" s="8" t="s">
         <v>705</v>
       </c>
@@ -13329,7 +13285,7 @@
       <c r="E373" s="34" t="s">
         <v>706</v>
       </c>
-      <c r="F373" s="50"/>
+      <c r="F373" s="41"/>
       <c r="G373" s="8" t="s">
         <v>707</v>
       </c>
@@ -13350,7 +13306,7 @@
       <c r="E374" s="34" t="s">
         <v>708</v>
       </c>
-      <c r="F374" s="50"/>
+      <c r="F374" s="41"/>
       <c r="G374" s="8" t="s">
         <v>709</v>
       </c>
@@ -13371,7 +13327,7 @@
       <c r="E375" s="34" t="s">
         <v>710</v>
       </c>
-      <c r="F375" s="50"/>
+      <c r="F375" s="41"/>
       <c r="G375" s="8" t="s">
         <v>711</v>
       </c>
@@ -13392,7 +13348,7 @@
       <c r="E376" s="34" t="s">
         <v>712</v>
       </c>
-      <c r="F376" s="50"/>
+      <c r="F376" s="41"/>
       <c r="G376" s="8" t="s">
         <v>713</v>
       </c>
@@ -13413,7 +13369,7 @@
       <c r="E377" s="34" t="s">
         <v>714</v>
       </c>
-      <c r="F377" s="50"/>
+      <c r="F377" s="41"/>
       <c r="G377" s="8" t="s">
         <v>715</v>
       </c>
@@ -13434,7 +13390,7 @@
       <c r="E378" s="34" t="s">
         <v>716</v>
       </c>
-      <c r="F378" s="50"/>
+      <c r="F378" s="41"/>
       <c r="G378" s="8" t="s">
         <v>717</v>
       </c>
@@ -13455,7 +13411,7 @@
       <c r="E379" s="34" t="s">
         <v>718</v>
       </c>
-      <c r="F379" s="50"/>
+      <c r="F379" s="41"/>
       <c r="G379" s="8" t="s">
         <v>719</v>
       </c>
@@ -13476,7 +13432,7 @@
       <c r="E380" s="34" t="s">
         <v>720</v>
       </c>
-      <c r="F380" s="50"/>
+      <c r="F380" s="41"/>
       <c r="G380" s="8" t="s">
         <v>721</v>
       </c>
@@ -13497,7 +13453,7 @@
       <c r="E381" s="34" t="s">
         <v>722</v>
       </c>
-      <c r="F381" s="50"/>
+      <c r="F381" s="41"/>
       <c r="G381" s="8" t="s">
         <v>723</v>
       </c>
@@ -13518,7 +13474,7 @@
       <c r="E382" s="34" t="s">
         <v>724</v>
       </c>
-      <c r="F382" s="50"/>
+      <c r="F382" s="41"/>
       <c r="G382" s="8" t="s">
         <v>725</v>
       </c>
@@ -13539,7 +13495,7 @@
       <c r="E383" s="34" t="s">
         <v>166</v>
       </c>
-      <c r="F383" s="50"/>
+      <c r="F383" s="41"/>
       <c r="G383" s="8" t="s">
         <v>726</v>
       </c>
@@ -13560,7 +13516,7 @@
       <c r="E384" s="34" t="s">
         <v>168</v>
       </c>
-      <c r="F384" s="50"/>
+      <c r="F384" s="41"/>
       <c r="G384" s="8" t="s">
         <v>727</v>
       </c>
@@ -13581,7 +13537,7 @@
       <c r="E385" s="34" t="s">
         <v>728</v>
       </c>
-      <c r="F385" s="50"/>
+      <c r="F385" s="41"/>
       <c r="G385" s="8" t="s">
         <v>729</v>
       </c>
@@ -13602,7 +13558,7 @@
       <c r="E386" s="34" t="s">
         <v>730</v>
       </c>
-      <c r="F386" s="50"/>
+      <c r="F386" s="41"/>
       <c r="G386" s="8" t="s">
         <v>731</v>
       </c>
@@ -13623,7 +13579,7 @@
       <c r="E387" s="34" t="s">
         <v>732</v>
       </c>
-      <c r="F387" s="50"/>
+      <c r="F387" s="41"/>
       <c r="G387" s="8" t="s">
         <v>733</v>
       </c>
@@ -13644,7 +13600,7 @@
       <c r="E388" s="34" t="s">
         <v>734</v>
       </c>
-      <c r="F388" s="50"/>
+      <c r="F388" s="41"/>
       <c r="G388" s="8" t="s">
         <v>735</v>
       </c>
@@ -13665,7 +13621,7 @@
       <c r="E389" s="34" t="s">
         <v>276</v>
       </c>
-      <c r="F389" s="50"/>
+      <c r="F389" s="41"/>
       <c r="G389" s="8" t="s">
         <v>736</v>
       </c>
@@ -13686,7 +13642,7 @@
       <c r="E390" s="34" t="s">
         <v>278</v>
       </c>
-      <c r="F390" s="50"/>
+      <c r="F390" s="41"/>
       <c r="G390" s="8" t="s">
         <v>737</v>
       </c>
@@ -13707,7 +13663,7 @@
       <c r="E391" s="34" t="s">
         <v>738</v>
       </c>
-      <c r="F391" s="50"/>
+      <c r="F391" s="41"/>
       <c r="G391" s="8" t="s">
         <v>739</v>
       </c>
@@ -13728,7 +13684,7 @@
       <c r="E392" s="34" t="s">
         <v>740</v>
       </c>
-      <c r="F392" s="50"/>
+      <c r="F392" s="41"/>
       <c r="G392" s="8" t="s">
         <v>741</v>
       </c>
@@ -13749,7 +13705,7 @@
       <c r="E393" s="34" t="s">
         <v>742</v>
       </c>
-      <c r="F393" s="50"/>
+      <c r="F393" s="41"/>
       <c r="G393" s="8" t="s">
         <v>743</v>
       </c>
@@ -13761,8 +13717,8 @@
         <v>72</v>
       </c>
       <c r="D394" s="22"/>
-      <c r="E394" s="40"/>
-      <c r="F394" s="51"/>
+      <c r="E394" s="42"/>
+      <c r="F394" s="42"/>
       <c r="G394" s="13" t="s">
         <v>73</v>
       </c>
@@ -13776,8 +13732,8 @@
       </c>
       <c r="C395" s="23"/>
       <c r="D395" s="23"/>
-      <c r="E395" s="41"/>
-      <c r="F395" s="54" t="s">
+      <c r="E395" s="38"/>
+      <c r="F395" s="37" t="s">
         <v>744</v>
       </c>
       <c r="G395" s="28" t="s">
@@ -13793,8 +13749,8 @@
       <c r="D396" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E396" s="42"/>
-      <c r="F396" s="55"/>
+      <c r="E396" s="40"/>
+      <c r="F396" s="39"/>
       <c r="G396" s="29"/>
     </row>
     <row r="397" spans="1:7">
@@ -13810,8 +13766,8 @@
       <c r="D397" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E397" s="39"/>
-      <c r="F397" s="46" t="s">
+      <c r="E397" s="41"/>
+      <c r="F397" s="34" t="s">
         <v>746</v>
       </c>
       <c r="G397" s="8" t="s">
@@ -13831,8 +13787,8 @@
       <c r="D398" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E398" s="39"/>
-      <c r="F398" s="46" t="s">
+      <c r="E398" s="41"/>
+      <c r="F398" s="34" t="s">
         <v>748</v>
       </c>
       <c r="G398" s="8" t="s">
@@ -13852,8 +13808,8 @@
       <c r="D399" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E399" s="39"/>
-      <c r="F399" s="46" t="s">
+      <c r="E399" s="41"/>
+      <c r="F399" s="34" t="s">
         <v>750</v>
       </c>
       <c r="G399" s="8" t="s">
@@ -13873,8 +13829,8 @@
       <c r="D400" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E400" s="39"/>
-      <c r="F400" s="46" t="s">
+      <c r="E400" s="41"/>
+      <c r="F400" s="34" t="s">
         <v>752</v>
       </c>
       <c r="G400" s="8" t="s">
@@ -13897,7 +13853,7 @@
       <c r="E401" s="34" t="s">
         <v>754</v>
       </c>
-      <c r="F401" s="50"/>
+      <c r="F401" s="41"/>
       <c r="G401" s="8" t="s">
         <v>755</v>
       </c>
@@ -13918,7 +13874,7 @@
       <c r="E402" s="34" t="s">
         <v>756</v>
       </c>
-      <c r="F402" s="50"/>
+      <c r="F402" s="41"/>
       <c r="G402" s="8" t="s">
         <v>757</v>
       </c>
@@ -13939,7 +13895,7 @@
       <c r="E403" s="34" t="s">
         <v>758</v>
       </c>
-      <c r="F403" s="50"/>
+      <c r="F403" s="41"/>
       <c r="G403" s="8" t="s">
         <v>759</v>
       </c>
@@ -13960,7 +13916,7 @@
       <c r="E404" s="34" t="s">
         <v>760</v>
       </c>
-      <c r="F404" s="50"/>
+      <c r="F404" s="41"/>
       <c r="G404" s="8" t="s">
         <v>761</v>
       </c>
@@ -13981,7 +13937,7 @@
       <c r="E405" s="34" t="s">
         <v>762</v>
       </c>
-      <c r="F405" s="50"/>
+      <c r="F405" s="41"/>
       <c r="G405" s="8" t="s">
         <v>763</v>
       </c>
@@ -14002,7 +13958,7 @@
       <c r="E406" s="34" t="s">
         <v>764</v>
       </c>
-      <c r="F406" s="50"/>
+      <c r="F406" s="41"/>
       <c r="G406" s="8" t="s">
         <v>765</v>
       </c>
@@ -14023,7 +13979,7 @@
       <c r="E407" s="34" t="s">
         <v>244</v>
       </c>
-      <c r="F407" s="50"/>
+      <c r="F407" s="41"/>
       <c r="G407" s="8" t="s">
         <v>766</v>
       </c>
@@ -14044,7 +14000,7 @@
       <c r="E408" s="34" t="s">
         <v>246</v>
       </c>
-      <c r="F408" s="50"/>
+      <c r="F408" s="41"/>
       <c r="G408" s="8" t="s">
         <v>767</v>
       </c>
@@ -14065,7 +14021,7 @@
       <c r="E409" s="34" t="s">
         <v>768</v>
       </c>
-      <c r="F409" s="50"/>
+      <c r="F409" s="41"/>
       <c r="G409" s="8" t="s">
         <v>769</v>
       </c>
@@ -14086,7 +14042,7 @@
       <c r="E410" s="34" t="s">
         <v>770</v>
       </c>
-      <c r="F410" s="50"/>
+      <c r="F410" s="41"/>
       <c r="G410" s="8" t="s">
         <v>771</v>
       </c>
@@ -14107,7 +14063,7 @@
       <c r="E411" s="34" t="s">
         <v>772</v>
       </c>
-      <c r="F411" s="50"/>
+      <c r="F411" s="41"/>
       <c r="G411" s="8" t="s">
         <v>773</v>
       </c>
@@ -14128,7 +14084,7 @@
       <c r="E412" s="34" t="s">
         <v>774</v>
       </c>
-      <c r="F412" s="50"/>
+      <c r="F412" s="41"/>
       <c r="G412" s="8" t="s">
         <v>775</v>
       </c>
@@ -14149,7 +14105,7 @@
       <c r="E413" s="34" t="s">
         <v>776</v>
       </c>
-      <c r="F413" s="50"/>
+      <c r="F413" s="41"/>
       <c r="G413" s="8" t="s">
         <v>777</v>
       </c>
@@ -14170,7 +14126,7 @@
       <c r="E414" s="34" t="s">
         <v>778</v>
       </c>
-      <c r="F414" s="50"/>
+      <c r="F414" s="41"/>
       <c r="G414" s="8" t="s">
         <v>779</v>
       </c>
@@ -14191,7 +14147,7 @@
       <c r="E415" s="34" t="s">
         <v>780</v>
       </c>
-      <c r="F415" s="50"/>
+      <c r="F415" s="41"/>
       <c r="G415" s="8" t="s">
         <v>781</v>
       </c>
@@ -14212,7 +14168,7 @@
       <c r="E416" s="34" t="s">
         <v>782</v>
       </c>
-      <c r="F416" s="50"/>
+      <c r="F416" s="41"/>
       <c r="G416" s="8" t="s">
         <v>783</v>
       </c>
@@ -14230,8 +14186,8 @@
       <c r="D417" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E417" s="39"/>
-      <c r="F417" s="46" t="s">
+      <c r="E417" s="41"/>
+      <c r="F417" s="34" t="s">
         <v>784</v>
       </c>
       <c r="G417" s="8" t="s">
@@ -14251,8 +14207,8 @@
       <c r="D418" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E418" s="39"/>
-      <c r="F418" s="46" t="s">
+      <c r="E418" s="41"/>
+      <c r="F418" s="34" t="s">
         <v>786</v>
       </c>
       <c r="G418" s="8" t="s">
@@ -14272,8 +14228,8 @@
       <c r="D419" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E419" s="39"/>
-      <c r="F419" s="46" t="s">
+      <c r="E419" s="41"/>
+      <c r="F419" s="34" t="s">
         <v>788</v>
       </c>
       <c r="G419" s="8" t="s">
@@ -14296,7 +14252,7 @@
       <c r="E420" s="34" t="s">
         <v>790</v>
       </c>
-      <c r="F420" s="50"/>
+      <c r="F420" s="41"/>
       <c r="G420" s="8" t="s">
         <v>791</v>
       </c>
@@ -14317,7 +14273,7 @@
       <c r="E421" s="34" t="s">
         <v>792</v>
       </c>
-      <c r="F421" s="50"/>
+      <c r="F421" s="41"/>
       <c r="G421" s="8" t="s">
         <v>793</v>
       </c>
@@ -14338,7 +14294,7 @@
       <c r="E422" s="34" t="s">
         <v>794</v>
       </c>
-      <c r="F422" s="50"/>
+      <c r="F422" s="41"/>
       <c r="G422" s="8" t="s">
         <v>795</v>
       </c>
@@ -14359,7 +14315,7 @@
       <c r="E423" s="34" t="s">
         <v>796</v>
       </c>
-      <c r="F423" s="50"/>
+      <c r="F423" s="41"/>
       <c r="G423" s="8" t="s">
         <v>797</v>
       </c>
@@ -14380,7 +14336,7 @@
       <c r="E424" s="34" t="s">
         <v>799</v>
       </c>
-      <c r="F424" s="50"/>
+      <c r="F424" s="41"/>
       <c r="G424" s="8" t="s">
         <v>800</v>
       </c>
@@ -14401,7 +14357,7 @@
       <c r="E425" s="34" t="s">
         <v>801</v>
       </c>
-      <c r="F425" s="50"/>
+      <c r="F425" s="41"/>
       <c r="G425" s="8" t="s">
         <v>802</v>
       </c>
@@ -14422,7 +14378,7 @@
       <c r="E426" s="34" t="s">
         <v>803</v>
       </c>
-      <c r="F426" s="50"/>
+      <c r="F426" s="41"/>
       <c r="G426" s="8" t="s">
         <v>804</v>
       </c>
@@ -14443,7 +14399,7 @@
       <c r="E427" s="34" t="s">
         <v>805</v>
       </c>
-      <c r="F427" s="50"/>
+      <c r="F427" s="41"/>
       <c r="G427" s="8" t="s">
         <v>806</v>
       </c>
@@ -14464,7 +14420,7 @@
       <c r="E428" s="34" t="s">
         <v>807</v>
       </c>
-      <c r="F428" s="50"/>
+      <c r="F428" s="41"/>
       <c r="G428" s="8" t="s">
         <v>808</v>
       </c>
@@ -14485,7 +14441,7 @@
       <c r="E429" s="34" t="s">
         <v>809</v>
       </c>
-      <c r="F429" s="50"/>
+      <c r="F429" s="41"/>
       <c r="G429" s="8" t="s">
         <v>810</v>
       </c>
@@ -14506,7 +14462,7 @@
       <c r="E430" s="34" t="s">
         <v>811</v>
       </c>
-      <c r="F430" s="50"/>
+      <c r="F430" s="41"/>
       <c r="G430" s="8" t="s">
         <v>812</v>
       </c>
@@ -14527,7 +14483,7 @@
       <c r="E431" s="34" t="s">
         <v>813</v>
       </c>
-      <c r="F431" s="50"/>
+      <c r="F431" s="41"/>
       <c r="G431" s="8" t="s">
         <v>814</v>
       </c>
@@ -14545,8 +14501,8 @@
       <c r="D432" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E432" s="39"/>
-      <c r="F432" s="46" t="s">
+      <c r="E432" s="41"/>
+      <c r="F432" s="34" t="s">
         <v>816</v>
       </c>
       <c r="G432" s="8" t="s">
@@ -14566,8 +14522,8 @@
       <c r="D433" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E433" s="39"/>
-      <c r="F433" s="46" t="s">
+      <c r="E433" s="41"/>
+      <c r="F433" s="34" t="s">
         <v>597</v>
       </c>
       <c r="G433" s="8" t="s">
@@ -14590,7 +14546,7 @@
       <c r="E434" s="34" t="s">
         <v>819</v>
       </c>
-      <c r="F434" s="50"/>
+      <c r="F434" s="41"/>
       <c r="G434" s="8" t="s">
         <v>820</v>
       </c>
@@ -14611,7 +14567,7 @@
       <c r="E435" s="34" t="s">
         <v>821</v>
       </c>
-      <c r="F435" s="50"/>
+      <c r="F435" s="41"/>
       <c r="G435" s="8" t="s">
         <v>822</v>
       </c>
@@ -14632,7 +14588,7 @@
       <c r="E436" s="34" t="s">
         <v>823</v>
       </c>
-      <c r="F436" s="50"/>
+      <c r="F436" s="41"/>
       <c r="G436" s="8" t="s">
         <v>824</v>
       </c>
@@ -14653,7 +14609,7 @@
       <c r="E437" s="34" t="s">
         <v>825</v>
       </c>
-      <c r="F437" s="50"/>
+      <c r="F437" s="41"/>
       <c r="G437" s="8" t="s">
         <v>826</v>
       </c>
@@ -14665,8 +14621,8 @@
         <v>72</v>
       </c>
       <c r="D438" s="22"/>
-      <c r="E438" s="40"/>
-      <c r="F438" s="51"/>
+      <c r="E438" s="42"/>
+      <c r="F438" s="42"/>
       <c r="G438" s="13" t="s">
         <v>73</v>
       </c>
@@ -14683,7 +14639,7 @@
       <c r="E439" s="37" t="s">
         <v>827</v>
       </c>
-      <c r="F439" s="48"/>
+      <c r="F439" s="38"/>
       <c r="G439" s="28" t="s">
         <v>828</v>
       </c>
@@ -14697,8 +14653,8 @@
       <c r="D440" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E440" s="38"/>
-      <c r="F440" s="49"/>
+      <c r="E440" s="39"/>
+      <c r="F440" s="40"/>
       <c r="G440" s="29"/>
     </row>
     <row r="441" spans="1:7">
@@ -14717,7 +14673,7 @@
       <c r="E441" s="34" t="s">
         <v>829</v>
       </c>
-      <c r="F441" s="50"/>
+      <c r="F441" s="41"/>
       <c r="G441" s="8" t="s">
         <v>830</v>
       </c>
@@ -14738,7 +14694,7 @@
       <c r="E442" s="34" t="s">
         <v>831</v>
       </c>
-      <c r="F442" s="50"/>
+      <c r="F442" s="41"/>
       <c r="G442" s="8" t="s">
         <v>832</v>
       </c>
@@ -14759,7 +14715,7 @@
       <c r="E443" s="34" t="s">
         <v>833</v>
       </c>
-      <c r="F443" s="50"/>
+      <c r="F443" s="41"/>
       <c r="G443" s="8" t="s">
         <v>834</v>
       </c>
@@ -14780,7 +14736,7 @@
       <c r="E444" s="34" t="s">
         <v>835</v>
       </c>
-      <c r="F444" s="50"/>
+      <c r="F444" s="41"/>
       <c r="G444" s="8" t="s">
         <v>836</v>
       </c>
@@ -14801,7 +14757,7 @@
       <c r="E445" s="34" t="s">
         <v>837</v>
       </c>
-      <c r="F445" s="50"/>
+      <c r="F445" s="41"/>
       <c r="G445" s="8" t="s">
         <v>838</v>
       </c>
@@ -14822,7 +14778,7 @@
       <c r="E446" s="34" t="s">
         <v>839</v>
       </c>
-      <c r="F446" s="50"/>
+      <c r="F446" s="41"/>
       <c r="G446" s="8" t="s">
         <v>840</v>
       </c>
@@ -14843,7 +14799,7 @@
       <c r="E447" s="34" t="s">
         <v>841</v>
       </c>
-      <c r="F447" s="50"/>
+      <c r="F447" s="41"/>
       <c r="G447" s="8" t="s">
         <v>842</v>
       </c>
@@ -14864,7 +14820,7 @@
       <c r="E448" s="34" t="s">
         <v>843</v>
       </c>
-      <c r="F448" s="50"/>
+      <c r="F448" s="41"/>
       <c r="G448" s="8" t="s">
         <v>844</v>
       </c>
@@ -14885,7 +14841,7 @@
       <c r="E449" s="34" t="s">
         <v>845</v>
       </c>
-      <c r="F449" s="50"/>
+      <c r="F449" s="41"/>
       <c r="G449" s="8" t="s">
         <v>846</v>
       </c>
@@ -14906,7 +14862,7 @@
       <c r="E450" s="34" t="s">
         <v>847</v>
       </c>
-      <c r="F450" s="50"/>
+      <c r="F450" s="41"/>
       <c r="G450" s="8" t="s">
         <v>848</v>
       </c>
@@ -14927,7 +14883,7 @@
       <c r="E451" s="34" t="s">
         <v>849</v>
       </c>
-      <c r="F451" s="50"/>
+      <c r="F451" s="41"/>
       <c r="G451" s="8" t="s">
         <v>850</v>
       </c>
@@ -14948,7 +14904,7 @@
       <c r="E452" s="34" t="s">
         <v>851</v>
       </c>
-      <c r="F452" s="50"/>
+      <c r="F452" s="41"/>
       <c r="G452" s="8" t="s">
         <v>852</v>
       </c>
@@ -14969,7 +14925,7 @@
       <c r="E453" s="34" t="s">
         <v>853</v>
       </c>
-      <c r="F453" s="50"/>
+      <c r="F453" s="41"/>
       <c r="G453" s="8" t="s">
         <v>854</v>
       </c>
@@ -14990,7 +14946,7 @@
       <c r="E454" s="34" t="s">
         <v>855</v>
       </c>
-      <c r="F454" s="50"/>
+      <c r="F454" s="41"/>
       <c r="G454" s="8" t="s">
         <v>856</v>
       </c>
@@ -15011,7 +14967,7 @@
       <c r="E455" s="34" t="s">
         <v>857</v>
       </c>
-      <c r="F455" s="50"/>
+      <c r="F455" s="41"/>
       <c r="G455" s="8" t="s">
         <v>858</v>
       </c>
@@ -15032,7 +14988,7 @@
       <c r="E456" s="34" t="s">
         <v>859</v>
       </c>
-      <c r="F456" s="50"/>
+      <c r="F456" s="41"/>
       <c r="G456" s="8" t="s">
         <v>860</v>
       </c>
@@ -15053,7 +15009,7 @@
       <c r="E457" s="34" t="s">
         <v>861</v>
       </c>
-      <c r="F457" s="50"/>
+      <c r="F457" s="41"/>
       <c r="G457" s="8" t="s">
         <v>862</v>
       </c>
@@ -15074,7 +15030,7 @@
       <c r="E458" s="34" t="s">
         <v>863</v>
       </c>
-      <c r="F458" s="50"/>
+      <c r="F458" s="41"/>
       <c r="G458" s="8" t="s">
         <v>864</v>
       </c>
@@ -15095,7 +15051,7 @@
       <c r="E459" s="34" t="s">
         <v>865</v>
       </c>
-      <c r="F459" s="50"/>
+      <c r="F459" s="41"/>
       <c r="G459" s="8" t="s">
         <v>866</v>
       </c>
@@ -15116,7 +15072,7 @@
       <c r="E460" s="34" t="s">
         <v>545</v>
       </c>
-      <c r="F460" s="50"/>
+      <c r="F460" s="41"/>
       <c r="G460" s="8" t="s">
         <v>867</v>
       </c>
@@ -15137,7 +15093,7 @@
       <c r="E461" s="34" t="s">
         <v>547</v>
       </c>
-      <c r="F461" s="50"/>
+      <c r="F461" s="41"/>
       <c r="G461" s="8" t="s">
         <v>868</v>
       </c>
@@ -15158,7 +15114,7 @@
       <c r="E462" s="34" t="s">
         <v>869</v>
       </c>
-      <c r="F462" s="50"/>
+      <c r="F462" s="41"/>
       <c r="G462" s="8" t="s">
         <v>870</v>
       </c>
@@ -15176,8 +15132,8 @@
       <c r="D463" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E463" s="39"/>
-      <c r="F463" s="46" t="s">
+      <c r="E463" s="41"/>
+      <c r="F463" s="34" t="s">
         <v>152</v>
       </c>
       <c r="G463" s="8" t="s">
@@ -15200,7 +15156,7 @@
       <c r="E464" s="34" t="s">
         <v>872</v>
       </c>
-      <c r="F464" s="50"/>
+      <c r="F464" s="41"/>
       <c r="G464" s="8" t="s">
         <v>873</v>
       </c>
@@ -15221,7 +15177,7 @@
       <c r="E465" s="34" t="s">
         <v>874</v>
       </c>
-      <c r="F465" s="50"/>
+      <c r="F465" s="41"/>
       <c r="G465" s="8" t="s">
         <v>875</v>
       </c>
@@ -15239,8 +15195,8 @@
       <c r="D466" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E466" s="39"/>
-      <c r="F466" s="46" t="s">
+      <c r="E466" s="41"/>
+      <c r="F466" s="34" t="s">
         <v>876</v>
       </c>
       <c r="G466" s="8" t="s">
@@ -15260,8 +15216,8 @@
       <c r="D467" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E467" s="39"/>
-      <c r="F467" s="46" t="s">
+      <c r="E467" s="41"/>
+      <c r="F467" s="34" t="s">
         <v>878</v>
       </c>
       <c r="G467" s="8" t="s">
@@ -15284,7 +15240,7 @@
       <c r="E468" s="34" t="s">
         <v>881</v>
       </c>
-      <c r="F468" s="50"/>
+      <c r="F468" s="41"/>
       <c r="G468" s="8" t="s">
         <v>882</v>
       </c>
@@ -15305,7 +15261,7 @@
       <c r="E469" s="34" t="s">
         <v>883</v>
       </c>
-      <c r="F469" s="50"/>
+      <c r="F469" s="41"/>
       <c r="G469" s="8" t="s">
         <v>884</v>
       </c>
@@ -15323,8 +15279,8 @@
       <c r="D470" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E470" s="39"/>
-      <c r="F470" s="46" t="s">
+      <c r="E470" s="41"/>
+      <c r="F470" s="34" t="s">
         <v>885</v>
       </c>
       <c r="G470" s="8" t="s">
@@ -15347,7 +15303,7 @@
       <c r="E471" s="34" t="s">
         <v>887</v>
       </c>
-      <c r="F471" s="50"/>
+      <c r="F471" s="41"/>
       <c r="G471" s="8" t="s">
         <v>888</v>
       </c>
@@ -15368,7 +15324,7 @@
       <c r="E472" s="34" t="s">
         <v>889</v>
       </c>
-      <c r="F472" s="50"/>
+      <c r="F472" s="41"/>
       <c r="G472" s="8" t="s">
         <v>890</v>
       </c>
@@ -15389,7 +15345,7 @@
       <c r="E473" s="34" t="s">
         <v>891</v>
       </c>
-      <c r="F473" s="50"/>
+      <c r="F473" s="41"/>
       <c r="G473" s="8" t="s">
         <v>892</v>
       </c>
@@ -15410,7 +15366,7 @@
       <c r="E474" s="34" t="s">
         <v>893</v>
       </c>
-      <c r="F474" s="50"/>
+      <c r="F474" s="41"/>
       <c r="G474" s="8" t="s">
         <v>894</v>
       </c>
@@ -15431,7 +15387,7 @@
       <c r="E475" s="34" t="s">
         <v>895</v>
       </c>
-      <c r="F475" s="50"/>
+      <c r="F475" s="41"/>
       <c r="G475" s="8" t="s">
         <v>896</v>
       </c>
@@ -15452,7 +15408,7 @@
       <c r="E476" s="34" t="s">
         <v>897</v>
       </c>
-      <c r="F476" s="50"/>
+      <c r="F476" s="41"/>
       <c r="G476" s="8" t="s">
         <v>898</v>
       </c>
@@ -15473,7 +15429,7 @@
       <c r="E477" s="34" t="s">
         <v>899</v>
       </c>
-      <c r="F477" s="50"/>
+      <c r="F477" s="41"/>
       <c r="G477" s="8" t="s">
         <v>900</v>
       </c>
@@ -15494,7 +15450,7 @@
       <c r="E478" s="34" t="s">
         <v>901</v>
       </c>
-      <c r="F478" s="50"/>
+      <c r="F478" s="41"/>
       <c r="G478" s="8" t="s">
         <v>902</v>
       </c>
@@ -15515,7 +15471,7 @@
       <c r="E479" s="34" t="s">
         <v>903</v>
       </c>
-      <c r="F479" s="50"/>
+      <c r="F479" s="41"/>
       <c r="G479" s="8" t="s">
         <v>904</v>
       </c>
@@ -15536,7 +15492,7 @@
       <c r="E480" s="34" t="s">
         <v>905</v>
       </c>
-      <c r="F480" s="50"/>
+      <c r="F480" s="41"/>
       <c r="G480" s="8" t="s">
         <v>906</v>
       </c>
@@ -15557,7 +15513,7 @@
       <c r="E481" s="34" t="s">
         <v>907</v>
       </c>
-      <c r="F481" s="50"/>
+      <c r="F481" s="41"/>
       <c r="G481" s="8" t="s">
         <v>908</v>
       </c>
@@ -15569,8 +15525,8 @@
         <v>72</v>
       </c>
       <c r="D482" s="22"/>
-      <c r="E482" s="40"/>
-      <c r="F482" s="51"/>
+      <c r="E482" s="42"/>
+      <c r="F482" s="42"/>
       <c r="G482" s="13" t="s">
         <v>73</v>
       </c>
@@ -15587,7 +15543,7 @@
       <c r="E483" s="37" t="s">
         <v>909</v>
       </c>
-      <c r="F483" s="48"/>
+      <c r="F483" s="38"/>
       <c r="G483" s="28" t="s">
         <v>910</v>
       </c>
@@ -15601,8 +15557,8 @@
       <c r="D484" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E484" s="38"/>
-      <c r="F484" s="49"/>
+      <c r="E484" s="39"/>
+      <c r="F484" s="40"/>
       <c r="G484" s="29"/>
     </row>
     <row r="485" spans="1:7">
@@ -15621,7 +15577,7 @@
       <c r="E485" s="34" t="s">
         <v>911</v>
       </c>
-      <c r="F485" s="49"/>
+      <c r="F485" s="40"/>
       <c r="G485" s="8" t="s">
         <v>912</v>
       </c>
@@ -15642,7 +15598,7 @@
       <c r="E486" s="34" t="s">
         <v>913</v>
       </c>
-      <c r="F486" s="49"/>
+      <c r="F486" s="40"/>
       <c r="G486" s="8" t="s">
         <v>914</v>
       </c>
@@ -15663,7 +15619,7 @@
       <c r="E487" s="34" t="s">
         <v>915</v>
       </c>
-      <c r="F487" s="49"/>
+      <c r="F487" s="40"/>
       <c r="G487" s="8" t="s">
         <v>916</v>
       </c>
@@ -15684,7 +15640,7 @@
       <c r="E488" s="34" t="s">
         <v>917</v>
       </c>
-      <c r="F488" s="49"/>
+      <c r="F488" s="40"/>
       <c r="G488" s="8" t="s">
         <v>918</v>
       </c>
@@ -15705,7 +15661,7 @@
       <c r="E489" s="34" t="s">
         <v>919</v>
       </c>
-      <c r="F489" s="49"/>
+      <c r="F489" s="40"/>
       <c r="G489" s="8" t="s">
         <v>920</v>
       </c>
@@ -15726,7 +15682,7 @@
       <c r="E490" s="34" t="s">
         <v>921</v>
       </c>
-      <c r="F490" s="49"/>
+      <c r="F490" s="40"/>
       <c r="G490" s="8" t="s">
         <v>922</v>
       </c>
@@ -15747,7 +15703,7 @@
       <c r="E491" s="34" t="s">
         <v>923</v>
       </c>
-      <c r="F491" s="49"/>
+      <c r="F491" s="40"/>
       <c r="G491" s="8" t="s">
         <v>924</v>
       </c>
@@ -15768,7 +15724,7 @@
       <c r="E492" s="34" t="s">
         <v>925</v>
       </c>
-      <c r="F492" s="49"/>
+      <c r="F492" s="40"/>
       <c r="G492" s="8" t="s">
         <v>926</v>
       </c>
@@ -15789,7 +15745,7 @@
       <c r="E493" s="34" t="s">
         <v>927</v>
       </c>
-      <c r="F493" s="49"/>
+      <c r="F493" s="40"/>
       <c r="G493" s="8" t="s">
         <v>928</v>
       </c>
@@ -15810,7 +15766,7 @@
       <c r="E494" s="34" t="s">
         <v>929</v>
       </c>
-      <c r="F494" s="49"/>
+      <c r="F494" s="40"/>
       <c r="G494" s="8" t="s">
         <v>930</v>
       </c>
@@ -15831,7 +15787,7 @@
       <c r="E495" s="34" t="s">
         <v>931</v>
       </c>
-      <c r="F495" s="49"/>
+      <c r="F495" s="40"/>
       <c r="G495" s="8" t="s">
         <v>932</v>
       </c>
@@ -15852,7 +15808,7 @@
       <c r="E496" s="34" t="s">
         <v>933</v>
       </c>
-      <c r="F496" s="49"/>
+      <c r="F496" s="40"/>
       <c r="G496" s="8" t="s">
         <v>934</v>
       </c>
@@ -15873,7 +15829,7 @@
       <c r="E497" s="34" t="s">
         <v>935</v>
       </c>
-      <c r="F497" s="49"/>
+      <c r="F497" s="40"/>
       <c r="G497" s="8" t="s">
         <v>936</v>
       </c>
@@ -15894,7 +15850,7 @@
       <c r="E498" s="34" t="s">
         <v>937</v>
       </c>
-      <c r="F498" s="49"/>
+      <c r="F498" s="40"/>
       <c r="G498" s="8" t="s">
         <v>938</v>
       </c>
@@ -15915,7 +15871,7 @@
       <c r="E499" s="34" t="s">
         <v>939</v>
       </c>
-      <c r="F499" s="49"/>
+      <c r="F499" s="40"/>
       <c r="G499" s="8" t="s">
         <v>940</v>
       </c>
@@ -15936,7 +15892,7 @@
       <c r="E500" s="34" t="s">
         <v>941</v>
       </c>
-      <c r="F500" s="49"/>
+      <c r="F500" s="40"/>
       <c r="G500" s="8" t="s">
         <v>942</v>
       </c>
@@ -15957,7 +15913,7 @@
       <c r="E501" s="34" t="s">
         <v>943</v>
       </c>
-      <c r="F501" s="49"/>
+      <c r="F501" s="40"/>
       <c r="G501" s="8" t="s">
         <v>944</v>
       </c>
@@ -15978,7 +15934,7 @@
       <c r="E502" s="34" t="s">
         <v>945</v>
       </c>
-      <c r="F502" s="49"/>
+      <c r="F502" s="40"/>
       <c r="G502" s="8" t="s">
         <v>946</v>
       </c>
@@ -15999,7 +15955,7 @@
       <c r="E503" s="34" t="s">
         <v>947</v>
       </c>
-      <c r="F503" s="49"/>
+      <c r="F503" s="40"/>
       <c r="G503" s="8" t="s">
         <v>948</v>
       </c>
@@ -16020,7 +15976,7 @@
       <c r="E504" s="34" t="s">
         <v>949</v>
       </c>
-      <c r="F504" s="49"/>
+      <c r="F504" s="40"/>
       <c r="G504" s="8" t="s">
         <v>950</v>
       </c>
@@ -16041,7 +15997,7 @@
       <c r="E505" s="34" t="s">
         <v>951</v>
       </c>
-      <c r="F505" s="49"/>
+      <c r="F505" s="40"/>
       <c r="G505" s="8" t="s">
         <v>952</v>
       </c>
@@ -16062,7 +16018,7 @@
       <c r="E506" s="34" t="s">
         <v>953</v>
       </c>
-      <c r="F506" s="49"/>
+      <c r="F506" s="40"/>
       <c r="G506" s="8" t="s">
         <v>954</v>
       </c>
@@ -16083,7 +16039,7 @@
       <c r="E507" s="34" t="s">
         <v>955</v>
       </c>
-      <c r="F507" s="49"/>
+      <c r="F507" s="40"/>
       <c r="G507" s="8" t="s">
         <v>956</v>
       </c>
@@ -16104,7 +16060,7 @@
       <c r="E508" s="34" t="s">
         <v>957</v>
       </c>
-      <c r="F508" s="49"/>
+      <c r="F508" s="40"/>
       <c r="G508" s="8" t="s">
         <v>958</v>
       </c>
@@ -16125,7 +16081,7 @@
       <c r="E509" s="34" t="s">
         <v>959</v>
       </c>
-      <c r="F509" s="49"/>
+      <c r="F509" s="40"/>
       <c r="G509" s="8" t="s">
         <v>960</v>
       </c>
@@ -16146,7 +16102,7 @@
       <c r="E510" s="34" t="s">
         <v>961</v>
       </c>
-      <c r="F510" s="49"/>
+      <c r="F510" s="40"/>
       <c r="G510" s="8" t="s">
         <v>962</v>
       </c>
@@ -16167,7 +16123,7 @@
       <c r="E511" s="34" t="s">
         <v>963</v>
       </c>
-      <c r="F511" s="49"/>
+      <c r="F511" s="40"/>
       <c r="G511" s="8" t="s">
         <v>964</v>
       </c>
@@ -16188,7 +16144,7 @@
       <c r="E512" s="34" t="s">
         <v>965</v>
       </c>
-      <c r="F512" s="49"/>
+      <c r="F512" s="40"/>
       <c r="G512" s="8" t="s">
         <v>966</v>
       </c>
@@ -16209,7 +16165,7 @@
       <c r="E513" s="34" t="s">
         <v>967</v>
       </c>
-      <c r="F513" s="49"/>
+      <c r="F513" s="40"/>
       <c r="G513" s="8" t="s">
         <v>968</v>
       </c>
@@ -16230,7 +16186,7 @@
       <c r="E514" s="34" t="s">
         <v>969</v>
       </c>
-      <c r="F514" s="49"/>
+      <c r="F514" s="40"/>
       <c r="G514" s="8" t="s">
         <v>970</v>
       </c>
@@ -16251,7 +16207,7 @@
       <c r="E515" s="34" t="s">
         <v>971</v>
       </c>
-      <c r="F515" s="49"/>
+      <c r="F515" s="40"/>
       <c r="G515" s="8" t="s">
         <v>972</v>
       </c>
@@ -16272,7 +16228,7 @@
       <c r="E516" s="34" t="s">
         <v>973</v>
       </c>
-      <c r="F516" s="49"/>
+      <c r="F516" s="40"/>
       <c r="G516" s="8" t="s">
         <v>974</v>
       </c>
@@ -16293,7 +16249,7 @@
       <c r="E517" s="34" t="s">
         <v>923</v>
       </c>
-      <c r="F517" s="49"/>
+      <c r="F517" s="40"/>
       <c r="G517" s="8" t="s">
         <v>975</v>
       </c>
@@ -16314,7 +16270,7 @@
       <c r="E518" s="34" t="s">
         <v>925</v>
       </c>
-      <c r="F518" s="49"/>
+      <c r="F518" s="40"/>
       <c r="G518" s="8" t="s">
         <v>976</v>
       </c>
@@ -16335,7 +16291,7 @@
       <c r="E519" s="34" t="s">
         <v>977</v>
       </c>
-      <c r="F519" s="49"/>
+      <c r="F519" s="40"/>
       <c r="G519" s="8" t="s">
         <v>978</v>
       </c>
@@ -16356,7 +16312,7 @@
       <c r="E520" s="34" t="s">
         <v>979</v>
       </c>
-      <c r="F520" s="49"/>
+      <c r="F520" s="40"/>
       <c r="G520" s="8" t="s">
         <v>980</v>
       </c>
@@ -16377,7 +16333,7 @@
       <c r="E521" s="34" t="s">
         <v>981</v>
       </c>
-      <c r="F521" s="49"/>
+      <c r="F521" s="40"/>
       <c r="G521" s="8" t="s">
         <v>982</v>
       </c>
@@ -16398,7 +16354,7 @@
       <c r="E522" s="34" t="s">
         <v>983</v>
       </c>
-      <c r="F522" s="49"/>
+      <c r="F522" s="40"/>
       <c r="G522" s="8" t="s">
         <v>984</v>
       </c>
@@ -16419,7 +16375,7 @@
       <c r="E523" s="34" t="s">
         <v>963</v>
       </c>
-      <c r="F523" s="49"/>
+      <c r="F523" s="40"/>
       <c r="G523" s="8" t="s">
         <v>985</v>
       </c>
@@ -16440,7 +16396,7 @@
       <c r="E524" s="34" t="s">
         <v>965</v>
       </c>
-      <c r="F524" s="49"/>
+      <c r="F524" s="40"/>
       <c r="G524" s="8" t="s">
         <v>986</v>
       </c>
@@ -16461,7 +16417,7 @@
       <c r="E525" s="34" t="s">
         <v>987</v>
       </c>
-      <c r="F525" s="49"/>
+      <c r="F525" s="40"/>
       <c r="G525" s="8" t="s">
         <v>988</v>
       </c>
@@ -16473,8 +16429,8 @@
         <v>72</v>
       </c>
       <c r="D526" s="22"/>
-      <c r="E526" s="40"/>
-      <c r="F526" s="53"/>
+      <c r="E526" s="42"/>
+      <c r="F526" s="44"/>
       <c r="G526" s="13" t="s">
         <v>73</v>
       </c>
@@ -16491,7 +16447,7 @@
       <c r="E527" s="37" t="s">
         <v>989</v>
       </c>
-      <c r="F527" s="48"/>
+      <c r="F527" s="38"/>
       <c r="G527" s="28" t="s">
         <v>990</v>
       </c>
@@ -16505,8 +16461,8 @@
       <c r="D528" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E528" s="38"/>
-      <c r="F528" s="49"/>
+      <c r="E528" s="39"/>
+      <c r="F528" s="40"/>
       <c r="G528" s="29"/>
     </row>
     <row r="529" spans="1:7">
@@ -16525,7 +16481,7 @@
       <c r="E529" s="34" t="s">
         <v>991</v>
       </c>
-      <c r="F529" s="49"/>
+      <c r="F529" s="40"/>
       <c r="G529" s="8" t="s">
         <v>992</v>
       </c>
@@ -16546,7 +16502,7 @@
       <c r="E530" s="34" t="s">
         <v>993</v>
       </c>
-      <c r="F530" s="49"/>
+      <c r="F530" s="40"/>
       <c r="G530" s="8" t="s">
         <v>994</v>
       </c>
@@ -16567,7 +16523,7 @@
       <c r="E531" s="34" t="s">
         <v>995</v>
       </c>
-      <c r="F531" s="49"/>
+      <c r="F531" s="40"/>
       <c r="G531" s="8" t="s">
         <v>996</v>
       </c>
@@ -16588,7 +16544,7 @@
       <c r="E532" s="34" t="s">
         <v>997</v>
       </c>
-      <c r="F532" s="49"/>
+      <c r="F532" s="40"/>
       <c r="G532" s="8" t="s">
         <v>998</v>
       </c>
@@ -16609,7 +16565,7 @@
       <c r="E533" s="34" t="s">
         <v>999</v>
       </c>
-      <c r="F533" s="49"/>
+      <c r="F533" s="40"/>
       <c r="G533" s="8" t="s">
         <v>1000</v>
       </c>
@@ -16630,7 +16586,7 @@
       <c r="E534" s="34" t="s">
         <v>1001</v>
       </c>
-      <c r="F534" s="49"/>
+      <c r="F534" s="40"/>
       <c r="G534" s="8" t="s">
         <v>1002</v>
       </c>
@@ -16651,7 +16607,7 @@
       <c r="E535" s="34" t="s">
         <v>1003</v>
       </c>
-      <c r="F535" s="49"/>
+      <c r="F535" s="40"/>
       <c r="G535" s="8" t="s">
         <v>1004</v>
       </c>
@@ -16672,7 +16628,7 @@
       <c r="E536" s="34" t="s">
         <v>1005</v>
       </c>
-      <c r="F536" s="49"/>
+      <c r="F536" s="40"/>
       <c r="G536" s="8" t="s">
         <v>1006</v>
       </c>
@@ -16693,7 +16649,7 @@
       <c r="E537" s="34" t="s">
         <v>1007</v>
       </c>
-      <c r="F537" s="49"/>
+      <c r="F537" s="40"/>
       <c r="G537" s="8" t="s">
         <v>1008</v>
       </c>
@@ -16714,7 +16670,7 @@
       <c r="E538" s="34" t="s">
         <v>1009</v>
       </c>
-      <c r="F538" s="49"/>
+      <c r="F538" s="40"/>
       <c r="G538" s="8" t="s">
         <v>1010</v>
       </c>
@@ -16735,7 +16691,7 @@
       <c r="E539" s="34" t="s">
         <v>1011</v>
       </c>
-      <c r="F539" s="49"/>
+      <c r="F539" s="40"/>
       <c r="G539" s="8" t="s">
         <v>1012</v>
       </c>
@@ -16756,7 +16712,7 @@
       <c r="E540" s="34" t="s">
         <v>1013</v>
       </c>
-      <c r="F540" s="49"/>
+      <c r="F540" s="40"/>
       <c r="G540" s="8" t="s">
         <v>1014</v>
       </c>
@@ -16777,7 +16733,7 @@
       <c r="E541" s="34" t="s">
         <v>1015</v>
       </c>
-      <c r="F541" s="49"/>
+      <c r="F541" s="40"/>
       <c r="G541" s="8" t="s">
         <v>1016</v>
       </c>
@@ -16798,7 +16754,7 @@
       <c r="E542" s="34" t="s">
         <v>1017</v>
       </c>
-      <c r="F542" s="49"/>
+      <c r="F542" s="40"/>
       <c r="G542" s="8" t="s">
         <v>1018</v>
       </c>
@@ -16819,7 +16775,7 @@
       <c r="E543" s="34" t="s">
         <v>1019</v>
       </c>
-      <c r="F543" s="49"/>
+      <c r="F543" s="40"/>
       <c r="G543" s="8" t="s">
         <v>1020</v>
       </c>
@@ -16840,7 +16796,7 @@
       <c r="E544" s="34" t="s">
         <v>1021</v>
       </c>
-      <c r="F544" s="49"/>
+      <c r="F544" s="40"/>
       <c r="G544" s="8" t="s">
         <v>1022</v>
       </c>
@@ -16861,7 +16817,7 @@
       <c r="E545" s="34" t="s">
         <v>1023</v>
       </c>
-      <c r="F545" s="49"/>
+      <c r="F545" s="40"/>
       <c r="G545" s="8" t="s">
         <v>1024</v>
       </c>
@@ -16882,7 +16838,7 @@
       <c r="E546" s="34" t="s">
         <v>1025</v>
       </c>
-      <c r="F546" s="49"/>
+      <c r="F546" s="40"/>
       <c r="G546" s="8" t="s">
         <v>1026</v>
       </c>
@@ -16903,7 +16859,7 @@
       <c r="E547" s="34" t="s">
         <v>1027</v>
       </c>
-      <c r="F547" s="49"/>
+      <c r="F547" s="40"/>
       <c r="G547" s="8" t="s">
         <v>1028</v>
       </c>
@@ -16924,7 +16880,7 @@
       <c r="E548" s="34" t="s">
         <v>1029</v>
       </c>
-      <c r="F548" s="49"/>
+      <c r="F548" s="40"/>
       <c r="G548" s="8" t="s">
         <v>1030</v>
       </c>
@@ -16945,7 +16901,7 @@
       <c r="E549" s="34" t="s">
         <v>895</v>
       </c>
-      <c r="F549" s="49"/>
+      <c r="F549" s="40"/>
       <c r="G549" s="8" t="s">
         <v>1031</v>
       </c>
@@ -16966,7 +16922,7 @@
       <c r="E550" s="34" t="s">
         <v>897</v>
       </c>
-      <c r="F550" s="49"/>
+      <c r="F550" s="40"/>
       <c r="G550" s="8" t="s">
         <v>1032</v>
       </c>
@@ -16987,7 +16943,7 @@
       <c r="E551" s="34" t="s">
         <v>1033</v>
       </c>
-      <c r="F551" s="49"/>
+      <c r="F551" s="40"/>
       <c r="G551" s="8" t="s">
         <v>1034</v>
       </c>
@@ -17008,7 +16964,7 @@
       <c r="E552" s="34" t="s">
         <v>1035</v>
       </c>
-      <c r="F552" s="49"/>
+      <c r="F552" s="40"/>
       <c r="G552" s="8" t="s">
         <v>1036</v>
       </c>
@@ -17029,7 +16985,7 @@
       <c r="E553" s="34" t="s">
         <v>1037</v>
       </c>
-      <c r="F553" s="49"/>
+      <c r="F553" s="40"/>
       <c r="G553" s="8" t="s">
         <v>1038</v>
       </c>
@@ -17050,7 +17006,7 @@
       <c r="E554" s="34" t="s">
         <v>1039</v>
       </c>
-      <c r="F554" s="49"/>
+      <c r="F554" s="40"/>
       <c r="G554" s="8" t="s">
         <v>1040</v>
       </c>
@@ -17071,7 +17027,7 @@
       <c r="E555" s="34" t="s">
         <v>927</v>
       </c>
-      <c r="F555" s="49"/>
+      <c r="F555" s="40"/>
       <c r="G555" s="8" t="s">
         <v>1041</v>
       </c>
@@ -17092,7 +17048,7 @@
       <c r="E556" s="34" t="s">
         <v>929</v>
       </c>
-      <c r="F556" s="49"/>
+      <c r="F556" s="40"/>
       <c r="G556" s="8" t="s">
         <v>1042</v>
       </c>
@@ -17113,7 +17069,7 @@
       <c r="E557" s="34" t="s">
         <v>1043</v>
       </c>
-      <c r="F557" s="49"/>
+      <c r="F557" s="40"/>
       <c r="G557" s="8" t="s">
         <v>1044</v>
       </c>
@@ -17134,7 +17090,7 @@
       <c r="E558" s="34" t="s">
         <v>1045</v>
       </c>
-      <c r="F558" s="49"/>
+      <c r="F558" s="40"/>
       <c r="G558" s="8" t="s">
         <v>1046</v>
       </c>
@@ -17155,7 +17111,7 @@
       <c r="E559" s="34" t="s">
         <v>1047</v>
       </c>
-      <c r="F559" s="49"/>
+      <c r="F559" s="40"/>
       <c r="G559" s="8" t="s">
         <v>1048</v>
       </c>
@@ -17176,7 +17132,7 @@
       <c r="E560" s="34" t="s">
         <v>1049</v>
       </c>
-      <c r="F560" s="49"/>
+      <c r="F560" s="40"/>
       <c r="G560" s="8" t="s">
         <v>1050</v>
       </c>
@@ -17197,7 +17153,7 @@
       <c r="E561" s="34" t="s">
         <v>963</v>
       </c>
-      <c r="F561" s="49"/>
+      <c r="F561" s="40"/>
       <c r="G561" s="8" t="s">
         <v>1051</v>
       </c>
@@ -17218,7 +17174,7 @@
       <c r="E562" s="34" t="s">
         <v>965</v>
       </c>
-      <c r="F562" s="49"/>
+      <c r="F562" s="40"/>
       <c r="G562" s="8" t="s">
         <v>1052</v>
       </c>
@@ -17239,7 +17195,7 @@
       <c r="E563" s="34" t="s">
         <v>927</v>
       </c>
-      <c r="F563" s="49"/>
+      <c r="F563" s="40"/>
       <c r="G563" s="8" t="s">
         <v>1053</v>
       </c>
@@ -17260,7 +17216,7 @@
       <c r="E564" s="34" t="s">
         <v>929</v>
       </c>
-      <c r="F564" s="49"/>
+      <c r="F564" s="40"/>
       <c r="G564" s="8" t="s">
         <v>1054</v>
       </c>
@@ -17281,7 +17237,7 @@
       <c r="E565" s="34" t="s">
         <v>1055</v>
       </c>
-      <c r="F565" s="49"/>
+      <c r="F565" s="40"/>
       <c r="G565" s="8" t="s">
         <v>1056</v>
       </c>
@@ -17302,7 +17258,7 @@
       <c r="E566" s="34" t="s">
         <v>1057</v>
       </c>
-      <c r="F566" s="49"/>
+      <c r="F566" s="40"/>
       <c r="G566" s="8" t="s">
         <v>1058</v>
       </c>
@@ -17323,7 +17279,7 @@
       <c r="E567" s="34" t="s">
         <v>1059</v>
       </c>
-      <c r="F567" s="49"/>
+      <c r="F567" s="40"/>
       <c r="G567" s="8" t="s">
         <v>1060</v>
       </c>
@@ -17344,7 +17300,7 @@
       <c r="E568" s="34" t="s">
         <v>1061</v>
       </c>
-      <c r="F568" s="49"/>
+      <c r="F568" s="40"/>
       <c r="G568" s="8" t="s">
         <v>1062</v>
       </c>
@@ -17365,7 +17321,7 @@
       <c r="E569" s="34" t="s">
         <v>1063</v>
       </c>
-      <c r="F569" s="49"/>
+      <c r="F569" s="40"/>
       <c r="G569" s="8" t="s">
         <v>1064</v>
       </c>
@@ -17377,8 +17333,8 @@
         <v>72</v>
       </c>
       <c r="D570" s="22"/>
-      <c r="E570" s="40"/>
-      <c r="F570" s="53"/>
+      <c r="E570" s="42"/>
+      <c r="F570" s="44"/>
       <c r="G570" s="13" t="s">
         <v>73</v>
       </c>
@@ -17395,7 +17351,7 @@
       <c r="E571" s="37" t="s">
         <v>1065</v>
       </c>
-      <c r="F571" s="48"/>
+      <c r="F571" s="38"/>
       <c r="G571" s="28" t="s">
         <v>1066</v>
       </c>
@@ -17409,8 +17365,8 @@
       <c r="D572" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E572" s="38"/>
-      <c r="F572" s="49"/>
+      <c r="E572" s="39"/>
+      <c r="F572" s="40"/>
       <c r="G572" s="29"/>
     </row>
     <row r="573" spans="1:7">
@@ -17429,7 +17385,7 @@
       <c r="E573" s="34" t="s">
         <v>923</v>
       </c>
-      <c r="F573" s="49"/>
+      <c r="F573" s="40"/>
       <c r="G573" s="8" t="s">
         <v>1067</v>
       </c>
@@ -17450,7 +17406,7 @@
       <c r="E574" s="34" t="s">
         <v>925</v>
       </c>
-      <c r="F574" s="49"/>
+      <c r="F574" s="40"/>
       <c r="G574" s="8" t="s">
         <v>1068</v>
       </c>
@@ -17471,7 +17427,7 @@
       <c r="E575" s="34" t="s">
         <v>959</v>
       </c>
-      <c r="F575" s="49"/>
+      <c r="F575" s="40"/>
       <c r="G575" s="8" t="s">
         <v>1069</v>
       </c>
@@ -17492,7 +17448,7 @@
       <c r="E576" s="34" t="s">
         <v>961</v>
       </c>
-      <c r="F576" s="49"/>
+      <c r="F576" s="40"/>
       <c r="G576" s="8" t="s">
         <v>1070</v>
       </c>
@@ -17513,7 +17469,7 @@
       <c r="E577" s="34" t="s">
         <v>1071</v>
       </c>
-      <c r="F577" s="49"/>
+      <c r="F577" s="40"/>
       <c r="G577" s="8" t="s">
         <v>1072</v>
       </c>
@@ -17534,7 +17490,7 @@
       <c r="E578" s="34" t="s">
         <v>1073</v>
       </c>
-      <c r="F578" s="49"/>
+      <c r="F578" s="40"/>
       <c r="G578" s="8" t="s">
         <v>1074</v>
       </c>
@@ -17555,7 +17511,7 @@
       <c r="E579" s="34" t="s">
         <v>1075</v>
       </c>
-      <c r="F579" s="49"/>
+      <c r="F579" s="40"/>
       <c r="G579" s="8" t="s">
         <v>1076</v>
       </c>
@@ -17576,7 +17532,7 @@
       <c r="E580" s="34" t="s">
         <v>1077</v>
       </c>
-      <c r="F580" s="49"/>
+      <c r="F580" s="40"/>
       <c r="G580" s="8" t="s">
         <v>1078</v>
       </c>
@@ -17597,7 +17553,7 @@
       <c r="E581" s="34" t="s">
         <v>1079</v>
       </c>
-      <c r="F581" s="49"/>
+      <c r="F581" s="40"/>
       <c r="G581" s="8" t="s">
         <v>1080</v>
       </c>
@@ -17618,7 +17574,7 @@
       <c r="E582" s="34" t="s">
         <v>1081</v>
       </c>
-      <c r="F582" s="49"/>
+      <c r="F582" s="40"/>
       <c r="G582" s="8" t="s">
         <v>1082</v>
       </c>
@@ -17639,7 +17595,7 @@
       <c r="E583" s="34" t="s">
         <v>1083</v>
       </c>
-      <c r="F583" s="49"/>
+      <c r="F583" s="40"/>
       <c r="G583" s="8" t="s">
         <v>1084</v>
       </c>
@@ -17660,7 +17616,7 @@
       <c r="E584" s="34" t="s">
         <v>1085</v>
       </c>
-      <c r="F584" s="49"/>
+      <c r="F584" s="40"/>
       <c r="G584" s="8" t="s">
         <v>1086</v>
       </c>
@@ -17681,7 +17637,7 @@
       <c r="E585" s="34" t="s">
         <v>1087</v>
       </c>
-      <c r="F585" s="49"/>
+      <c r="F585" s="40"/>
       <c r="G585" s="8" t="s">
         <v>1088</v>
       </c>
@@ -17702,7 +17658,7 @@
       <c r="E586" s="34" t="s">
         <v>1089</v>
       </c>
-      <c r="F586" s="49"/>
+      <c r="F586" s="40"/>
       <c r="G586" s="8" t="s">
         <v>1090</v>
       </c>
@@ -17723,7 +17679,7 @@
       <c r="E587" s="34" t="s">
         <v>1091</v>
       </c>
-      <c r="F587" s="49"/>
+      <c r="F587" s="40"/>
       <c r="G587" s="8" t="s">
         <v>1092</v>
       </c>
@@ -17744,7 +17700,7 @@
       <c r="E588" s="34" t="s">
         <v>1093</v>
       </c>
-      <c r="F588" s="49"/>
+      <c r="F588" s="40"/>
       <c r="G588" s="8" t="s">
         <v>1094</v>
       </c>
@@ -17765,7 +17721,7 @@
       <c r="E589" s="34" t="s">
         <v>919</v>
       </c>
-      <c r="F589" s="49"/>
+      <c r="F589" s="40"/>
       <c r="G589" s="8" t="s">
         <v>1095</v>
       </c>
@@ -17786,7 +17742,7 @@
       <c r="E590" s="34" t="s">
         <v>921</v>
       </c>
-      <c r="F590" s="49"/>
+      <c r="F590" s="40"/>
       <c r="G590" s="8" t="s">
         <v>1096</v>
       </c>
@@ -17807,7 +17763,7 @@
       <c r="E591" s="34" t="s">
         <v>1097</v>
       </c>
-      <c r="F591" s="49"/>
+      <c r="F591" s="40"/>
       <c r="G591" s="8" t="s">
         <v>1098</v>
       </c>
@@ -17828,7 +17784,7 @@
       <c r="E592" s="34" t="s">
         <v>1099</v>
       </c>
-      <c r="F592" s="49"/>
+      <c r="F592" s="40"/>
       <c r="G592" s="8" t="s">
         <v>1100</v>
       </c>
@@ -17849,7 +17805,7 @@
       <c r="E593" s="34" t="s">
         <v>959</v>
       </c>
-      <c r="F593" s="49"/>
+      <c r="F593" s="40"/>
       <c r="G593" s="8" t="s">
         <v>1101</v>
       </c>
@@ -17870,7 +17826,7 @@
       <c r="E594" s="34" t="s">
         <v>961</v>
       </c>
-      <c r="F594" s="49"/>
+      <c r="F594" s="40"/>
       <c r="G594" s="8" t="s">
         <v>1102</v>
       </c>
@@ -17891,7 +17847,7 @@
       <c r="E595" s="34" t="s">
         <v>1103</v>
       </c>
-      <c r="F595" s="49"/>
+      <c r="F595" s="40"/>
       <c r="G595" s="8" t="s">
         <v>1104</v>
       </c>
@@ -17912,7 +17868,7 @@
       <c r="E596" s="34" t="s">
         <v>1105</v>
       </c>
-      <c r="F596" s="49"/>
+      <c r="F596" s="40"/>
       <c r="G596" s="8" t="s">
         <v>1106</v>
       </c>
@@ -17933,7 +17889,7 @@
       <c r="E597" s="34" t="s">
         <v>1107</v>
       </c>
-      <c r="F597" s="49"/>
+      <c r="F597" s="40"/>
       <c r="G597" s="8" t="s">
         <v>1108</v>
       </c>
@@ -17954,7 +17910,7 @@
       <c r="E598" s="34" t="s">
         <v>1109</v>
       </c>
-      <c r="F598" s="49"/>
+      <c r="F598" s="40"/>
       <c r="G598" s="8" t="s">
         <v>1110</v>
       </c>
@@ -17975,7 +17931,7 @@
       <c r="E599" s="34" t="s">
         <v>1111</v>
       </c>
-      <c r="F599" s="49"/>
+      <c r="F599" s="40"/>
       <c r="G599" s="8" t="s">
         <v>1112</v>
       </c>
@@ -17996,7 +17952,7 @@
       <c r="E600" s="34" t="s">
         <v>1113</v>
       </c>
-      <c r="F600" s="49"/>
+      <c r="F600" s="40"/>
       <c r="G600" s="8" t="s">
         <v>1114</v>
       </c>
@@ -18017,7 +17973,7 @@
       <c r="E601" s="34" t="s">
         <v>1115</v>
       </c>
-      <c r="F601" s="49"/>
+      <c r="F601" s="40"/>
       <c r="G601" s="8" t="s">
         <v>1116</v>
       </c>
@@ -18038,7 +17994,7 @@
       <c r="E602" s="34" t="s">
         <v>1117</v>
       </c>
-      <c r="F602" s="49"/>
+      <c r="F602" s="40"/>
       <c r="G602" s="8" t="s">
         <v>1118</v>
       </c>
@@ -18059,7 +18015,7 @@
       <c r="E603" s="34" t="s">
         <v>963</v>
       </c>
-      <c r="F603" s="49"/>
+      <c r="F603" s="40"/>
       <c r="G603" s="8" t="s">
         <v>1119</v>
       </c>
@@ -18080,7 +18036,7 @@
       <c r="E604" s="34" t="s">
         <v>965</v>
       </c>
-      <c r="F604" s="49"/>
+      <c r="F604" s="40"/>
       <c r="G604" s="8" t="s">
         <v>1120</v>
       </c>
@@ -18101,7 +18057,7 @@
       <c r="E605" s="34" t="s">
         <v>1121</v>
       </c>
-      <c r="F605" s="49"/>
+      <c r="F605" s="40"/>
       <c r="G605" s="8" t="s">
         <v>1122</v>
       </c>
@@ -18122,7 +18078,7 @@
       <c r="E606" s="34" t="s">
         <v>1123</v>
       </c>
-      <c r="F606" s="49"/>
+      <c r="F606" s="40"/>
       <c r="G606" s="8" t="s">
         <v>1124</v>
       </c>
@@ -18143,7 +18099,7 @@
       <c r="E607" s="34" t="s">
         <v>927</v>
       </c>
-      <c r="F607" s="49"/>
+      <c r="F607" s="40"/>
       <c r="G607" s="8" t="s">
         <v>1125</v>
       </c>
@@ -18164,7 +18120,7 @@
       <c r="E608" s="34" t="s">
         <v>929</v>
       </c>
-      <c r="F608" s="49"/>
+      <c r="F608" s="40"/>
       <c r="G608" s="8" t="s">
         <v>1126</v>
       </c>
@@ -18185,7 +18141,7 @@
       <c r="E609" s="34" t="s">
         <v>963</v>
       </c>
-      <c r="F609" s="49"/>
+      <c r="F609" s="40"/>
       <c r="G609" s="8" t="s">
         <v>1127</v>
       </c>
@@ -18206,7 +18162,7 @@
       <c r="E610" s="34" t="s">
         <v>965</v>
       </c>
-      <c r="F610" s="49"/>
+      <c r="F610" s="40"/>
       <c r="G610" s="8" t="s">
         <v>1128</v>
       </c>
@@ -18227,7 +18183,7 @@
       <c r="E611" s="34" t="s">
         <v>1129</v>
       </c>
-      <c r="F611" s="49"/>
+      <c r="F611" s="40"/>
       <c r="G611" s="8" t="s">
         <v>1130</v>
       </c>
@@ -18248,7 +18204,7 @@
       <c r="E612" s="34" t="s">
         <v>1131</v>
       </c>
-      <c r="F612" s="49"/>
+      <c r="F612" s="40"/>
       <c r="G612" s="8" t="s">
         <v>1132</v>
       </c>
@@ -18269,7 +18225,7 @@
       <c r="E613" s="34" t="s">
         <v>963</v>
       </c>
-      <c r="F613" s="49"/>
+      <c r="F613" s="40"/>
       <c r="G613" s="8" t="s">
         <v>1133</v>
       </c>
@@ -18281,8 +18237,8 @@
         <v>72</v>
       </c>
       <c r="D614" s="22"/>
-      <c r="E614" s="40"/>
-      <c r="F614" s="53"/>
+      <c r="E614" s="42"/>
+      <c r="F614" s="44"/>
       <c r="G614" s="13" t="s">
         <v>73</v>
       </c>
@@ -18299,7 +18255,7 @@
       <c r="E615" s="37" t="s">
         <v>965</v>
       </c>
-      <c r="F615" s="48"/>
+      <c r="F615" s="38"/>
       <c r="G615" s="28" t="s">
         <v>1134</v>
       </c>
@@ -18313,8 +18269,8 @@
       <c r="D616" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E616" s="38"/>
-      <c r="F616" s="49"/>
+      <c r="E616" s="39"/>
+      <c r="F616" s="40"/>
       <c r="G616" s="29"/>
     </row>
     <row r="617" spans="1:7">
@@ -18333,7 +18289,7 @@
       <c r="E617" s="34" t="s">
         <v>1135</v>
       </c>
-      <c r="F617" s="49"/>
+      <c r="F617" s="40"/>
       <c r="G617" s="8" t="s">
         <v>1136</v>
       </c>
@@ -18354,7 +18310,7 @@
       <c r="E618" s="34" t="s">
         <v>1137</v>
       </c>
-      <c r="F618" s="49"/>
+      <c r="F618" s="40"/>
       <c r="G618" s="8" t="s">
         <v>1138</v>
       </c>
@@ -18375,7 +18331,7 @@
       <c r="E619" s="34" t="s">
         <v>963</v>
       </c>
-      <c r="F619" s="49"/>
+      <c r="F619" s="40"/>
       <c r="G619" s="8" t="s">
         <v>1139</v>
       </c>
@@ -18396,7 +18352,7 @@
       <c r="E620" s="34" t="s">
         <v>965</v>
       </c>
-      <c r="F620" s="49"/>
+      <c r="F620" s="40"/>
       <c r="G620" s="8" t="s">
         <v>1140</v>
       </c>
@@ -18417,7 +18373,7 @@
       <c r="E621" s="34" t="s">
         <v>1141</v>
       </c>
-      <c r="F621" s="49"/>
+      <c r="F621" s="40"/>
       <c r="G621" s="8" t="s">
         <v>1142</v>
       </c>
@@ -18438,7 +18394,7 @@
       <c r="E622" s="34" t="s">
         <v>1143</v>
       </c>
-      <c r="F622" s="49"/>
+      <c r="F622" s="40"/>
       <c r="G622" s="8" t="s">
         <v>1144</v>
       </c>
@@ -18459,7 +18415,7 @@
       <c r="E623" s="34" t="s">
         <v>1043</v>
       </c>
-      <c r="F623" s="49"/>
+      <c r="F623" s="40"/>
       <c r="G623" s="8" t="s">
         <v>1145</v>
       </c>
@@ -18480,7 +18436,7 @@
       <c r="E624" s="34" t="s">
         <v>1045</v>
       </c>
-      <c r="F624" s="49"/>
+      <c r="F624" s="40"/>
       <c r="G624" s="8" t="s">
         <v>1146</v>
       </c>
@@ -18501,7 +18457,7 @@
       <c r="E625" s="34" t="s">
         <v>1147</v>
       </c>
-      <c r="F625" s="49"/>
+      <c r="F625" s="40"/>
       <c r="G625" s="8" t="s">
         <v>1148</v>
       </c>
@@ -18522,7 +18478,7 @@
       <c r="E626" s="34" t="s">
         <v>1149</v>
       </c>
-      <c r="F626" s="49"/>
+      <c r="F626" s="40"/>
       <c r="G626" s="8" t="s">
         <v>1150</v>
       </c>
@@ -18543,7 +18499,7 @@
       <c r="E627" s="34" t="s">
         <v>959</v>
       </c>
-      <c r="F627" s="49"/>
+      <c r="F627" s="40"/>
       <c r="G627" s="8" t="s">
         <v>1151</v>
       </c>
@@ -18564,7 +18520,7 @@
       <c r="E628" s="34" t="s">
         <v>961</v>
       </c>
-      <c r="F628" s="49"/>
+      <c r="F628" s="40"/>
       <c r="G628" s="8" t="s">
         <v>1152</v>
       </c>
@@ -18585,7 +18541,7 @@
       <c r="E629" s="34" t="s">
         <v>1153</v>
       </c>
-      <c r="F629" s="49"/>
+      <c r="F629" s="40"/>
       <c r="G629" s="8" t="s">
         <v>1154</v>
       </c>
@@ -18606,7 +18562,7 @@
       <c r="E630" s="34" t="s">
         <v>1155</v>
       </c>
-      <c r="F630" s="49"/>
+      <c r="F630" s="40"/>
       <c r="G630" s="8" t="s">
         <v>1156</v>
       </c>
@@ -18627,7 +18583,7 @@
       <c r="E631" s="34" t="s">
         <v>1157</v>
       </c>
-      <c r="F631" s="49"/>
+      <c r="F631" s="40"/>
       <c r="G631" s="8" t="s">
         <v>1158</v>
       </c>
@@ -18648,7 +18604,7 @@
       <c r="E632" s="34" t="s">
         <v>1159</v>
       </c>
-      <c r="F632" s="49"/>
+      <c r="F632" s="40"/>
       <c r="G632" s="8" t="s">
         <v>1160</v>
       </c>
@@ -18669,7 +18625,7 @@
       <c r="E633" s="34" t="s">
         <v>1161</v>
       </c>
-      <c r="F633" s="49"/>
+      <c r="F633" s="40"/>
       <c r="G633" s="8" t="s">
         <v>1162</v>
       </c>
@@ -18690,7 +18646,7 @@
       <c r="E634" s="34" t="s">
         <v>1163</v>
       </c>
-      <c r="F634" s="49"/>
+      <c r="F634" s="40"/>
       <c r="G634" s="8" t="s">
         <v>1164</v>
       </c>
@@ -18711,7 +18667,7 @@
       <c r="E635" s="34" t="s">
         <v>1043</v>
       </c>
-      <c r="F635" s="49"/>
+      <c r="F635" s="40"/>
       <c r="G635" s="8" t="s">
         <v>1165</v>
       </c>
@@ -18732,7 +18688,7 @@
       <c r="E636" s="34" t="s">
         <v>1045</v>
       </c>
-      <c r="F636" s="49"/>
+      <c r="F636" s="40"/>
       <c r="G636" s="8" t="s">
         <v>1166</v>
       </c>
@@ -18753,7 +18709,7 @@
       <c r="E637" s="34" t="s">
         <v>1167</v>
       </c>
-      <c r="F637" s="49"/>
+      <c r="F637" s="40"/>
       <c r="G637" s="8" t="s">
         <v>1168</v>
       </c>
@@ -18774,7 +18730,7 @@
       <c r="E638" s="34" t="s">
         <v>1169</v>
       </c>
-      <c r="F638" s="49"/>
+      <c r="F638" s="40"/>
       <c r="G638" s="8" t="s">
         <v>1170</v>
       </c>
@@ -18795,7 +18751,7 @@
       <c r="E639" s="34" t="s">
         <v>1171</v>
       </c>
-      <c r="F639" s="49"/>
+      <c r="F639" s="40"/>
       <c r="G639" s="8" t="s">
         <v>1172</v>
       </c>
@@ -18816,7 +18772,7 @@
       <c r="E640" s="34" t="s">
         <v>1173</v>
       </c>
-      <c r="F640" s="49"/>
+      <c r="F640" s="40"/>
       <c r="G640" s="8" t="s">
         <v>1174</v>
       </c>
@@ -18837,7 +18793,7 @@
       <c r="E641" s="34" t="s">
         <v>1167</v>
       </c>
-      <c r="F641" s="49"/>
+      <c r="F641" s="40"/>
       <c r="G641" s="8" t="s">
         <v>1175</v>
       </c>
@@ -18858,7 +18814,7 @@
       <c r="E642" s="34" t="s">
         <v>1169</v>
       </c>
-      <c r="F642" s="49"/>
+      <c r="F642" s="40"/>
       <c r="G642" s="8" t="s">
         <v>1176</v>
       </c>
@@ -18879,7 +18835,7 @@
       <c r="E643" s="34" t="s">
         <v>963</v>
       </c>
-      <c r="F643" s="49"/>
+      <c r="F643" s="40"/>
       <c r="G643" s="8" t="s">
         <v>1177</v>
       </c>
@@ -18900,7 +18856,7 @@
       <c r="E644" s="34" t="s">
         <v>965</v>
       </c>
-      <c r="F644" s="49"/>
+      <c r="F644" s="40"/>
       <c r="G644" s="8" t="s">
         <v>1178</v>
       </c>
@@ -18921,7 +18877,7 @@
       <c r="E645" s="34" t="s">
         <v>1179</v>
       </c>
-      <c r="F645" s="49"/>
+      <c r="F645" s="40"/>
       <c r="G645" s="8" t="s">
         <v>1180</v>
       </c>
@@ -18942,7 +18898,7 @@
       <c r="E646" s="34" t="s">
         <v>1181</v>
       </c>
-      <c r="F646" s="49"/>
+      <c r="F646" s="40"/>
       <c r="G646" s="8" t="s">
         <v>1182</v>
       </c>
@@ -18963,7 +18919,7 @@
       <c r="E647" s="34" t="s">
         <v>1183</v>
       </c>
-      <c r="F647" s="49"/>
+      <c r="F647" s="40"/>
       <c r="G647" s="8" t="s">
         <v>1184</v>
       </c>
@@ -18984,7 +18940,7 @@
       <c r="E648" s="34" t="s">
         <v>1185</v>
       </c>
-      <c r="F648" s="49"/>
+      <c r="F648" s="40"/>
       <c r="G648" s="8" t="s">
         <v>1186</v>
       </c>
@@ -19005,7 +18961,7 @@
       <c r="E649" s="34" t="s">
         <v>1187</v>
       </c>
-      <c r="F649" s="49"/>
+      <c r="F649" s="40"/>
       <c r="G649" s="8" t="s">
         <v>1188</v>
       </c>
@@ -19026,7 +18982,7 @@
       <c r="E650" s="34" t="s">
         <v>1189</v>
       </c>
-      <c r="F650" s="49"/>
+      <c r="F650" s="40"/>
       <c r="G650" s="8" t="s">
         <v>1190</v>
       </c>
@@ -19047,7 +19003,7 @@
       <c r="E651" s="34" t="s">
         <v>963</v>
       </c>
-      <c r="F651" s="49"/>
+      <c r="F651" s="40"/>
       <c r="G651" s="8" t="s">
         <v>1191</v>
       </c>
@@ -19068,7 +19024,7 @@
       <c r="E652" s="34" t="s">
         <v>965</v>
       </c>
-      <c r="F652" s="49"/>
+      <c r="F652" s="40"/>
       <c r="G652" s="8" t="s">
         <v>1192</v>
       </c>
@@ -19089,7 +19045,7 @@
       <c r="E653" s="34" t="s">
         <v>1193</v>
       </c>
-      <c r="F653" s="49"/>
+      <c r="F653" s="40"/>
       <c r="G653" s="8" t="s">
         <v>1194</v>
       </c>
@@ -19110,7 +19066,7 @@
       <c r="E654" s="34" t="s">
         <v>1195</v>
       </c>
-      <c r="F654" s="49"/>
+      <c r="F654" s="40"/>
       <c r="G654" s="8" t="s">
         <v>1196</v>
       </c>
@@ -19131,7 +19087,7 @@
       <c r="E655" s="34" t="s">
         <v>959</v>
       </c>
-      <c r="F655" s="49"/>
+      <c r="F655" s="40"/>
       <c r="G655" s="8" t="s">
         <v>1197</v>
       </c>
@@ -19152,7 +19108,7 @@
       <c r="E656" s="34" t="s">
         <v>961</v>
       </c>
-      <c r="F656" s="49"/>
+      <c r="F656" s="40"/>
       <c r="G656" s="8" t="s">
         <v>1198</v>
       </c>
@@ -19173,7 +19129,7 @@
       <c r="E657" s="34" t="s">
         <v>999</v>
       </c>
-      <c r="F657" s="49"/>
+      <c r="F657" s="40"/>
       <c r="G657" s="8" t="s">
         <v>1199</v>
       </c>
@@ -19185,8 +19141,8 @@
         <v>72</v>
       </c>
       <c r="D658" s="22"/>
-      <c r="E658" s="40"/>
-      <c r="F658" s="53"/>
+      <c r="E658" s="42"/>
+      <c r="F658" s="44"/>
       <c r="G658" s="13" t="s">
         <v>73</v>
       </c>
@@ -19203,7 +19159,7 @@
       <c r="E659" s="37" t="s">
         <v>1001</v>
       </c>
-      <c r="F659" s="48"/>
+      <c r="F659" s="38"/>
       <c r="G659" s="28" t="s">
         <v>1200</v>
       </c>
@@ -19217,8 +19173,8 @@
       <c r="D660" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E660" s="38"/>
-      <c r="F660" s="49"/>
+      <c r="E660" s="39"/>
+      <c r="F660" s="40"/>
       <c r="G660" s="29"/>
     </row>
     <row r="661" spans="1:7">
@@ -19237,7 +19193,7 @@
       <c r="E661" s="34" t="s">
         <v>1201</v>
       </c>
-      <c r="F661" s="49"/>
+      <c r="F661" s="40"/>
       <c r="G661" s="8" t="s">
         <v>1202</v>
       </c>
@@ -19258,7 +19214,7 @@
       <c r="E662" s="34" t="s">
         <v>1203</v>
       </c>
-      <c r="F662" s="49"/>
+      <c r="F662" s="40"/>
       <c r="G662" s="8" t="s">
         <v>1204</v>
       </c>
@@ -19279,7 +19235,7 @@
       <c r="E663" s="34" t="s">
         <v>1205</v>
       </c>
-      <c r="F663" s="49"/>
+      <c r="F663" s="40"/>
       <c r="G663" s="8" t="s">
         <v>1206</v>
       </c>
@@ -19300,7 +19256,7 @@
       <c r="E664" s="34" t="s">
         <v>1207</v>
       </c>
-      <c r="F664" s="49"/>
+      <c r="F664" s="40"/>
       <c r="G664" s="8" t="s">
         <v>1208</v>
       </c>
@@ -19321,7 +19277,7 @@
       <c r="E665" s="34" t="s">
         <v>959</v>
       </c>
-      <c r="F665" s="49"/>
+      <c r="F665" s="40"/>
       <c r="G665" s="8" t="s">
         <v>1209</v>
       </c>
@@ -19342,7 +19298,7 @@
       <c r="E666" s="34" t="s">
         <v>961</v>
       </c>
-      <c r="F666" s="49"/>
+      <c r="F666" s="40"/>
       <c r="G666" s="8" t="s">
         <v>1210</v>
       </c>
@@ -19363,7 +19319,7 @@
       <c r="E667" s="34" t="s">
         <v>963</v>
       </c>
-      <c r="F667" s="49"/>
+      <c r="F667" s="40"/>
       <c r="G667" s="8" t="s">
         <v>1211</v>
       </c>
@@ -19384,7 +19340,7 @@
       <c r="E668" s="34" t="s">
         <v>965</v>
       </c>
-      <c r="F668" s="49"/>
+      <c r="F668" s="40"/>
       <c r="G668" s="8" t="s">
         <v>1212</v>
       </c>
@@ -19405,7 +19361,7 @@
       <c r="E669" s="34" t="s">
         <v>943</v>
       </c>
-      <c r="F669" s="49"/>
+      <c r="F669" s="40"/>
       <c r="G669" s="8" t="s">
         <v>1213</v>
       </c>
@@ -19426,7 +19382,7 @@
       <c r="E670" s="34" t="s">
         <v>945</v>
       </c>
-      <c r="F670" s="49"/>
+      <c r="F670" s="40"/>
       <c r="G670" s="8" t="s">
         <v>1214</v>
       </c>
@@ -19447,7 +19403,7 @@
       <c r="E671" s="34" t="s">
         <v>1215</v>
       </c>
-      <c r="F671" s="49"/>
+      <c r="F671" s="40"/>
       <c r="G671" s="8" t="s">
         <v>1216</v>
       </c>
@@ -19468,7 +19424,7 @@
       <c r="E672" s="34" t="s">
         <v>1217</v>
       </c>
-      <c r="F672" s="49"/>
+      <c r="F672" s="40"/>
       <c r="G672" s="8" t="s">
         <v>1218</v>
       </c>
@@ -19489,7 +19445,7 @@
       <c r="E673" s="34" t="s">
         <v>963</v>
       </c>
-      <c r="F673" s="49"/>
+      <c r="F673" s="40"/>
       <c r="G673" s="8" t="s">
         <v>1219</v>
       </c>
@@ -19510,7 +19466,7 @@
       <c r="E674" s="34" t="s">
         <v>965</v>
       </c>
-      <c r="F674" s="49"/>
+      <c r="F674" s="40"/>
       <c r="G674" s="8" t="s">
         <v>1220</v>
       </c>
@@ -19531,7 +19487,7 @@
       <c r="E675" s="34" t="s">
         <v>963</v>
       </c>
-      <c r="F675" s="49"/>
+      <c r="F675" s="40"/>
       <c r="G675" s="8" t="s">
         <v>1221</v>
       </c>
@@ -19552,7 +19508,7 @@
       <c r="E676" s="34" t="s">
         <v>965</v>
       </c>
-      <c r="F676" s="49"/>
+      <c r="F676" s="40"/>
       <c r="G676" s="8" t="s">
         <v>1222</v>
       </c>
@@ -19573,7 +19529,7 @@
       <c r="E677" s="34" t="s">
         <v>1223</v>
       </c>
-      <c r="F677" s="49"/>
+      <c r="F677" s="40"/>
       <c r="G677" s="8" t="s">
         <v>1224</v>
       </c>
@@ -19594,7 +19550,7 @@
       <c r="E678" s="34" t="s">
         <v>1225</v>
       </c>
-      <c r="F678" s="49"/>
+      <c r="F678" s="40"/>
       <c r="G678" s="8" t="s">
         <v>1226</v>
       </c>
@@ -19615,7 +19571,7 @@
       <c r="E679" s="34" t="s">
         <v>1227</v>
       </c>
-      <c r="F679" s="49"/>
+      <c r="F679" s="40"/>
       <c r="G679" s="8" t="s">
         <v>1228</v>
       </c>
@@ -19636,7 +19592,7 @@
       <c r="E680" s="34" t="s">
         <v>1229</v>
       </c>
-      <c r="F680" s="49"/>
+      <c r="F680" s="40"/>
       <c r="G680" s="8" t="s">
         <v>1230</v>
       </c>
@@ -19657,7 +19613,7 @@
       <c r="E681" s="34" t="s">
         <v>927</v>
       </c>
-      <c r="F681" s="49"/>
+      <c r="F681" s="40"/>
       <c r="G681" s="8" t="s">
         <v>1231</v>
       </c>
@@ -19678,7 +19634,7 @@
       <c r="E682" s="34" t="s">
         <v>929</v>
       </c>
-      <c r="F682" s="49"/>
+      <c r="F682" s="40"/>
       <c r="G682" s="8" t="s">
         <v>1232</v>
       </c>
@@ -19699,7 +19655,7 @@
       <c r="E683" s="34" t="s">
         <v>1233</v>
       </c>
-      <c r="F683" s="49"/>
+      <c r="F683" s="40"/>
       <c r="G683" s="8" t="s">
         <v>1234</v>
       </c>
@@ -19720,7 +19676,7 @@
       <c r="E684" s="34" t="s">
         <v>1235</v>
       </c>
-      <c r="F684" s="49"/>
+      <c r="F684" s="40"/>
       <c r="G684" s="8" t="s">
         <v>1236</v>
       </c>
@@ -19741,7 +19697,7 @@
       <c r="E685" s="34" t="s">
         <v>1237</v>
       </c>
-      <c r="F685" s="49"/>
+      <c r="F685" s="40"/>
       <c r="G685" s="8" t="s">
         <v>1238</v>
       </c>
@@ -19762,7 +19718,7 @@
       <c r="E686" s="34" t="s">
         <v>1239</v>
       </c>
-      <c r="F686" s="49"/>
+      <c r="F686" s="40"/>
       <c r="G686" s="8" t="s">
         <v>1240</v>
       </c>
@@ -19783,7 +19739,7 @@
       <c r="E687" s="34" t="s">
         <v>1237</v>
       </c>
-      <c r="F687" s="49"/>
+      <c r="F687" s="40"/>
       <c r="G687" s="8" t="s">
         <v>1241</v>
       </c>
@@ -19804,7 +19760,7 @@
       <c r="E688" s="34" t="s">
         <v>1239</v>
       </c>
-      <c r="F688" s="49"/>
+      <c r="F688" s="40"/>
       <c r="G688" s="8" t="s">
         <v>1242</v>
       </c>
@@ -19825,7 +19781,7 @@
       <c r="E689" s="34" t="s">
         <v>1243</v>
       </c>
-      <c r="F689" s="49"/>
+      <c r="F689" s="40"/>
       <c r="G689" s="8" t="s">
         <v>1244</v>
       </c>
@@ -19846,7 +19802,7 @@
       <c r="E690" s="34" t="s">
         <v>1245</v>
       </c>
-      <c r="F690" s="49"/>
+      <c r="F690" s="40"/>
       <c r="G690" s="8" t="s">
         <v>1246</v>
       </c>
@@ -19867,7 +19823,7 @@
       <c r="E691" s="34" t="s">
         <v>1237</v>
       </c>
-      <c r="F691" s="49"/>
+      <c r="F691" s="40"/>
       <c r="G691" s="8" t="s">
         <v>1247</v>
       </c>
@@ -19888,7 +19844,7 @@
       <c r="E692" s="34" t="s">
         <v>1239</v>
       </c>
-      <c r="F692" s="49"/>
+      <c r="F692" s="40"/>
       <c r="G692" s="8" t="s">
         <v>1248</v>
       </c>
@@ -19909,7 +19865,7 @@
       <c r="E693" s="34" t="s">
         <v>1237</v>
       </c>
-      <c r="F693" s="49"/>
+      <c r="F693" s="40"/>
       <c r="G693" s="8" t="s">
         <v>1249</v>
       </c>
@@ -19930,7 +19886,7 @@
       <c r="E694" s="34" t="s">
         <v>1239</v>
       </c>
-      <c r="F694" s="49"/>
+      <c r="F694" s="40"/>
       <c r="G694" s="8" t="s">
         <v>1250</v>
       </c>
@@ -19951,7 +19907,7 @@
       <c r="E695" s="34" t="s">
         <v>1243</v>
       </c>
-      <c r="F695" s="49"/>
+      <c r="F695" s="40"/>
       <c r="G695" s="8" t="s">
         <v>1251</v>
       </c>
@@ -19972,7 +19928,7 @@
       <c r="E696" s="34" t="s">
         <v>1245</v>
       </c>
-      <c r="F696" s="49"/>
+      <c r="F696" s="40"/>
       <c r="G696" s="8" t="s">
         <v>1252</v>
       </c>
@@ -19993,7 +19949,7 @@
       <c r="E697" s="34" t="s">
         <v>1254</v>
       </c>
-      <c r="F697" s="49"/>
+      <c r="F697" s="40"/>
       <c r="G697" s="8" t="s">
         <v>1255</v>
       </c>
@@ -20014,7 +19970,7 @@
       <c r="E698" s="34" t="s">
         <v>1256</v>
       </c>
-      <c r="F698" s="49"/>
+      <c r="F698" s="40"/>
       <c r="G698" s="8" t="s">
         <v>1257</v>
       </c>
@@ -20035,7 +19991,7 @@
       <c r="E699" s="34" t="s">
         <v>1237</v>
       </c>
-      <c r="F699" s="49"/>
+      <c r="F699" s="40"/>
       <c r="G699" s="8" t="s">
         <v>1258</v>
       </c>
@@ -20056,7 +20012,7 @@
       <c r="E700" s="34" t="s">
         <v>1239</v>
       </c>
-      <c r="F700" s="49"/>
+      <c r="F700" s="40"/>
       <c r="G700" s="8" t="s">
         <v>1259</v>
       </c>
@@ -20077,7 +20033,7 @@
       <c r="E701" s="34" t="s">
         <v>1260</v>
       </c>
-      <c r="F701" s="49"/>
+      <c r="F701" s="40"/>
       <c r="G701" s="8" t="s">
         <v>1261</v>
       </c>
@@ -20089,8 +20045,8 @@
         <v>72</v>
       </c>
       <c r="D702" s="22"/>
-      <c r="E702" s="40"/>
-      <c r="F702" s="53"/>
+      <c r="E702" s="42"/>
+      <c r="F702" s="44"/>
       <c r="G702" s="13" t="s">
         <v>73</v>
       </c>
@@ -20107,7 +20063,7 @@
       <c r="E703" s="37" t="s">
         <v>1262</v>
       </c>
-      <c r="F703" s="48"/>
+      <c r="F703" s="38"/>
       <c r="G703" s="28" t="s">
         <v>1263</v>
       </c>
@@ -20121,8 +20077,8 @@
       <c r="D704" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E704" s="38"/>
-      <c r="F704" s="49"/>
+      <c r="E704" s="39"/>
+      <c r="F704" s="40"/>
       <c r="G704" s="29"/>
     </row>
     <row r="705" spans="1:7">
@@ -20141,7 +20097,7 @@
       <c r="E705" s="34" t="s">
         <v>1264</v>
       </c>
-      <c r="F705" s="49"/>
+      <c r="F705" s="40"/>
       <c r="G705" s="8" t="s">
         <v>1265</v>
       </c>
@@ -20162,7 +20118,7 @@
       <c r="E706" s="34" t="s">
         <v>1266</v>
       </c>
-      <c r="F706" s="49"/>
+      <c r="F706" s="40"/>
       <c r="G706" s="8" t="s">
         <v>1267</v>
       </c>
@@ -20183,7 +20139,7 @@
       <c r="E707" s="34" t="s">
         <v>1268</v>
       </c>
-      <c r="F707" s="49"/>
+      <c r="F707" s="40"/>
       <c r="G707" s="8" t="s">
         <v>1269</v>
       </c>
@@ -20204,7 +20160,7 @@
       <c r="E708" s="34" t="s">
         <v>1270</v>
       </c>
-      <c r="F708" s="49"/>
+      <c r="F708" s="40"/>
       <c r="G708" s="8" t="s">
         <v>1271</v>
       </c>
@@ -20225,7 +20181,7 @@
       <c r="E709" s="34" t="s">
         <v>1272</v>
       </c>
-      <c r="F709" s="49"/>
+      <c r="F709" s="40"/>
       <c r="G709" s="8" t="s">
         <v>1273</v>
       </c>
@@ -20246,7 +20202,7 @@
       <c r="E710" s="34" t="s">
         <v>1274</v>
       </c>
-      <c r="F710" s="49"/>
+      <c r="F710" s="40"/>
       <c r="G710" s="8" t="s">
         <v>1275</v>
       </c>
@@ -20267,7 +20223,7 @@
       <c r="E711" s="34" t="s">
         <v>1276</v>
       </c>
-      <c r="F711" s="49"/>
+      <c r="F711" s="40"/>
       <c r="G711" s="8" t="s">
         <v>1277</v>
       </c>
@@ -20288,7 +20244,7 @@
       <c r="E712" s="34" t="s">
         <v>1278</v>
       </c>
-      <c r="F712" s="49"/>
+      <c r="F712" s="40"/>
       <c r="G712" s="8" t="s">
         <v>1279</v>
       </c>
@@ -20309,7 +20265,7 @@
       <c r="E713" s="34" t="s">
         <v>1280</v>
       </c>
-      <c r="F713" s="49"/>
+      <c r="F713" s="40"/>
       <c r="G713" s="8" t="s">
         <v>1281</v>
       </c>
@@ -20330,7 +20286,7 @@
       <c r="E714" s="34" t="s">
         <v>1282</v>
       </c>
-      <c r="F714" s="49"/>
+      <c r="F714" s="40"/>
       <c r="G714" s="8" t="s">
         <v>1283</v>
       </c>
@@ -20351,7 +20307,7 @@
       <c r="E715" s="34" t="s">
         <v>1284</v>
       </c>
-      <c r="F715" s="49"/>
+      <c r="F715" s="40"/>
       <c r="G715" s="8" t="s">
         <v>1285</v>
       </c>
@@ -20372,7 +20328,7 @@
       <c r="E716" s="34" t="s">
         <v>1286</v>
       </c>
-      <c r="F716" s="49"/>
+      <c r="F716" s="40"/>
       <c r="G716" s="8" t="s">
         <v>1287</v>
       </c>
@@ -20393,7 +20349,7 @@
       <c r="E717" s="34" t="s">
         <v>1288</v>
       </c>
-      <c r="F717" s="49"/>
+      <c r="F717" s="40"/>
       <c r="G717" s="8" t="s">
         <v>1289</v>
       </c>
@@ -20414,7 +20370,7 @@
       <c r="E718" s="34" t="s">
         <v>1290</v>
       </c>
-      <c r="F718" s="49"/>
+      <c r="F718" s="40"/>
       <c r="G718" s="8" t="s">
         <v>1291</v>
       </c>
@@ -20435,7 +20391,7 @@
       <c r="E719" s="34" t="s">
         <v>1292</v>
       </c>
-      <c r="F719" s="49"/>
+      <c r="F719" s="40"/>
       <c r="G719" s="8" t="s">
         <v>1293</v>
       </c>
@@ -20456,7 +20412,7 @@
       <c r="E720" s="34" t="s">
         <v>1294</v>
       </c>
-      <c r="F720" s="49"/>
+      <c r="F720" s="40"/>
       <c r="G720" s="8" t="s">
         <v>1295</v>
       </c>
@@ -20477,7 +20433,7 @@
       <c r="E721" s="34" t="s">
         <v>1296</v>
       </c>
-      <c r="F721" s="49"/>
+      <c r="F721" s="40"/>
       <c r="G721" s="8" t="s">
         <v>1297</v>
       </c>
@@ -20498,7 +20454,7 @@
       <c r="E722" s="34" t="s">
         <v>1298</v>
       </c>
-      <c r="F722" s="49"/>
+      <c r="F722" s="40"/>
       <c r="G722" s="8" t="s">
         <v>1299</v>
       </c>
@@ -20519,7 +20475,7 @@
       <c r="E723" s="34" t="s">
         <v>1300</v>
       </c>
-      <c r="F723" s="49"/>
+      <c r="F723" s="40"/>
       <c r="G723" s="8" t="s">
         <v>1301</v>
       </c>
@@ -20540,7 +20496,7 @@
       <c r="E724" s="34" t="s">
         <v>1302</v>
       </c>
-      <c r="F724" s="49"/>
+      <c r="F724" s="40"/>
       <c r="G724" s="8" t="s">
         <v>1303</v>
       </c>
@@ -20561,7 +20517,7 @@
       <c r="E725" s="34" t="s">
         <v>1304</v>
       </c>
-      <c r="F725" s="49"/>
+      <c r="F725" s="40"/>
       <c r="G725" s="8" t="s">
         <v>1305</v>
       </c>
@@ -20582,7 +20538,7 @@
       <c r="E726" s="34" t="s">
         <v>1306</v>
       </c>
-      <c r="F726" s="49"/>
+      <c r="F726" s="40"/>
       <c r="G726" s="8" t="s">
         <v>1307</v>
       </c>
@@ -20603,7 +20559,7 @@
       <c r="E727" s="34" t="s">
         <v>1300</v>
       </c>
-      <c r="F727" s="49"/>
+      <c r="F727" s="40"/>
       <c r="G727" s="8" t="s">
         <v>1308</v>
       </c>
@@ -20624,7 +20580,7 @@
       <c r="E728" s="34" t="s">
         <v>1302</v>
       </c>
-      <c r="F728" s="49"/>
+      <c r="F728" s="40"/>
       <c r="G728" s="8" t="s">
         <v>1309</v>
       </c>
@@ -20645,7 +20601,7 @@
       <c r="E729" s="34" t="s">
         <v>1300</v>
       </c>
-      <c r="F729" s="49"/>
+      <c r="F729" s="40"/>
       <c r="G729" s="8" t="s">
         <v>1310</v>
       </c>
@@ -20666,7 +20622,7 @@
       <c r="E730" s="34" t="s">
         <v>1302</v>
       </c>
-      <c r="F730" s="49"/>
+      <c r="F730" s="40"/>
       <c r="G730" s="8" t="s">
         <v>1311</v>
       </c>
@@ -20687,7 +20643,7 @@
       <c r="E731" s="34" t="s">
         <v>1312</v>
       </c>
-      <c r="F731" s="49"/>
+      <c r="F731" s="40"/>
       <c r="G731" s="8" t="s">
         <v>1313</v>
       </c>
@@ -20708,7 +20664,7 @@
       <c r="E732" s="34" t="s">
         <v>1314</v>
       </c>
-      <c r="F732" s="49"/>
+      <c r="F732" s="40"/>
       <c r="G732" s="8" t="s">
         <v>1315</v>
       </c>
@@ -20729,7 +20685,7 @@
       <c r="E733" s="34" t="s">
         <v>1304</v>
       </c>
-      <c r="F733" s="49"/>
+      <c r="F733" s="40"/>
       <c r="G733" s="8" t="s">
         <v>1316</v>
       </c>
@@ -20750,7 +20706,7 @@
       <c r="E734" s="34" t="s">
         <v>1306</v>
       </c>
-      <c r="F734" s="49"/>
+      <c r="F734" s="40"/>
       <c r="G734" s="8" t="s">
         <v>1317</v>
       </c>
@@ -20771,7 +20727,7 @@
       <c r="E735" s="34" t="s">
         <v>1304</v>
       </c>
-      <c r="F735" s="49"/>
+      <c r="F735" s="40"/>
       <c r="G735" s="8" t="s">
         <v>1318</v>
       </c>
@@ -20792,7 +20748,7 @@
       <c r="E736" s="34" t="s">
         <v>1306</v>
       </c>
-      <c r="F736" s="49"/>
+      <c r="F736" s="40"/>
       <c r="G736" s="8" t="s">
         <v>1319</v>
       </c>
@@ -20813,7 +20769,7 @@
       <c r="E737" s="34" t="s">
         <v>1320</v>
       </c>
-      <c r="F737" s="49"/>
+      <c r="F737" s="40"/>
       <c r="G737" s="8" t="s">
         <v>1321</v>
       </c>
@@ -20834,7 +20790,7 @@
       <c r="E738" s="34" t="s">
         <v>1322</v>
       </c>
-      <c r="F738" s="49"/>
+      <c r="F738" s="40"/>
       <c r="G738" s="8" t="s">
         <v>1323</v>
       </c>
@@ -20855,7 +20811,7 @@
       <c r="E739" s="34" t="s">
         <v>1324</v>
       </c>
-      <c r="F739" s="49"/>
+      <c r="F739" s="40"/>
       <c r="G739" s="8" t="s">
         <v>1325</v>
       </c>
@@ -20876,7 +20832,7 @@
       <c r="E740" s="34" t="s">
         <v>1326</v>
       </c>
-      <c r="F740" s="49"/>
+      <c r="F740" s="40"/>
       <c r="G740" s="8" t="s">
         <v>1327</v>
       </c>
@@ -20897,7 +20853,7 @@
       <c r="E741" s="34" t="s">
         <v>1304</v>
       </c>
-      <c r="F741" s="49"/>
+      <c r="F741" s="40"/>
       <c r="G741" s="8" t="s">
         <v>1328</v>
       </c>
@@ -20918,7 +20874,7 @@
       <c r="E742" s="34" t="s">
         <v>1306</v>
       </c>
-      <c r="F742" s="49"/>
+      <c r="F742" s="40"/>
       <c r="G742" s="8" t="s">
         <v>1329</v>
       </c>
@@ -20939,7 +20895,7 @@
       <c r="E743" s="34" t="s">
         <v>1300</v>
       </c>
-      <c r="F743" s="49"/>
+      <c r="F743" s="40"/>
       <c r="G743" s="8" t="s">
         <v>1330</v>
       </c>
@@ -20960,7 +20916,7 @@
       <c r="E744" s="34" t="s">
         <v>1302</v>
       </c>
-      <c r="F744" s="49"/>
+      <c r="F744" s="40"/>
       <c r="G744" s="8" t="s">
         <v>1331</v>
       </c>
@@ -20981,7 +20937,7 @@
       <c r="E745" s="34" t="s">
         <v>1332</v>
       </c>
-      <c r="F745" s="49"/>
+      <c r="F745" s="40"/>
       <c r="G745" s="8" t="s">
         <v>1333</v>
       </c>
@@ -20993,8 +20949,8 @@
         <v>72</v>
       </c>
       <c r="D746" s="22"/>
-      <c r="E746" s="40"/>
-      <c r="F746" s="53"/>
+      <c r="E746" s="42"/>
+      <c r="F746" s="44"/>
       <c r="G746" s="13" t="s">
         <v>73</v>
       </c>
@@ -21011,7 +20967,7 @@
       <c r="E747" s="37" t="s">
         <v>1334</v>
       </c>
-      <c r="F747" s="48"/>
+      <c r="F747" s="38"/>
       <c r="G747" s="28" t="s">
         <v>1335</v>
       </c>
@@ -21025,8 +20981,8 @@
       <c r="D748" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E748" s="38"/>
-      <c r="F748" s="49"/>
+      <c r="E748" s="39"/>
+      <c r="F748" s="40"/>
       <c r="G748" s="29"/>
     </row>
     <row r="749" spans="1:7">
@@ -21045,7 +21001,7 @@
       <c r="E749" s="34" t="s">
         <v>1336</v>
       </c>
-      <c r="F749" s="49"/>
+      <c r="F749" s="40"/>
       <c r="G749" s="8" t="s">
         <v>1337</v>
       </c>
@@ -21066,7 +21022,7 @@
       <c r="E750" s="34" t="s">
         <v>1338</v>
       </c>
-      <c r="F750" s="49"/>
+      <c r="F750" s="40"/>
       <c r="G750" s="8" t="s">
         <v>1339</v>
       </c>
@@ -21087,7 +21043,7 @@
       <c r="E751" s="34" t="s">
         <v>1300</v>
       </c>
-      <c r="F751" s="49"/>
+      <c r="F751" s="40"/>
       <c r="G751" s="8" t="s">
         <v>1340</v>
       </c>
@@ -21108,7 +21064,7 @@
       <c r="E752" s="34" t="s">
         <v>1302</v>
       </c>
-      <c r="F752" s="49"/>
+      <c r="F752" s="40"/>
       <c r="G752" s="8" t="s">
         <v>1341</v>
       </c>
@@ -21129,7 +21085,7 @@
       <c r="E753" s="34" t="s">
         <v>1342</v>
       </c>
-      <c r="F753" s="49"/>
+      <c r="F753" s="40"/>
       <c r="G753" s="8" t="s">
         <v>1343</v>
       </c>
@@ -21150,7 +21106,7 @@
       <c r="E754" s="34" t="s">
         <v>1344</v>
       </c>
-      <c r="F754" s="49"/>
+      <c r="F754" s="40"/>
       <c r="G754" s="8" t="s">
         <v>1345</v>
       </c>
@@ -21171,7 +21127,7 @@
       <c r="E755" s="34" t="s">
         <v>1346</v>
       </c>
-      <c r="F755" s="49"/>
+      <c r="F755" s="40"/>
       <c r="G755" s="8" t="s">
         <v>1347</v>
       </c>
@@ -21192,7 +21148,7 @@
       <c r="E756" s="34" t="s">
         <v>1348</v>
       </c>
-      <c r="F756" s="49"/>
+      <c r="F756" s="40"/>
       <c r="G756" s="8" t="s">
         <v>1349</v>
       </c>
@@ -21213,7 +21169,7 @@
       <c r="E757" s="34" t="s">
         <v>1350</v>
       </c>
-      <c r="F757" s="49"/>
+      <c r="F757" s="40"/>
       <c r="G757" s="8" t="s">
         <v>1351</v>
       </c>
@@ -21234,7 +21190,7 @@
       <c r="E758" s="34" t="s">
         <v>1352</v>
       </c>
-      <c r="F758" s="49"/>
+      <c r="F758" s="40"/>
       <c r="G758" s="8" t="s">
         <v>1353</v>
       </c>
@@ -21255,7 +21211,7 @@
       <c r="E759" s="34" t="s">
         <v>1354</v>
       </c>
-      <c r="F759" s="49"/>
+      <c r="F759" s="40"/>
       <c r="G759" s="8" t="s">
         <v>1355</v>
       </c>
@@ -21276,7 +21232,7 @@
       <c r="E760" s="34" t="s">
         <v>1356</v>
       </c>
-      <c r="F760" s="49"/>
+      <c r="F760" s="40"/>
       <c r="G760" s="8" t="s">
         <v>1357</v>
       </c>
@@ -21297,7 +21253,7 @@
       <c r="E761" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="F761" s="49"/>
+      <c r="F761" s="40"/>
       <c r="G761" s="8" t="s">
         <v>1358</v>
       </c>
@@ -21318,7 +21274,7 @@
       <c r="E762" s="34" t="s">
         <v>41</v>
       </c>
-      <c r="F762" s="49"/>
+      <c r="F762" s="40"/>
       <c r="G762" s="8" t="s">
         <v>1359</v>
       </c>
@@ -21339,7 +21295,7 @@
       <c r="E763" s="34" t="s">
         <v>1360</v>
       </c>
-      <c r="F763" s="49"/>
+      <c r="F763" s="40"/>
       <c r="G763" s="8" t="s">
         <v>1361</v>
       </c>
@@ -21360,7 +21316,7 @@
       <c r="E764" s="34" t="s">
         <v>1362</v>
       </c>
-      <c r="F764" s="49"/>
+      <c r="F764" s="40"/>
       <c r="G764" s="8" t="s">
         <v>1363</v>
       </c>
@@ -21381,7 +21337,7 @@
       <c r="E765" s="34" t="s">
         <v>1364</v>
       </c>
-      <c r="F765" s="49"/>
+      <c r="F765" s="40"/>
       <c r="G765" s="8" t="s">
         <v>1365</v>
       </c>
@@ -21402,7 +21358,7 @@
       <c r="E766" s="34" t="s">
         <v>1366</v>
       </c>
-      <c r="F766" s="49"/>
+      <c r="F766" s="40"/>
       <c r="G766" s="8" t="s">
         <v>1367</v>
       </c>
@@ -21423,7 +21379,7 @@
       <c r="E767" s="34" t="s">
         <v>1368</v>
       </c>
-      <c r="F767" s="49"/>
+      <c r="F767" s="40"/>
       <c r="G767" s="8" t="s">
         <v>1369</v>
       </c>
@@ -21444,7 +21400,7 @@
       <c r="E768" s="34" t="s">
         <v>1370</v>
       </c>
-      <c r="F768" s="49"/>
+      <c r="F768" s="40"/>
       <c r="G768" s="8" t="s">
         <v>1371</v>
       </c>
@@ -21465,7 +21421,7 @@
       <c r="E769" s="34" t="s">
         <v>1227</v>
       </c>
-      <c r="F769" s="49"/>
+      <c r="F769" s="40"/>
       <c r="G769" s="8" t="s">
         <v>1372</v>
       </c>
@@ -21486,7 +21442,7 @@
       <c r="E770" s="34" t="s">
         <v>1229</v>
       </c>
-      <c r="F770" s="49"/>
+      <c r="F770" s="40"/>
       <c r="G770" s="8" t="s">
         <v>1373</v>
       </c>
@@ -21507,7 +21463,7 @@
       <c r="E771" s="34" t="s">
         <v>1374</v>
       </c>
-      <c r="F771" s="49"/>
+      <c r="F771" s="40"/>
       <c r="G771" s="8" t="s">
         <v>1375</v>
       </c>
@@ -21528,7 +21484,7 @@
       <c r="E772" s="34" t="s">
         <v>1376</v>
       </c>
-      <c r="F772" s="49"/>
+      <c r="F772" s="40"/>
       <c r="G772" s="8" t="s">
         <v>1377</v>
       </c>
@@ -21549,7 +21505,7 @@
       <c r="E773" s="34" t="s">
         <v>1378</v>
       </c>
-      <c r="F773" s="49"/>
+      <c r="F773" s="40"/>
       <c r="G773" s="8" t="s">
         <v>1379</v>
       </c>
@@ -21570,7 +21526,7 @@
       <c r="E774" s="34" t="s">
         <v>1380</v>
       </c>
-      <c r="F774" s="49"/>
+      <c r="F774" s="40"/>
       <c r="G774" s="8" t="s">
         <v>1381</v>
       </c>
@@ -21591,7 +21547,7 @@
       <c r="E775" s="34" t="s">
         <v>1374</v>
       </c>
-      <c r="F775" s="49"/>
+      <c r="F775" s="40"/>
       <c r="G775" s="8" t="s">
         <v>1382</v>
       </c>
@@ -21612,7 +21568,7 @@
       <c r="E776" s="34" t="s">
         <v>1376</v>
       </c>
-      <c r="F776" s="49"/>
+      <c r="F776" s="40"/>
       <c r="G776" s="8" t="s">
         <v>1383</v>
       </c>
@@ -21633,7 +21589,7 @@
       <c r="E777" s="34" t="s">
         <v>1384</v>
       </c>
-      <c r="F777" s="49"/>
+      <c r="F777" s="40"/>
       <c r="G777" s="8" t="s">
         <v>1385</v>
       </c>
@@ -21654,7 +21610,7 @@
       <c r="E778" s="34" t="s">
         <v>1386</v>
       </c>
-      <c r="F778" s="49"/>
+      <c r="F778" s="40"/>
       <c r="G778" s="8" t="s">
         <v>1387</v>
       </c>
@@ -21675,7 +21631,7 @@
       <c r="E779" s="34" t="s">
         <v>1388</v>
       </c>
-      <c r="F779" s="49"/>
+      <c r="F779" s="40"/>
       <c r="G779" s="8" t="s">
         <v>1389</v>
       </c>
@@ -21696,7 +21652,7 @@
       <c r="E780" s="34" t="s">
         <v>1390</v>
       </c>
-      <c r="F780" s="49"/>
+      <c r="F780" s="40"/>
       <c r="G780" s="8" t="s">
         <v>1391</v>
       </c>
@@ -21717,7 +21673,7 @@
       <c r="E781" s="34" t="s">
         <v>1392</v>
       </c>
-      <c r="F781" s="49"/>
+      <c r="F781" s="40"/>
       <c r="G781" s="8" t="s">
         <v>1393</v>
       </c>
@@ -21738,7 +21694,7 @@
       <c r="E782" s="34" t="s">
         <v>1394</v>
       </c>
-      <c r="F782" s="49"/>
+      <c r="F782" s="40"/>
       <c r="G782" s="8" t="s">
         <v>1395</v>
       </c>
@@ -21759,7 +21715,7 @@
       <c r="E783" s="34" t="s">
         <v>1396</v>
       </c>
-      <c r="F783" s="49"/>
+      <c r="F783" s="40"/>
       <c r="G783" s="8" t="s">
         <v>1397</v>
       </c>
@@ -21780,7 +21736,7 @@
       <c r="E784" s="34" t="s">
         <v>1398</v>
       </c>
-      <c r="F784" s="49"/>
+      <c r="F784" s="40"/>
       <c r="G784" s="8" t="s">
         <v>1399</v>
       </c>
@@ -21801,7 +21757,7 @@
       <c r="E785" s="34" t="s">
         <v>1400</v>
       </c>
-      <c r="F785" s="49"/>
+      <c r="F785" s="40"/>
       <c r="G785" s="8" t="s">
         <v>1401</v>
       </c>
@@ -21822,7 +21778,7 @@
       <c r="E786" s="34" t="s">
         <v>1402</v>
       </c>
-      <c r="F786" s="49"/>
+      <c r="F786" s="40"/>
       <c r="G786" s="8" t="s">
         <v>1403</v>
       </c>
@@ -21843,7 +21799,7 @@
       <c r="E787" s="34" t="s">
         <v>1404</v>
       </c>
-      <c r="F787" s="49"/>
+      <c r="F787" s="40"/>
       <c r="G787" s="8" t="s">
         <v>1405</v>
       </c>
@@ -21864,7 +21820,7 @@
       <c r="E788" s="34" t="s">
         <v>1406</v>
       </c>
-      <c r="F788" s="49"/>
+      <c r="F788" s="40"/>
       <c r="G788" s="8" t="s">
         <v>1407</v>
       </c>
@@ -21885,7 +21841,7 @@
       <c r="E789" s="34" t="s">
         <v>1374</v>
       </c>
-      <c r="F789" s="49"/>
+      <c r="F789" s="40"/>
       <c r="G789" s="8" t="s">
         <v>1408</v>
       </c>
@@ -21897,8 +21853,8 @@
         <v>72</v>
       </c>
       <c r="D790" s="22"/>
-      <c r="E790" s="40"/>
-      <c r="F790" s="53"/>
+      <c r="E790" s="42"/>
+      <c r="F790" s="44"/>
       <c r="G790" s="13" t="s">
         <v>73</v>
       </c>
@@ -21915,7 +21871,7 @@
       <c r="E791" s="37" t="s">
         <v>1376</v>
       </c>
-      <c r="F791" s="48"/>
+      <c r="F791" s="38"/>
       <c r="G791" s="28" t="s">
         <v>1409</v>
       </c>
@@ -21929,8 +21885,8 @@
       <c r="D792" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E792" s="38"/>
-      <c r="F792" s="49"/>
+      <c r="E792" s="39"/>
+      <c r="F792" s="40"/>
       <c r="G792" s="29"/>
     </row>
     <row r="793" spans="1:7">
@@ -21949,7 +21905,7 @@
       <c r="E793" s="34" t="s">
         <v>1410</v>
       </c>
-      <c r="F793" s="49"/>
+      <c r="F793" s="40"/>
       <c r="G793" s="8" t="s">
         <v>1411</v>
       </c>
@@ -21970,7 +21926,7 @@
       <c r="E794" s="34" t="s">
         <v>1412</v>
       </c>
-      <c r="F794" s="49"/>
+      <c r="F794" s="40"/>
       <c r="G794" s="8" t="s">
         <v>1413</v>
       </c>
@@ -21991,7 +21947,7 @@
       <c r="E795" s="34" t="s">
         <v>1414</v>
       </c>
-      <c r="F795" s="49"/>
+      <c r="F795" s="40"/>
       <c r="G795" s="8" t="s">
         <v>1415</v>
       </c>
@@ -22012,7 +21968,7 @@
       <c r="E796" s="34" t="s">
         <v>1416</v>
       </c>
-      <c r="F796" s="49"/>
+      <c r="F796" s="40"/>
       <c r="G796" s="8" t="s">
         <v>1417</v>
       </c>
@@ -22033,7 +21989,7 @@
       <c r="E797" s="34" t="s">
         <v>1418</v>
       </c>
-      <c r="F797" s="49"/>
+      <c r="F797" s="40"/>
       <c r="G797" s="8" t="s">
         <v>1419</v>
       </c>
@@ -22054,7 +22010,7 @@
       <c r="E798" s="34" t="s">
         <v>1420</v>
       </c>
-      <c r="F798" s="49"/>
+      <c r="F798" s="40"/>
       <c r="G798" s="8" t="s">
         <v>1421</v>
       </c>
@@ -22075,7 +22031,7 @@
       <c r="E799" s="34" t="s">
         <v>1374</v>
       </c>
-      <c r="F799" s="49"/>
+      <c r="F799" s="40"/>
       <c r="G799" s="8" t="s">
         <v>1422</v>
       </c>
@@ -22096,7 +22052,7 @@
       <c r="E800" s="34" t="s">
         <v>1376</v>
       </c>
-      <c r="F800" s="49"/>
+      <c r="F800" s="40"/>
       <c r="G800" s="8" t="s">
         <v>1423</v>
       </c>
@@ -22117,7 +22073,7 @@
       <c r="E801" s="34" t="s">
         <v>1374</v>
       </c>
-      <c r="F801" s="49"/>
+      <c r="F801" s="40"/>
       <c r="G801" s="8" t="s">
         <v>1424</v>
       </c>
@@ -22138,7 +22094,7 @@
       <c r="E802" s="34" t="s">
         <v>1376</v>
       </c>
-      <c r="F802" s="49"/>
+      <c r="F802" s="40"/>
       <c r="G802" s="8" t="s">
         <v>1425</v>
       </c>
@@ -22159,7 +22115,7 @@
       <c r="E803" s="34" t="s">
         <v>1374</v>
       </c>
-      <c r="F803" s="49"/>
+      <c r="F803" s="40"/>
       <c r="G803" s="8" t="s">
         <v>1426</v>
       </c>
@@ -22180,7 +22136,7 @@
       <c r="E804" s="34" t="s">
         <v>1376</v>
       </c>
-      <c r="F804" s="49"/>
+      <c r="F804" s="40"/>
       <c r="G804" s="8" t="s">
         <v>1427</v>
       </c>
@@ -22201,7 +22157,7 @@
       <c r="E805" s="34" t="s">
         <v>1428</v>
       </c>
-      <c r="F805" s="49"/>
+      <c r="F805" s="40"/>
       <c r="G805" s="8" t="s">
         <v>1429</v>
       </c>
@@ -22222,7 +22178,7 @@
       <c r="E806" s="34" t="s">
         <v>1430</v>
       </c>
-      <c r="F806" s="49"/>
+      <c r="F806" s="40"/>
       <c r="G806" s="8" t="s">
         <v>1431</v>
       </c>
@@ -22243,7 +22199,7 @@
       <c r="E807" s="34" t="s">
         <v>1432</v>
       </c>
-      <c r="F807" s="49"/>
+      <c r="F807" s="40"/>
       <c r="G807" s="8" t="s">
         <v>1433</v>
       </c>
@@ -22264,7 +22220,7 @@
       <c r="E808" s="34" t="s">
         <v>1434</v>
       </c>
-      <c r="F808" s="49"/>
+      <c r="F808" s="40"/>
       <c r="G808" s="8" t="s">
         <v>1435</v>
       </c>
@@ -22285,7 +22241,7 @@
       <c r="E809" s="34" t="s">
         <v>1436</v>
       </c>
-      <c r="F809" s="49"/>
+      <c r="F809" s="40"/>
       <c r="G809" s="8" t="s">
         <v>1437</v>
       </c>
@@ -22306,7 +22262,7 @@
       <c r="E810" s="34" t="s">
         <v>1438</v>
       </c>
-      <c r="F810" s="49"/>
+      <c r="F810" s="40"/>
       <c r="G810" s="8" t="s">
         <v>1439</v>
       </c>
@@ -22327,7 +22283,7 @@
       <c r="E811" s="34" t="s">
         <v>1440</v>
       </c>
-      <c r="F811" s="49"/>
+      <c r="F811" s="40"/>
       <c r="G811" s="8" t="s">
         <v>1441</v>
       </c>
@@ -22348,7 +22304,7 @@
       <c r="E812" s="34" t="s">
         <v>1442</v>
       </c>
-      <c r="F812" s="49"/>
+      <c r="F812" s="40"/>
       <c r="G812" s="8" t="s">
         <v>1443</v>
       </c>
@@ -22369,7 +22325,7 @@
       <c r="E813" s="34" t="s">
         <v>1440</v>
       </c>
-      <c r="F813" s="49"/>
+      <c r="F813" s="40"/>
       <c r="G813" s="8" t="s">
         <v>1444</v>
       </c>
@@ -22390,7 +22346,7 @@
       <c r="E814" s="34" t="s">
         <v>1442</v>
       </c>
-      <c r="F814" s="49"/>
+      <c r="F814" s="40"/>
       <c r="G814" s="8" t="s">
         <v>1445</v>
       </c>
@@ -22411,7 +22367,7 @@
       <c r="E815" s="34" t="s">
         <v>1446</v>
       </c>
-      <c r="F815" s="49"/>
+      <c r="F815" s="40"/>
       <c r="G815" s="8" t="s">
         <v>1447</v>
       </c>
@@ -22432,7 +22388,7 @@
       <c r="E816" s="34" t="s">
         <v>1448</v>
       </c>
-      <c r="F816" s="49"/>
+      <c r="F816" s="40"/>
       <c r="G816" s="8" t="s">
         <v>1449</v>
       </c>
@@ -22453,7 +22409,7 @@
       <c r="E817" s="34" t="s">
         <v>1450</v>
       </c>
-      <c r="F817" s="49"/>
+      <c r="F817" s="40"/>
       <c r="G817" s="8" t="s">
         <v>1451</v>
       </c>
@@ -22474,7 +22430,7 @@
       <c r="E818" s="34" t="s">
         <v>1452</v>
       </c>
-      <c r="F818" s="49"/>
+      <c r="F818" s="40"/>
       <c r="G818" s="8" t="s">
         <v>1453</v>
       </c>
@@ -22495,7 +22451,7 @@
       <c r="E819" s="34" t="s">
         <v>1454</v>
       </c>
-      <c r="F819" s="49"/>
+      <c r="F819" s="40"/>
       <c r="G819" s="8" t="s">
         <v>1455</v>
       </c>
@@ -22516,7 +22472,7 @@
       <c r="E820" s="34" t="s">
         <v>1456</v>
       </c>
-      <c r="F820" s="49"/>
+      <c r="F820" s="40"/>
       <c r="G820" s="8" t="s">
         <v>1457</v>
       </c>
@@ -22537,7 +22493,7 @@
       <c r="E821" s="34" t="s">
         <v>1458</v>
       </c>
-      <c r="F821" s="49"/>
+      <c r="F821" s="40"/>
       <c r="G821" s="8" t="s">
         <v>1459</v>
       </c>
@@ -22558,7 +22514,7 @@
       <c r="E822" s="34" t="s">
         <v>1460</v>
       </c>
-      <c r="F822" s="49"/>
+      <c r="F822" s="40"/>
       <c r="G822" s="8" t="s">
         <v>1461</v>
       </c>
@@ -22579,7 +22535,7 @@
       <c r="E823" s="34" t="s">
         <v>1462</v>
       </c>
-      <c r="F823" s="49"/>
+      <c r="F823" s="40"/>
       <c r="G823" s="8" t="s">
         <v>1463</v>
       </c>
@@ -22600,7 +22556,7 @@
       <c r="E824" s="34" t="s">
         <v>1464</v>
       </c>
-      <c r="F824" s="49"/>
+      <c r="F824" s="40"/>
       <c r="G824" s="8" t="s">
         <v>1465</v>
       </c>
@@ -22621,7 +22577,7 @@
       <c r="E825" s="34" t="s">
         <v>1466</v>
       </c>
-      <c r="F825" s="49"/>
+      <c r="F825" s="40"/>
       <c r="G825" s="8" t="s">
         <v>1467</v>
       </c>
@@ -22642,7 +22598,7 @@
       <c r="E826" s="34" t="s">
         <v>1468</v>
       </c>
-      <c r="F826" s="49"/>
+      <c r="F826" s="40"/>
       <c r="G826" s="8" t="s">
         <v>1469</v>
       </c>
@@ -22663,7 +22619,7 @@
       <c r="E827" s="34" t="s">
         <v>1470</v>
       </c>
-      <c r="F827" s="49"/>
+      <c r="F827" s="40"/>
       <c r="G827" s="8" t="s">
         <v>1471</v>
       </c>
@@ -22684,7 +22640,7 @@
       <c r="E828" s="34" t="s">
         <v>1472</v>
       </c>
-      <c r="F828" s="49"/>
+      <c r="F828" s="40"/>
       <c r="G828" s="8" t="s">
         <v>1473</v>
       </c>
@@ -22705,7 +22661,7 @@
       <c r="E829" s="34" t="s">
         <v>1462</v>
       </c>
-      <c r="F829" s="49"/>
+      <c r="F829" s="40"/>
       <c r="G829" s="8" t="s">
         <v>1474</v>
       </c>
@@ -22726,7 +22682,7 @@
       <c r="E830" s="34" t="s">
         <v>1464</v>
       </c>
-      <c r="F830" s="49"/>
+      <c r="F830" s="40"/>
       <c r="G830" s="8" t="s">
         <v>1475</v>
       </c>
@@ -22747,7 +22703,7 @@
       <c r="E831" s="34" t="s">
         <v>1227</v>
       </c>
-      <c r="F831" s="49"/>
+      <c r="F831" s="40"/>
       <c r="G831" s="8" t="s">
         <v>1476</v>
       </c>
@@ -22768,7 +22724,7 @@
       <c r="E832" s="34" t="s">
         <v>1229</v>
       </c>
-      <c r="F832" s="49"/>
+      <c r="F832" s="40"/>
       <c r="G832" s="8" t="s">
         <v>1477</v>
       </c>
@@ -22789,7 +22745,7 @@
       <c r="E833" s="34" t="s">
         <v>1478</v>
       </c>
-      <c r="F833" s="49"/>
+      <c r="F833" s="40"/>
       <c r="G833" s="8" t="s">
         <v>1479</v>
       </c>
@@ -22801,8 +22757,8 @@
         <v>72</v>
       </c>
       <c r="D834" s="22"/>
-      <c r="E834" s="40"/>
-      <c r="F834" s="53"/>
+      <c r="E834" s="42"/>
+      <c r="F834" s="44"/>
       <c r="G834" s="13" t="s">
         <v>73</v>
       </c>
@@ -22819,7 +22775,7 @@
       <c r="E835" s="37" t="s">
         <v>1480</v>
       </c>
-      <c r="F835" s="48"/>
+      <c r="F835" s="38"/>
       <c r="G835" s="28" t="s">
         <v>1481</v>
       </c>
@@ -22833,8 +22789,8 @@
       <c r="D836" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E836" s="38"/>
-      <c r="F836" s="49"/>
+      <c r="E836" s="39"/>
+      <c r="F836" s="40"/>
       <c r="G836" s="29"/>
     </row>
     <row r="837" spans="1:7">
@@ -22853,7 +22809,7 @@
       <c r="E837" s="34" t="s">
         <v>1482</v>
       </c>
-      <c r="F837" s="49"/>
+      <c r="F837" s="40"/>
       <c r="G837" s="8" t="s">
         <v>1483</v>
       </c>
@@ -22874,7 +22830,7 @@
       <c r="E838" s="34" t="s">
         <v>1484</v>
       </c>
-      <c r="F838" s="49"/>
+      <c r="F838" s="40"/>
       <c r="G838" s="8" t="s">
         <v>1485</v>
       </c>
@@ -22895,7 +22851,7 @@
       <c r="E839" s="34" t="s">
         <v>1486</v>
       </c>
-      <c r="F839" s="49"/>
+      <c r="F839" s="40"/>
       <c r="G839" s="8" t="s">
         <v>1487</v>
       </c>
@@ -22916,7 +22872,7 @@
       <c r="E840" s="34" t="s">
         <v>1488</v>
       </c>
-      <c r="F840" s="49"/>
+      <c r="F840" s="40"/>
       <c r="G840" s="8" t="s">
         <v>1489</v>
       </c>
@@ -22937,7 +22893,7 @@
       <c r="E841" s="34" t="s">
         <v>1490</v>
       </c>
-      <c r="F841" s="49"/>
+      <c r="F841" s="40"/>
       <c r="G841" s="8" t="s">
         <v>1491</v>
       </c>
@@ -22958,7 +22914,7 @@
       <c r="E842" s="34" t="s">
         <v>1492</v>
       </c>
-      <c r="F842" s="49"/>
+      <c r="F842" s="40"/>
       <c r="G842" s="8" t="s">
         <v>1493</v>
       </c>
@@ -22979,7 +22935,7 @@
       <c r="E843" s="34" t="s">
         <v>1494</v>
       </c>
-      <c r="F843" s="49"/>
+      <c r="F843" s="40"/>
       <c r="G843" s="8" t="s">
         <v>1495</v>
       </c>
@@ -23000,7 +22956,7 @@
       <c r="E844" s="34" t="s">
         <v>1496</v>
       </c>
-      <c r="F844" s="49"/>
+      <c r="F844" s="40"/>
       <c r="G844" s="8" t="s">
         <v>1497</v>
       </c>
@@ -23021,7 +22977,7 @@
       <c r="E845" s="34" t="s">
         <v>1498</v>
       </c>
-      <c r="F845" s="49"/>
+      <c r="F845" s="40"/>
       <c r="G845" s="8" t="s">
         <v>1499</v>
       </c>
@@ -23042,7 +22998,7 @@
       <c r="E846" s="34" t="s">
         <v>1500</v>
       </c>
-      <c r="F846" s="49"/>
+      <c r="F846" s="40"/>
       <c r="G846" s="8" t="s">
         <v>1501</v>
       </c>
@@ -23063,7 +23019,7 @@
       <c r="E847" s="34" t="s">
         <v>1502</v>
       </c>
-      <c r="F847" s="49"/>
+      <c r="F847" s="40"/>
       <c r="G847" s="8" t="s">
         <v>1503</v>
       </c>
@@ -23084,7 +23040,7 @@
       <c r="E848" s="34" t="s">
         <v>1504</v>
       </c>
-      <c r="F848" s="49"/>
+      <c r="F848" s="40"/>
       <c r="G848" s="8" t="s">
         <v>1505</v>
       </c>
@@ -23105,7 +23061,7 @@
       <c r="E849" s="34" t="s">
         <v>1506</v>
       </c>
-      <c r="F849" s="49"/>
+      <c r="F849" s="40"/>
       <c r="G849" s="8" t="s">
         <v>1507</v>
       </c>
@@ -23126,7 +23082,7 @@
       <c r="E850" s="34" t="s">
         <v>1508</v>
       </c>
-      <c r="F850" s="49"/>
+      <c r="F850" s="40"/>
       <c r="G850" s="8" t="s">
         <v>1509</v>
       </c>
@@ -23147,7 +23103,7 @@
       <c r="E851" s="34" t="s">
         <v>1227</v>
       </c>
-      <c r="F851" s="49"/>
+      <c r="F851" s="40"/>
       <c r="G851" s="8" t="s">
         <v>1510</v>
       </c>
@@ -23168,7 +23124,7 @@
       <c r="E852" s="34" t="s">
         <v>1229</v>
       </c>
-      <c r="F852" s="49"/>
+      <c r="F852" s="40"/>
       <c r="G852" s="8" t="s">
         <v>1511</v>
       </c>
@@ -23189,7 +23145,7 @@
       <c r="E853" s="34" t="s">
         <v>1512</v>
       </c>
-      <c r="F853" s="49"/>
+      <c r="F853" s="40"/>
       <c r="G853" s="8" t="s">
         <v>1513</v>
       </c>
@@ -23210,7 +23166,7 @@
       <c r="E854" s="34" t="s">
         <v>1514</v>
       </c>
-      <c r="F854" s="49"/>
+      <c r="F854" s="40"/>
       <c r="G854" s="8" t="s">
         <v>1515</v>
       </c>
@@ -23231,7 +23187,7 @@
       <c r="E855" s="34" t="s">
         <v>1516</v>
       </c>
-      <c r="F855" s="49"/>
+      <c r="F855" s="40"/>
       <c r="G855" s="8" t="s">
         <v>1517</v>
       </c>
@@ -23252,7 +23208,7 @@
       <c r="E856" s="34" t="s">
         <v>1518</v>
       </c>
-      <c r="F856" s="49"/>
+      <c r="F856" s="40"/>
       <c r="G856" s="8" t="s">
         <v>1519</v>
       </c>
@@ -23273,7 +23229,7 @@
       <c r="E857" s="34" t="s">
         <v>1520</v>
       </c>
-      <c r="F857" s="49"/>
+      <c r="F857" s="40"/>
       <c r="G857" s="8" t="s">
         <v>1521</v>
       </c>
@@ -23294,7 +23250,7 @@
       <c r="E858" s="34" t="s">
         <v>1522</v>
       </c>
-      <c r="F858" s="49"/>
+      <c r="F858" s="40"/>
       <c r="G858" s="8" t="s">
         <v>1523</v>
       </c>
@@ -23315,7 +23271,7 @@
       <c r="E859" s="34" t="s">
         <v>1524</v>
       </c>
-      <c r="F859" s="49"/>
+      <c r="F859" s="40"/>
       <c r="G859" s="8" t="s">
         <v>1525</v>
       </c>
@@ -23336,7 +23292,7 @@
       <c r="E860" s="34" t="s">
         <v>1526</v>
       </c>
-      <c r="F860" s="49"/>
+      <c r="F860" s="40"/>
       <c r="G860" s="8" t="s">
         <v>1527</v>
       </c>
@@ -23357,7 +23313,7 @@
       <c r="E861" s="34" t="s">
         <v>1528</v>
       </c>
-      <c r="F861" s="49"/>
+      <c r="F861" s="40"/>
       <c r="G861" s="8" t="s">
         <v>1529</v>
       </c>
@@ -23378,7 +23334,7 @@
       <c r="E862" s="34" t="s">
         <v>1530</v>
       </c>
-      <c r="F862" s="49"/>
+      <c r="F862" s="40"/>
       <c r="G862" s="8" t="s">
         <v>1531</v>
       </c>
@@ -23399,7 +23355,7 @@
       <c r="E863" s="34" t="s">
         <v>1532</v>
       </c>
-      <c r="F863" s="49"/>
+      <c r="F863" s="40"/>
       <c r="G863" s="8" t="s">
         <v>1533</v>
       </c>
@@ -23420,7 +23376,7 @@
       <c r="E864" s="34" t="s">
         <v>1534</v>
       </c>
-      <c r="F864" s="49"/>
+      <c r="F864" s="40"/>
       <c r="G864" s="8" t="s">
         <v>1535</v>
       </c>
@@ -23441,7 +23397,7 @@
       <c r="E865" s="34" t="s">
         <v>1536</v>
       </c>
-      <c r="F865" s="49"/>
+      <c r="F865" s="40"/>
       <c r="G865" s="8" t="s">
         <v>1537</v>
       </c>
@@ -23462,7 +23418,7 @@
       <c r="E866" s="34" t="s">
         <v>1538</v>
       </c>
-      <c r="F866" s="49"/>
+      <c r="F866" s="40"/>
       <c r="G866" s="8" t="s">
         <v>1539</v>
       </c>
@@ -23483,7 +23439,7 @@
       <c r="E867" s="34" t="s">
         <v>1540</v>
       </c>
-      <c r="F867" s="49"/>
+      <c r="F867" s="40"/>
       <c r="G867" s="8" t="s">
         <v>1541</v>
       </c>
@@ -23504,7 +23460,7 @@
       <c r="E868" s="34" t="s">
         <v>1542</v>
       </c>
-      <c r="F868" s="49"/>
+      <c r="F868" s="40"/>
       <c r="G868" s="8" t="s">
         <v>1543</v>
       </c>
@@ -23525,7 +23481,7 @@
       <c r="E869" s="34" t="s">
         <v>1544</v>
       </c>
-      <c r="F869" s="49"/>
+      <c r="F869" s="40"/>
       <c r="G869" s="8" t="s">
         <v>1545</v>
       </c>
@@ -23546,7 +23502,7 @@
       <c r="E870" s="34" t="s">
         <v>1546</v>
       </c>
-      <c r="F870" s="49"/>
+      <c r="F870" s="40"/>
       <c r="G870" s="8" t="s">
         <v>1547</v>
       </c>
@@ -23567,7 +23523,7 @@
       <c r="E871" s="34" t="s">
         <v>1548</v>
       </c>
-      <c r="F871" s="49"/>
+      <c r="F871" s="40"/>
       <c r="G871" s="8" t="s">
         <v>1549</v>
       </c>
@@ -23588,7 +23544,7 @@
       <c r="E872" s="34" t="s">
         <v>1550</v>
       </c>
-      <c r="F872" s="49"/>
+      <c r="F872" s="40"/>
       <c r="G872" s="8" t="s">
         <v>1551</v>
       </c>
@@ -23609,7 +23565,7 @@
       <c r="E873" s="34" t="s">
         <v>1552</v>
       </c>
-      <c r="F873" s="49"/>
+      <c r="F873" s="40"/>
       <c r="G873" s="8" t="s">
         <v>1553</v>
       </c>
@@ -23630,7 +23586,7 @@
       <c r="E874" s="34" t="s">
         <v>1554</v>
       </c>
-      <c r="F874" s="49"/>
+      <c r="F874" s="40"/>
       <c r="G874" s="8" t="s">
         <v>1555</v>
       </c>
@@ -23651,7 +23607,7 @@
       <c r="E875" s="34" t="s">
         <v>1556</v>
       </c>
-      <c r="F875" s="49"/>
+      <c r="F875" s="40"/>
       <c r="G875" s="8" t="s">
         <v>1557</v>
       </c>
@@ -23672,7 +23628,7 @@
       <c r="E876" s="34" t="s">
         <v>1558</v>
       </c>
-      <c r="F876" s="49"/>
+      <c r="F876" s="40"/>
       <c r="G876" s="8" t="s">
         <v>1559</v>
       </c>
@@ -23693,7 +23649,7 @@
       <c r="E877" s="34" t="s">
         <v>1560</v>
       </c>
-      <c r="F877" s="49"/>
+      <c r="F877" s="40"/>
       <c r="G877" s="8" t="s">
         <v>1561</v>
       </c>
@@ -23705,8 +23661,8 @@
         <v>72</v>
       </c>
       <c r="D878" s="22"/>
-      <c r="E878" s="40"/>
-      <c r="F878" s="53"/>
+      <c r="E878" s="42"/>
+      <c r="F878" s="44"/>
       <c r="G878" s="13" t="s">
         <v>73</v>
       </c>
@@ -23723,7 +23679,7 @@
       <c r="E879" s="37" t="s">
         <v>1562</v>
       </c>
-      <c r="F879" s="48"/>
+      <c r="F879" s="38"/>
       <c r="G879" s="28" t="s">
         <v>1563</v>
       </c>
@@ -23737,8 +23693,8 @@
       <c r="D880" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E880" s="38"/>
-      <c r="F880" s="49"/>
+      <c r="E880" s="39"/>
+      <c r="F880" s="40"/>
       <c r="G880" s="29"/>
     </row>
     <row r="881" spans="1:7">
@@ -23757,7 +23713,7 @@
       <c r="E881" s="34" t="s">
         <v>1556</v>
       </c>
-      <c r="F881" s="49"/>
+      <c r="F881" s="40"/>
       <c r="G881" s="8" t="s">
         <v>1564</v>
       </c>
@@ -23778,7 +23734,7 @@
       <c r="E882" s="34" t="s">
         <v>1558</v>
       </c>
-      <c r="F882" s="49"/>
+      <c r="F882" s="40"/>
       <c r="G882" s="8" t="s">
         <v>1565</v>
       </c>
@@ -23799,7 +23755,7 @@
       <c r="E883" s="34" t="s">
         <v>1566</v>
       </c>
-      <c r="F883" s="49"/>
+      <c r="F883" s="40"/>
       <c r="G883" s="8" t="s">
         <v>1567</v>
       </c>
@@ -23820,7 +23776,7 @@
       <c r="E884" s="34" t="s">
         <v>1568</v>
       </c>
-      <c r="F884" s="49"/>
+      <c r="F884" s="40"/>
       <c r="G884" s="8" t="s">
         <v>1569</v>
       </c>
@@ -23841,7 +23797,7 @@
       <c r="E885" s="34" t="s">
         <v>1570</v>
       </c>
-      <c r="F885" s="49"/>
+      <c r="F885" s="40"/>
       <c r="G885" s="8" t="s">
         <v>1571</v>
       </c>
@@ -23862,7 +23818,7 @@
       <c r="E886" s="34" t="s">
         <v>1572</v>
       </c>
-      <c r="F886" s="49"/>
+      <c r="F886" s="40"/>
       <c r="G886" s="8" t="s">
         <v>1573</v>
       </c>
@@ -23883,7 +23839,7 @@
       <c r="E887" s="34" t="s">
         <v>1574</v>
       </c>
-      <c r="F887" s="49"/>
+      <c r="F887" s="40"/>
       <c r="G887" s="8" t="s">
         <v>1575</v>
       </c>
@@ -23904,7 +23860,7 @@
       <c r="E888" s="34" t="s">
         <v>1576</v>
       </c>
-      <c r="F888" s="49"/>
+      <c r="F888" s="40"/>
       <c r="G888" s="8" t="s">
         <v>1577</v>
       </c>
@@ -23925,7 +23881,7 @@
       <c r="E889" s="34" t="s">
         <v>1578</v>
       </c>
-      <c r="F889" s="49"/>
+      <c r="F889" s="40"/>
       <c r="G889" s="8" t="s">
         <v>1579</v>
       </c>
@@ -23946,7 +23902,7 @@
       <c r="E890" s="34" t="s">
         <v>1580</v>
       </c>
-      <c r="F890" s="49"/>
+      <c r="F890" s="40"/>
       <c r="G890" s="8" t="s">
         <v>1581</v>
       </c>
@@ -23967,7 +23923,7 @@
       <c r="E891" s="34" t="s">
         <v>1582</v>
       </c>
-      <c r="F891" s="49"/>
+      <c r="F891" s="40"/>
       <c r="G891" s="8" t="s">
         <v>1583</v>
       </c>
@@ -23988,7 +23944,7 @@
       <c r="E892" s="34" t="s">
         <v>1584</v>
       </c>
-      <c r="F892" s="49"/>
+      <c r="F892" s="40"/>
       <c r="G892" s="8" t="s">
         <v>1585</v>
       </c>
@@ -24009,7 +23965,7 @@
       <c r="E893" s="34" t="s">
         <v>1586</v>
       </c>
-      <c r="F893" s="49"/>
+      <c r="F893" s="40"/>
       <c r="G893" s="8" t="s">
         <v>1587</v>
       </c>
@@ -24030,7 +23986,7 @@
       <c r="E894" s="34" t="s">
         <v>1588</v>
       </c>
-      <c r="F894" s="49"/>
+      <c r="F894" s="40"/>
       <c r="G894" s="8" t="s">
         <v>1589</v>
       </c>
@@ -24051,7 +24007,7 @@
       <c r="E895" s="34" t="s">
         <v>1590</v>
       </c>
-      <c r="F895" s="49"/>
+      <c r="F895" s="40"/>
       <c r="G895" s="8" t="s">
         <v>1591</v>
       </c>
@@ -24072,7 +24028,7 @@
       <c r="E896" s="34" t="s">
         <v>1592</v>
       </c>
-      <c r="F896" s="49"/>
+      <c r="F896" s="40"/>
       <c r="G896" s="8" t="s">
         <v>1593</v>
       </c>
@@ -24093,7 +24049,7 @@
       <c r="E897" s="34" t="s">
         <v>1594</v>
       </c>
-      <c r="F897" s="49"/>
+      <c r="F897" s="40"/>
       <c r="G897" s="8" t="s">
         <v>1595</v>
       </c>
@@ -24114,7 +24070,7 @@
       <c r="E898" s="34" t="s">
         <v>1596</v>
       </c>
-      <c r="F898" s="49"/>
+      <c r="F898" s="40"/>
       <c r="G898" s="8" t="s">
         <v>1597</v>
       </c>
@@ -24135,7 +24091,7 @@
       <c r="E899" s="34" t="s">
         <v>1598</v>
       </c>
-      <c r="F899" s="49"/>
+      <c r="F899" s="40"/>
       <c r="G899" s="8" t="s">
         <v>1599</v>
       </c>
@@ -24156,7 +24112,7 @@
       <c r="E900" s="34" t="s">
         <v>1600</v>
       </c>
-      <c r="F900" s="49"/>
+      <c r="F900" s="40"/>
       <c r="G900" s="8" t="s">
         <v>1601</v>
       </c>
@@ -24177,7 +24133,7 @@
       <c r="E901" s="34" t="s">
         <v>1602</v>
       </c>
-      <c r="F901" s="49"/>
+      <c r="F901" s="40"/>
       <c r="G901" s="8" t="s">
         <v>1603</v>
       </c>
@@ -24198,7 +24154,7 @@
       <c r="E902" s="34" t="s">
         <v>1604</v>
       </c>
-      <c r="F902" s="49"/>
+      <c r="F902" s="40"/>
       <c r="G902" s="8" t="s">
         <v>1605</v>
       </c>
@@ -24219,7 +24175,7 @@
       <c r="E903" s="34" t="s">
         <v>1606</v>
       </c>
-      <c r="F903" s="49"/>
+      <c r="F903" s="40"/>
       <c r="G903" s="8" t="s">
         <v>1607</v>
       </c>
@@ -24240,7 +24196,7 @@
       <c r="E904" s="34" t="s">
         <v>1608</v>
       </c>
-      <c r="F904" s="49"/>
+      <c r="F904" s="40"/>
       <c r="G904" s="8" t="s">
         <v>1609</v>
       </c>
@@ -24261,7 +24217,7 @@
       <c r="E905" s="34" t="s">
         <v>1610</v>
       </c>
-      <c r="F905" s="49"/>
+      <c r="F905" s="40"/>
       <c r="G905" s="8" t="s">
         <v>73</v>
       </c>
@@ -24282,7 +24238,7 @@
       <c r="E906" s="34" t="s">
         <v>1611</v>
       </c>
-      <c r="F906" s="49"/>
+      <c r="F906" s="40"/>
       <c r="G906" s="8" t="s">
         <v>1612</v>
       </c>
@@ -24303,7 +24259,7 @@
       <c r="E907" s="34" t="s">
         <v>1613</v>
       </c>
-      <c r="F907" s="49"/>
+      <c r="F907" s="40"/>
       <c r="G907" s="8" t="s">
         <v>1614</v>
       </c>
@@ -24324,7 +24280,7 @@
       <c r="E908" s="34" t="s">
         <v>1615</v>
       </c>
-      <c r="F908" s="49"/>
+      <c r="F908" s="40"/>
       <c r="G908" s="8" t="s">
         <v>1616</v>
       </c>
@@ -24345,7 +24301,7 @@
       <c r="E909" s="34" t="s">
         <v>1617</v>
       </c>
-      <c r="F909" s="49"/>
+      <c r="F909" s="40"/>
       <c r="G909" s="8" t="s">
         <v>1618</v>
       </c>
@@ -24366,7 +24322,7 @@
       <c r="E910" s="34" t="s">
         <v>1619</v>
       </c>
-      <c r="F910" s="49"/>
+      <c r="F910" s="40"/>
       <c r="G910" s="8" t="s">
         <v>1620</v>
       </c>
@@ -24387,7 +24343,7 @@
       <c r="E911" s="34" t="s">
         <v>1621</v>
       </c>
-      <c r="F911" s="49"/>
+      <c r="F911" s="40"/>
       <c r="G911" s="8" t="s">
         <v>1622</v>
       </c>
@@ -24408,7 +24364,7 @@
       <c r="E912" s="34" t="s">
         <v>1623</v>
       </c>
-      <c r="F912" s="49"/>
+      <c r="F912" s="40"/>
       <c r="G912" s="8" t="s">
         <v>1624</v>
       </c>
@@ -24429,7 +24385,7 @@
       <c r="E913" s="34" t="s">
         <v>1556</v>
       </c>
-      <c r="F913" s="49"/>
+      <c r="F913" s="40"/>
       <c r="G913" s="8" t="s">
         <v>1625</v>
       </c>
@@ -24450,7 +24406,7 @@
       <c r="E914" s="34" t="s">
         <v>1558</v>
       </c>
-      <c r="F914" s="49"/>
+      <c r="F914" s="40"/>
       <c r="G914" s="8" t="s">
         <v>1626</v>
       </c>
@@ -24471,7 +24427,7 @@
       <c r="E915" s="34" t="s">
         <v>1627</v>
       </c>
-      <c r="F915" s="49"/>
+      <c r="F915" s="40"/>
       <c r="G915" s="8" t="s">
         <v>1628</v>
       </c>
@@ -24492,7 +24448,7 @@
       <c r="E916" s="34" t="s">
         <v>1629</v>
       </c>
-      <c r="F916" s="49"/>
+      <c r="F916" s="40"/>
       <c r="G916" s="8" t="s">
         <v>1630</v>
       </c>
@@ -24513,7 +24469,7 @@
       <c r="E917" s="34" t="s">
         <v>1631</v>
       </c>
-      <c r="F917" s="49"/>
+      <c r="F917" s="40"/>
       <c r="G917" s="8" t="s">
         <v>1632</v>
       </c>
@@ -24534,7 +24490,7 @@
       <c r="E918" s="34" t="s">
         <v>1633</v>
       </c>
-      <c r="F918" s="49"/>
+      <c r="F918" s="40"/>
       <c r="G918" s="8" t="s">
         <v>1634</v>
       </c>
@@ -24555,7 +24511,7 @@
       <c r="E919" s="34" t="s">
         <v>1635</v>
       </c>
-      <c r="F919" s="49"/>
+      <c r="F919" s="40"/>
       <c r="G919" s="8" t="s">
         <v>1636</v>
       </c>
@@ -24576,7 +24532,7 @@
       <c r="E920" s="34" t="s">
         <v>1637</v>
       </c>
-      <c r="F920" s="49"/>
+      <c r="F920" s="40"/>
       <c r="G920" s="8" t="s">
         <v>1638</v>
       </c>
@@ -24597,7 +24553,7 @@
       <c r="E921" s="34" t="s">
         <v>1639</v>
       </c>
-      <c r="F921" s="49"/>
+      <c r="F921" s="40"/>
       <c r="G921" s="8" t="s">
         <v>1640</v>
       </c>
@@ -24609,8 +24565,8 @@
         <v>72</v>
       </c>
       <c r="D922" s="22"/>
-      <c r="E922" s="40"/>
-      <c r="F922" s="53"/>
+      <c r="E922" s="42"/>
+      <c r="F922" s="44"/>
       <c r="G922" s="13" t="s">
         <v>73</v>
       </c>
@@ -24627,7 +24583,7 @@
       <c r="E923" s="37" t="s">
         <v>1641</v>
       </c>
-      <c r="F923" s="48"/>
+      <c r="F923" s="38"/>
       <c r="G923" s="30" t="s">
         <v>1642</v>
       </c>
@@ -24641,8 +24597,8 @@
       <c r="D924" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E924" s="38"/>
-      <c r="F924" s="49"/>
+      <c r="E924" s="39"/>
+      <c r="F924" s="40"/>
       <c r="G924" s="31"/>
     </row>
     <row r="925" spans="1:7" ht="24">
@@ -24661,7 +24617,7 @@
       <c r="E925" s="34" t="s">
         <v>1237</v>
       </c>
-      <c r="F925" s="50"/>
+      <c r="F925" s="41"/>
       <c r="G925" s="24" t="s">
         <v>1643</v>
       </c>
@@ -24682,7 +24638,7 @@
       <c r="E926" s="34" t="s">
         <v>1239</v>
       </c>
-      <c r="F926" s="50"/>
+      <c r="F926" s="41"/>
       <c r="G926" s="24" t="s">
         <v>1644</v>
       </c>
@@ -24703,7 +24659,7 @@
       <c r="E927" s="34" t="s">
         <v>1645</v>
       </c>
-      <c r="F927" s="50"/>
+      <c r="F927" s="41"/>
       <c r="G927" s="24" t="s">
         <v>1646</v>
       </c>
@@ -24724,7 +24680,7 @@
       <c r="E928" s="34" t="s">
         <v>1647</v>
       </c>
-      <c r="F928" s="50"/>
+      <c r="F928" s="41"/>
       <c r="G928" s="24" t="s">
         <v>1648</v>
       </c>
@@ -24745,7 +24701,7 @@
       <c r="E929" s="34" t="s">
         <v>1649</v>
       </c>
-      <c r="F929" s="50"/>
+      <c r="F929" s="41"/>
       <c r="G929" s="24" t="s">
         <v>1650</v>
       </c>
@@ -24766,7 +24722,7 @@
       <c r="E930" s="34" t="s">
         <v>1651</v>
       </c>
-      <c r="F930" s="50"/>
+      <c r="F930" s="41"/>
       <c r="G930" s="24" t="s">
         <v>1652</v>
       </c>
@@ -24787,7 +24743,7 @@
       <c r="E931" s="34" t="s">
         <v>1653</v>
       </c>
-      <c r="F931" s="50"/>
+      <c r="F931" s="41"/>
       <c r="G931" s="24" t="s">
         <v>1654</v>
       </c>
@@ -24808,7 +24764,7 @@
       <c r="E932" s="34" t="s">
         <v>1655</v>
       </c>
-      <c r="F932" s="50"/>
+      <c r="F932" s="41"/>
       <c r="G932" s="24" t="s">
         <v>1656</v>
       </c>
@@ -24829,7 +24785,7 @@
       <c r="E933" s="34" t="s">
         <v>1657</v>
       </c>
-      <c r="F933" s="50"/>
+      <c r="F933" s="41"/>
       <c r="G933" s="24" t="s">
         <v>1658</v>
       </c>
@@ -24850,7 +24806,7 @@
       <c r="E934" s="34" t="s">
         <v>1659</v>
       </c>
-      <c r="F934" s="50"/>
+      <c r="F934" s="41"/>
       <c r="G934" s="24" t="s">
         <v>1660</v>
       </c>
@@ -24871,7 +24827,7 @@
       <c r="E935" s="34" t="s">
         <v>1661</v>
       </c>
-      <c r="F935" s="50"/>
+      <c r="F935" s="41"/>
       <c r="G935" s="24" t="s">
         <v>1662</v>
       </c>
@@ -24892,7 +24848,7 @@
       <c r="E936" s="34" t="s">
         <v>1663</v>
       </c>
-      <c r="F936" s="50"/>
+      <c r="F936" s="41"/>
       <c r="G936" s="24" t="s">
         <v>1664</v>
       </c>
@@ -24913,7 +24869,7 @@
       <c r="E937" s="34" t="s">
         <v>1665</v>
       </c>
-      <c r="F937" s="50"/>
+      <c r="F937" s="41"/>
       <c r="G937" s="24" t="s">
         <v>1666</v>
       </c>
@@ -24934,7 +24890,7 @@
       <c r="E938" s="34" t="s">
         <v>1667</v>
       </c>
-      <c r="F938" s="50"/>
+      <c r="F938" s="41"/>
       <c r="G938" s="24" t="s">
         <v>1668</v>
       </c>
@@ -24952,8 +24908,8 @@
       <c r="D939" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E939" s="39"/>
-      <c r="F939" s="56" t="s">
+      <c r="E939" s="41"/>
+      <c r="F939" s="45" t="s">
         <v>1669</v>
       </c>
       <c r="G939" s="24" t="s">
@@ -24976,7 +24932,7 @@
       <c r="E940" s="34" t="s">
         <v>77</v>
       </c>
-      <c r="F940" s="50"/>
+      <c r="F940" s="41"/>
       <c r="G940" s="24" t="s">
         <v>1672</v>
       </c>
@@ -24997,7 +24953,7 @@
       <c r="E941" s="34" t="s">
         <v>1673</v>
       </c>
-      <c r="F941" s="50"/>
+      <c r="F941" s="41"/>
       <c r="G941" s="24" t="s">
         <v>88</v>
       </c>
@@ -25009,104 +24965,14 @@
         <v>1674</v>
       </c>
       <c r="D942" s="22"/>
-      <c r="E942" s="40"/>
-      <c r="F942" s="51"/>
+      <c r="E942" s="42"/>
+      <c r="F942" s="42"/>
       <c r="G942" s="25" t="s">
         <v>88</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="105">
-    <mergeCell ref="A43:A44"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="E43:E44"/>
-    <mergeCell ref="F43:F44"/>
-    <mergeCell ref="G43:G44"/>
-    <mergeCell ref="A87:A88"/>
-    <mergeCell ref="B87:B88"/>
-    <mergeCell ref="E87:E88"/>
-    <mergeCell ref="F87:F88"/>
-    <mergeCell ref="G87:G88"/>
-    <mergeCell ref="A131:A132"/>
-    <mergeCell ref="B131:B132"/>
-    <mergeCell ref="E131:E132"/>
-    <mergeCell ref="F131:F174"/>
-    <mergeCell ref="G131:G132"/>
-    <mergeCell ref="A175:A176"/>
-    <mergeCell ref="B175:B176"/>
-    <mergeCell ref="E175:E176"/>
-    <mergeCell ref="F175:F176"/>
-    <mergeCell ref="G175:G176"/>
-    <mergeCell ref="A219:A220"/>
-    <mergeCell ref="B219:B220"/>
-    <mergeCell ref="E219:E220"/>
-    <mergeCell ref="F219:F220"/>
-    <mergeCell ref="G219:G220"/>
-    <mergeCell ref="A263:A264"/>
-    <mergeCell ref="B263:B264"/>
-    <mergeCell ref="E263:E264"/>
-    <mergeCell ref="F263:F306"/>
-    <mergeCell ref="G263:G264"/>
-    <mergeCell ref="A307:A308"/>
-    <mergeCell ref="B307:B308"/>
-    <mergeCell ref="E307:E308"/>
-    <mergeCell ref="F307:F308"/>
-    <mergeCell ref="G307:G308"/>
-    <mergeCell ref="A351:A352"/>
-    <mergeCell ref="B351:B352"/>
-    <mergeCell ref="E351:E352"/>
-    <mergeCell ref="F351:F352"/>
-    <mergeCell ref="G351:G352"/>
-    <mergeCell ref="A395:A396"/>
-    <mergeCell ref="B395:B396"/>
-    <mergeCell ref="E395:E396"/>
-    <mergeCell ref="F395:F396"/>
-    <mergeCell ref="G395:G396"/>
-    <mergeCell ref="A439:A440"/>
-    <mergeCell ref="B439:B440"/>
-    <mergeCell ref="E439:E440"/>
-    <mergeCell ref="F439:F440"/>
-    <mergeCell ref="G439:G440"/>
-    <mergeCell ref="A483:A484"/>
-    <mergeCell ref="B483:B484"/>
-    <mergeCell ref="E483:E484"/>
-    <mergeCell ref="F483:F526"/>
-    <mergeCell ref="G483:G484"/>
-    <mergeCell ref="A527:A528"/>
-    <mergeCell ref="B527:B528"/>
-    <mergeCell ref="E527:E528"/>
-    <mergeCell ref="F527:F570"/>
-    <mergeCell ref="G527:G528"/>
-    <mergeCell ref="A571:A572"/>
-    <mergeCell ref="B571:B572"/>
-    <mergeCell ref="E571:E572"/>
-    <mergeCell ref="F571:F614"/>
-    <mergeCell ref="G571:G572"/>
-    <mergeCell ref="A615:A616"/>
-    <mergeCell ref="B615:B616"/>
-    <mergeCell ref="E615:E616"/>
-    <mergeCell ref="F615:F658"/>
-    <mergeCell ref="G615:G616"/>
-    <mergeCell ref="A659:A660"/>
-    <mergeCell ref="B659:B660"/>
-    <mergeCell ref="E659:E660"/>
-    <mergeCell ref="F659:F702"/>
-    <mergeCell ref="G659:G660"/>
-    <mergeCell ref="A703:A704"/>
-    <mergeCell ref="B703:B704"/>
-    <mergeCell ref="E703:E704"/>
-    <mergeCell ref="F703:F746"/>
-    <mergeCell ref="G703:G704"/>
-    <mergeCell ref="A747:A748"/>
-    <mergeCell ref="B747:B748"/>
-    <mergeCell ref="E747:E748"/>
-    <mergeCell ref="F747:F790"/>
-    <mergeCell ref="G747:G748"/>
-    <mergeCell ref="A791:A792"/>
-    <mergeCell ref="B791:B792"/>
-    <mergeCell ref="E791:E792"/>
-    <mergeCell ref="F791:F834"/>
-    <mergeCell ref="G791:G792"/>
     <mergeCell ref="A923:A924"/>
     <mergeCell ref="B923:B924"/>
     <mergeCell ref="E923:E924"/>
@@ -25122,6 +24988,96 @@
     <mergeCell ref="E879:E880"/>
     <mergeCell ref="F879:F922"/>
     <mergeCell ref="G879:G880"/>
+    <mergeCell ref="A747:A748"/>
+    <mergeCell ref="B747:B748"/>
+    <mergeCell ref="E747:E748"/>
+    <mergeCell ref="F747:F790"/>
+    <mergeCell ref="G747:G748"/>
+    <mergeCell ref="A791:A792"/>
+    <mergeCell ref="B791:B792"/>
+    <mergeCell ref="E791:E792"/>
+    <mergeCell ref="F791:F834"/>
+    <mergeCell ref="G791:G792"/>
+    <mergeCell ref="A659:A660"/>
+    <mergeCell ref="B659:B660"/>
+    <mergeCell ref="E659:E660"/>
+    <mergeCell ref="F659:F702"/>
+    <mergeCell ref="G659:G660"/>
+    <mergeCell ref="A703:A704"/>
+    <mergeCell ref="B703:B704"/>
+    <mergeCell ref="E703:E704"/>
+    <mergeCell ref="F703:F746"/>
+    <mergeCell ref="G703:G704"/>
+    <mergeCell ref="A571:A572"/>
+    <mergeCell ref="B571:B572"/>
+    <mergeCell ref="E571:E572"/>
+    <mergeCell ref="F571:F614"/>
+    <mergeCell ref="G571:G572"/>
+    <mergeCell ref="A615:A616"/>
+    <mergeCell ref="B615:B616"/>
+    <mergeCell ref="E615:E616"/>
+    <mergeCell ref="F615:F658"/>
+    <mergeCell ref="G615:G616"/>
+    <mergeCell ref="A483:A484"/>
+    <mergeCell ref="B483:B484"/>
+    <mergeCell ref="E483:E484"/>
+    <mergeCell ref="F483:F526"/>
+    <mergeCell ref="G483:G484"/>
+    <mergeCell ref="A527:A528"/>
+    <mergeCell ref="B527:B528"/>
+    <mergeCell ref="E527:E528"/>
+    <mergeCell ref="F527:F570"/>
+    <mergeCell ref="G527:G528"/>
+    <mergeCell ref="A395:A396"/>
+    <mergeCell ref="B395:B396"/>
+    <mergeCell ref="E395:E396"/>
+    <mergeCell ref="F395:F396"/>
+    <mergeCell ref="G395:G396"/>
+    <mergeCell ref="A439:A440"/>
+    <mergeCell ref="B439:B440"/>
+    <mergeCell ref="E439:E440"/>
+    <mergeCell ref="F439:F440"/>
+    <mergeCell ref="G439:G440"/>
+    <mergeCell ref="A307:A308"/>
+    <mergeCell ref="B307:B308"/>
+    <mergeCell ref="E307:E308"/>
+    <mergeCell ref="F307:F308"/>
+    <mergeCell ref="G307:G308"/>
+    <mergeCell ref="A351:A352"/>
+    <mergeCell ref="B351:B352"/>
+    <mergeCell ref="E351:E352"/>
+    <mergeCell ref="F351:F352"/>
+    <mergeCell ref="G351:G352"/>
+    <mergeCell ref="A219:A220"/>
+    <mergeCell ref="B219:B220"/>
+    <mergeCell ref="E219:E220"/>
+    <mergeCell ref="F219:F220"/>
+    <mergeCell ref="G219:G220"/>
+    <mergeCell ref="A263:A264"/>
+    <mergeCell ref="B263:B264"/>
+    <mergeCell ref="E263:E264"/>
+    <mergeCell ref="F263:F306"/>
+    <mergeCell ref="G263:G264"/>
+    <mergeCell ref="A131:A132"/>
+    <mergeCell ref="B131:B132"/>
+    <mergeCell ref="E131:E132"/>
+    <mergeCell ref="F131:F174"/>
+    <mergeCell ref="G131:G132"/>
+    <mergeCell ref="A175:A176"/>
+    <mergeCell ref="B175:B176"/>
+    <mergeCell ref="E175:E176"/>
+    <mergeCell ref="F175:F176"/>
+    <mergeCell ref="G175:G176"/>
+    <mergeCell ref="A43:A44"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="E43:E44"/>
+    <mergeCell ref="F43:F44"/>
+    <mergeCell ref="G43:G44"/>
+    <mergeCell ref="A87:A88"/>
+    <mergeCell ref="B87:B88"/>
+    <mergeCell ref="E87:E88"/>
+    <mergeCell ref="F87:F88"/>
+    <mergeCell ref="G87:G88"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
